--- a/templates_excel/03_Checklist_Hệ thống mới.xlsx
+++ b/templates_excel/03_Checklist_Hệ thống mới.xlsx
@@ -5,12 +5,12 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://vngms-my.sharepoint.com/personal/quantc_vng_com_vn/Documents/quantc/Task-and-planing/Kiểm soát hardening IT Infrastructure với chuẩn hóa cấu hình/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://vngms-my.sharepoint.com/personal/quantc_vng_com_vn/Documents/quantc/Task-and-planing/Kiểm soát hardening IT Infrastructure với chuẩn hóa cấu hình/Hardening_System_Application/templates_excel/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="89" documentId="13_ncr:1_{24055782-F57B-453E-8ABC-F4DD773A7A72}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{A2E01A7D-34C5-444C-B45C-B49B552D5F68}"/>
+  <xr:revisionPtr revIDLastSave="91" documentId="13_ncr:1_{24055782-F57B-453E-8ABC-F4DD773A7A72}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{48B3BC85-D83F-4BE4-A5A6-2D59A281ADEB}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="500" firstSheet="1" activeTab="5" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="500" firstSheet="1" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Hướng dẫn" sheetId="1" r:id="rId1"/>
@@ -164,15 +164,9 @@
     <t>grep PermitRootLogin /etc/ssh/sshd_config</t>
   </si>
   <si>
-    <t>MaxAuthTries = 5</t>
-  </si>
-  <si>
     <t>grep MaxAuthTries /etc/ssh/sshd_config</t>
   </si>
   <si>
-    <t>LoginGraceTime = 20</t>
-  </si>
-  <si>
     <t>grep LoginGraceTime /etc/ssh/sshd_config</t>
   </si>
   <si>
@@ -1470,6 +1464,12 @@
   </si>
   <si>
     <t>stat -c '%n %a %U:%G' /etc/security/opasswd 2&gt;/dev/null || echo 'file not exist'</t>
+  </si>
+  <si>
+    <t>MaxAuthTries = 4</t>
+  </si>
+  <si>
+    <t>LoginGraceTime = 60</t>
   </si>
 </sst>
 </file>
@@ -1587,6 +1587,7 @@
     <font>
       <sz val="10"/>
       <name val="Arial"/>
+      <family val="2"/>
     </font>
   </fonts>
   <fills count="8">
@@ -1763,6 +1764,30 @@
     <xf numFmtId="0" fontId="14" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="10" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="4" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="6" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="6" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="7" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="7" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
@@ -1808,6 +1833,9 @@
     <xf numFmtId="9" fontId="12" fillId="6" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="12" fillId="5" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="11" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -1815,33 +1843,6 @@
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="10" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="4" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="5" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="6" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="6" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="7" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="7" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -2302,110 +2303,110 @@
   <sheetData>
     <row r="1" spans="2:4" ht="18.75" customHeight="1" x14ac:dyDescent="0.3"/>
     <row r="2" spans="2:4" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B2" s="28" t="s">
+      <c r="B2" s="36" t="s">
         <v>0</v>
       </c>
-      <c r="C2" s="28"/>
-      <c r="D2" s="28"/>
+      <c r="C2" s="36"/>
+      <c r="D2" s="36"/>
     </row>
     <row r="3" spans="2:4" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B3" s="28"/>
-      <c r="C3" s="28"/>
-      <c r="D3" s="28"/>
+      <c r="B3" s="36"/>
+      <c r="C3" s="36"/>
+      <c r="D3" s="36"/>
     </row>
     <row r="4" spans="2:4" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B4" s="28"/>
-      <c r="C4" s="28"/>
-      <c r="D4" s="28"/>
+      <c r="B4" s="36"/>
+      <c r="C4" s="36"/>
+      <c r="D4" s="36"/>
     </row>
     <row r="5" spans="2:4" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B5" s="28"/>
-      <c r="C5" s="28"/>
-      <c r="D5" s="28"/>
+      <c r="B5" s="36"/>
+      <c r="C5" s="36"/>
+      <c r="D5" s="36"/>
     </row>
     <row r="6" spans="2:4" ht="18.75" customHeight="1" x14ac:dyDescent="0.3"/>
     <row r="7" spans="2:4" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B7" s="3" t="s">
         <v>1</v>
       </c>
-      <c r="C7" s="25" t="s">
+      <c r="C7" s="33" t="s">
         <v>2</v>
       </c>
-      <c r="D7" s="25"/>
+      <c r="D7" s="33"/>
     </row>
     <row r="8" spans="2:4" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B8" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="C8" s="25" t="s">
+      <c r="C8" s="33" t="s">
         <v>4</v>
       </c>
-      <c r="D8" s="25"/>
+      <c r="D8" s="33"/>
     </row>
     <row r="9" spans="2:4" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B9" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="C9" s="25" t="s">
+      <c r="C9" s="33" t="s">
         <v>6</v>
       </c>
-      <c r="D9" s="25"/>
+      <c r="D9" s="33"/>
     </row>
     <row r="10" spans="2:4" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B10" s="3" t="s">
         <v>7</v>
       </c>
-      <c r="C10" s="25" t="s">
+      <c r="C10" s="33" t="s">
         <v>8</v>
       </c>
-      <c r="D10" s="25"/>
+      <c r="D10" s="33"/>
     </row>
     <row r="11" spans="2:4" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B11" s="27" t="s">
-        <v>434</v>
-      </c>
-      <c r="C11" s="27"/>
-      <c r="D11" s="27"/>
+      <c r="B11" s="35" t="s">
+        <v>432</v>
+      </c>
+      <c r="C11" s="35"/>
+      <c r="D11" s="35"/>
     </row>
     <row r="12" spans="2:4" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B12" s="25" t="s">
+      <c r="B12" s="33" t="s">
         <v>9</v>
       </c>
-      <c r="C12" s="25"/>
-      <c r="D12" s="25"/>
+      <c r="C12" s="33"/>
+      <c r="D12" s="33"/>
     </row>
     <row r="13" spans="2:4" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B13" s="25" t="s">
+      <c r="B13" s="33" t="s">
         <v>10</v>
       </c>
-      <c r="C13" s="25"/>
-      <c r="D13" s="25"/>
+      <c r="C13" s="33"/>
+      <c r="D13" s="33"/>
     </row>
     <row r="14" spans="2:4" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B14" s="25" t="s">
+      <c r="B14" s="33" t="s">
         <v>11</v>
       </c>
-      <c r="C14" s="25"/>
-      <c r="D14" s="25"/>
+      <c r="C14" s="33"/>
+      <c r="D14" s="33"/>
     </row>
     <row r="15" spans="2:4" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B15" s="25" t="s">
+      <c r="B15" s="33" t="s">
         <v>12</v>
       </c>
-      <c r="C15" s="25"/>
-      <c r="D15" s="25"/>
+      <c r="C15" s="33"/>
+      <c r="D15" s="33"/>
     </row>
     <row r="16" spans="2:4" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B16" s="25" t="s">
+      <c r="B16" s="33" t="s">
         <v>13</v>
       </c>
-      <c r="C16" s="25"/>
-      <c r="D16" s="25"/>
+      <c r="C16" s="33"/>
+      <c r="D16" s="33"/>
     </row>
     <row r="17" spans="2:4" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B17" s="26"/>
-      <c r="C17" s="26"/>
-      <c r="D17" s="26"/>
+      <c r="B17" s="34"/>
+      <c r="C17" s="34"/>
+      <c r="D17" s="34"/>
     </row>
   </sheetData>
   <mergeCells count="12">
@@ -2441,21 +2442,21 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:6" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A1" s="35" t="s">
+      <c r="A1" s="43" t="s">
         <v>14</v>
       </c>
-      <c r="B1" s="35"/>
-      <c r="C1" s="35"/>
-      <c r="D1" s="35"/>
-      <c r="E1" s="35"/>
-      <c r="F1" s="35"/>
+      <c r="B1" s="43"/>
+      <c r="C1" s="43"/>
+      <c r="D1" s="43"/>
+      <c r="E1" s="43"/>
+      <c r="F1" s="43"/>
     </row>
     <row r="2" spans="1:6" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A2" s="36" t="s">
+      <c r="A2" s="44" t="s">
         <v>15</v>
       </c>
-      <c r="B2" s="36"/>
-      <c r="C2" s="36"/>
+      <c r="B2" s="44"/>
+      <c r="C2" s="44"/>
       <c r="D2" s="8" t="s">
         <v>16</v>
       </c>
@@ -2487,14 +2488,14 @@
       </c>
     </row>
     <row r="4" spans="1:6" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A4" s="33" t="s">
-        <v>435</v>
-      </c>
-      <c r="B4" s="33"/>
-      <c r="C4" s="33"/>
-      <c r="D4" s="33"/>
-      <c r="E4" s="33"/>
-      <c r="F4" s="33"/>
+      <c r="A4" s="41" t="s">
+        <v>433</v>
+      </c>
+      <c r="B4" s="41"/>
+      <c r="C4" s="41"/>
+      <c r="D4" s="41"/>
+      <c r="E4" s="41"/>
+      <c r="F4" s="41"/>
     </row>
     <row r="5" spans="1:6" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A5" s="15">
@@ -2510,7 +2511,7 @@
         <v>27</v>
       </c>
       <c r="E5" s="18" t="s">
-        <v>437</v>
+        <v>435</v>
       </c>
       <c r="F5" s="16"/>
     </row>
@@ -2528,7 +2529,7 @@
         <v>29</v>
       </c>
       <c r="E6" s="18" t="s">
-        <v>437</v>
+        <v>435</v>
       </c>
       <c r="F6" s="16"/>
     </row>
@@ -2546,7 +2547,7 @@
         <v>31</v>
       </c>
       <c r="E7" s="18" t="s">
-        <v>437</v>
+        <v>435</v>
       </c>
       <c r="F7" s="16"/>
     </row>
@@ -2564,7 +2565,7 @@
         <v>33</v>
       </c>
       <c r="E8" s="18" t="s">
-        <v>437</v>
+        <v>435</v>
       </c>
       <c r="F8" s="16"/>
     </row>
@@ -2582,19 +2583,19 @@
         <v>35</v>
       </c>
       <c r="E9" s="18" t="s">
-        <v>437</v>
+        <v>435</v>
       </c>
       <c r="F9" s="16"/>
     </row>
     <row r="10" spans="1:6" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A10" s="33" t="s">
+      <c r="A10" s="41" t="s">
         <v>36</v>
       </c>
-      <c r="B10" s="33"/>
-      <c r="C10" s="33"/>
-      <c r="D10" s="33"/>
-      <c r="E10" s="33"/>
-      <c r="F10" s="33"/>
+      <c r="B10" s="41"/>
+      <c r="C10" s="41"/>
+      <c r="D10" s="41"/>
+      <c r="E10" s="41"/>
+      <c r="F10" s="41"/>
     </row>
     <row r="11" spans="1:6" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A11" s="15">
@@ -2610,7 +2611,7 @@
         <v>39</v>
       </c>
       <c r="E11" s="18" t="s">
-        <v>437</v>
+        <v>435</v>
       </c>
       <c r="F11" s="16"/>
     </row>
@@ -2622,13 +2623,13 @@
         <v>37</v>
       </c>
       <c r="C12" s="16" t="s">
+        <v>474</v>
+      </c>
+      <c r="D12" s="17" t="s">
         <v>40</v>
       </c>
-      <c r="D12" s="17" t="s">
-        <v>41</v>
-      </c>
       <c r="E12" s="18" t="s">
-        <v>437</v>
+        <v>435</v>
       </c>
       <c r="F12" s="16"/>
     </row>
@@ -2640,13 +2641,13 @@
         <v>37</v>
       </c>
       <c r="C13" s="16" t="s">
-        <v>42</v>
+        <v>475</v>
       </c>
       <c r="D13" s="17" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="E13" s="18" t="s">
-        <v>437</v>
+        <v>435</v>
       </c>
       <c r="F13" s="16"/>
     </row>
@@ -2658,13 +2659,13 @@
         <v>37</v>
       </c>
       <c r="C14" s="16" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="D14" s="17" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="E14" s="18" t="s">
-        <v>437</v>
+        <v>435</v>
       </c>
       <c r="F14" s="16"/>
     </row>
@@ -2676,13 +2677,13 @@
         <v>37</v>
       </c>
       <c r="C15" s="16" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="D15" s="17" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="E15" s="18" t="s">
-        <v>437</v>
+        <v>435</v>
       </c>
       <c r="F15" s="16"/>
     </row>
@@ -2694,13 +2695,13 @@
         <v>37</v>
       </c>
       <c r="C16" s="16" t="s">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="D16" s="17" t="s">
-        <v>49</v>
+        <v>47</v>
       </c>
       <c r="E16" s="18" t="s">
-        <v>437</v>
+        <v>435</v>
       </c>
       <c r="F16" s="16"/>
     </row>
@@ -2712,13 +2713,13 @@
         <v>37</v>
       </c>
       <c r="C17" s="19" t="s">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="D17" s="17" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="E17" s="18" t="s">
-        <v>437</v>
+        <v>435</v>
       </c>
       <c r="F17" s="16"/>
     </row>
@@ -2730,13 +2731,13 @@
         <v>37</v>
       </c>
       <c r="C18" s="16" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="D18" s="17" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="E18" s="18" t="s">
-        <v>437</v>
+        <v>435</v>
       </c>
       <c r="F18" s="16"/>
     </row>
@@ -2748,13 +2749,13 @@
         <v>37</v>
       </c>
       <c r="C19" s="16" t="s">
-        <v>439</v>
+        <v>437</v>
       </c>
       <c r="D19" s="17" t="s">
-        <v>446</v>
+        <v>444</v>
       </c>
       <c r="E19" s="18" t="s">
-        <v>437</v>
+        <v>435</v>
       </c>
       <c r="F19" s="16"/>
     </row>
@@ -2766,13 +2767,13 @@
         <v>37</v>
       </c>
       <c r="C20" s="16" t="s">
-        <v>440</v>
+        <v>438</v>
       </c>
       <c r="D20" s="17" t="s">
-        <v>447</v>
+        <v>445</v>
       </c>
       <c r="E20" s="18" t="s">
-        <v>437</v>
+        <v>435</v>
       </c>
       <c r="F20" s="16"/>
     </row>
@@ -2784,13 +2785,13 @@
         <v>37</v>
       </c>
       <c r="C21" s="16" t="s">
-        <v>441</v>
+        <v>439</v>
       </c>
       <c r="D21" s="17" t="s">
-        <v>448</v>
+        <v>446</v>
       </c>
       <c r="E21" s="18" t="s">
-        <v>437</v>
+        <v>435</v>
       </c>
       <c r="F21" s="16"/>
     </row>
@@ -2802,13 +2803,13 @@
         <v>37</v>
       </c>
       <c r="C22" s="16" t="s">
-        <v>442</v>
+        <v>440</v>
       </c>
       <c r="D22" s="17" t="s">
-        <v>449</v>
+        <v>447</v>
       </c>
       <c r="E22" s="18" t="s">
-        <v>437</v>
+        <v>435</v>
       </c>
       <c r="F22" s="16"/>
     </row>
@@ -2820,13 +2821,13 @@
         <v>37</v>
       </c>
       <c r="C23" s="16" t="s">
-        <v>443</v>
+        <v>441</v>
       </c>
       <c r="D23" s="17" t="s">
-        <v>450</v>
+        <v>448</v>
       </c>
       <c r="E23" s="18" t="s">
-        <v>437</v>
+        <v>435</v>
       </c>
       <c r="F23" s="16"/>
     </row>
@@ -2838,13 +2839,13 @@
         <v>37</v>
       </c>
       <c r="C24" s="16" t="s">
-        <v>444</v>
+        <v>442</v>
       </c>
       <c r="D24" s="17" t="s">
-        <v>451</v>
+        <v>449</v>
       </c>
       <c r="E24" s="18" t="s">
-        <v>437</v>
+        <v>435</v>
       </c>
       <c r="F24" s="16"/>
     </row>
@@ -2856,41 +2857,41 @@
         <v>37</v>
       </c>
       <c r="C25" s="16" t="s">
-        <v>445</v>
+        <v>443</v>
       </c>
       <c r="D25" s="17" t="s">
-        <v>452</v>
+        <v>450</v>
       </c>
       <c r="E25" s="18" t="s">
-        <v>437</v>
+        <v>435</v>
       </c>
       <c r="F25" s="16"/>
     </row>
     <row r="26" spans="1:6" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A26" s="33" t="s">
-        <v>54</v>
-      </c>
-      <c r="B26" s="33"/>
-      <c r="C26" s="33"/>
-      <c r="D26" s="33"/>
-      <c r="E26" s="33"/>
-      <c r="F26" s="33"/>
+      <c r="A26" s="41" t="s">
+        <v>52</v>
+      </c>
+      <c r="B26" s="41"/>
+      <c r="C26" s="41"/>
+      <c r="D26" s="41"/>
+      <c r="E26" s="41"/>
+      <c r="F26" s="41"/>
     </row>
     <row r="27" spans="1:6" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A27" s="15">
         <v>21</v>
       </c>
       <c r="B27" s="16" t="s">
+        <v>53</v>
+      </c>
+      <c r="C27" s="16" t="s">
+        <v>54</v>
+      </c>
+      <c r="D27" s="17" t="s">
         <v>55</v>
       </c>
-      <c r="C27" s="16" t="s">
-        <v>56</v>
-      </c>
-      <c r="D27" s="17" t="s">
-        <v>57</v>
-      </c>
       <c r="E27" s="18" t="s">
-        <v>437</v>
+        <v>435</v>
       </c>
       <c r="F27" s="16"/>
     </row>
@@ -2899,16 +2900,16 @@
         <v>22</v>
       </c>
       <c r="B28" s="16" t="s">
-        <v>55</v>
+        <v>53</v>
       </c>
       <c r="C28" s="16" t="s">
-        <v>58</v>
+        <v>56</v>
       </c>
       <c r="D28" s="17" t="s">
-        <v>59</v>
+        <v>57</v>
       </c>
       <c r="E28" s="18" t="s">
-        <v>437</v>
+        <v>435</v>
       </c>
       <c r="F28" s="16"/>
     </row>
@@ -2917,16 +2918,16 @@
         <v>23</v>
       </c>
       <c r="B29" s="16" t="s">
-        <v>55</v>
+        <v>53</v>
       </c>
       <c r="C29" s="16" t="s">
-        <v>60</v>
+        <v>58</v>
       </c>
       <c r="D29" s="17" t="s">
-        <v>61</v>
+        <v>59</v>
       </c>
       <c r="E29" s="18" t="s">
-        <v>437</v>
+        <v>435</v>
       </c>
       <c r="F29" s="16"/>
     </row>
@@ -2935,16 +2936,16 @@
         <v>24</v>
       </c>
       <c r="B30" s="16" t="s">
-        <v>55</v>
+        <v>53</v>
       </c>
       <c r="C30" s="16" t="s">
-        <v>62</v>
+        <v>60</v>
       </c>
       <c r="D30" s="17" t="s">
-        <v>63</v>
+        <v>61</v>
       </c>
       <c r="E30" s="18" t="s">
-        <v>437</v>
+        <v>435</v>
       </c>
       <c r="F30" s="16"/>
     </row>
@@ -2953,16 +2954,16 @@
         <v>25</v>
       </c>
       <c r="B31" s="16" t="s">
-        <v>55</v>
+        <v>53</v>
       </c>
       <c r="C31" s="16" t="s">
-        <v>453</v>
+        <v>451</v>
       </c>
       <c r="D31" s="17" t="s">
-        <v>456</v>
+        <v>454</v>
       </c>
       <c r="E31" s="18" t="s">
-        <v>437</v>
+        <v>435</v>
       </c>
       <c r="F31" s="16"/>
     </row>
@@ -2971,16 +2972,16 @@
         <v>26</v>
       </c>
       <c r="B32" s="16" t="s">
-        <v>55</v>
+        <v>53</v>
       </c>
       <c r="C32" s="16" t="s">
-        <v>454</v>
+        <v>452</v>
       </c>
       <c r="D32" s="17" t="s">
-        <v>457</v>
+        <v>455</v>
       </c>
       <c r="E32" s="18" t="s">
-        <v>437</v>
+        <v>435</v>
       </c>
       <c r="F32" s="16"/>
     </row>
@@ -2989,44 +2990,44 @@
         <v>27</v>
       </c>
       <c r="B33" s="16" t="s">
-        <v>55</v>
+        <v>53</v>
       </c>
       <c r="C33" s="16" t="s">
-        <v>455</v>
+        <v>453</v>
       </c>
       <c r="D33" s="17" t="s">
-        <v>458</v>
+        <v>456</v>
       </c>
       <c r="E33" s="18" t="s">
-        <v>437</v>
+        <v>435</v>
       </c>
       <c r="F33" s="16"/>
     </row>
     <row r="34" spans="1:6" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A34" s="33" t="s">
-        <v>436</v>
-      </c>
-      <c r="B34" s="33"/>
-      <c r="C34" s="33"/>
-      <c r="D34" s="33"/>
-      <c r="E34" s="33"/>
-      <c r="F34" s="33"/>
+      <c r="A34" s="41" t="s">
+        <v>434</v>
+      </c>
+      <c r="B34" s="41"/>
+      <c r="C34" s="41"/>
+      <c r="D34" s="41"/>
+      <c r="E34" s="41"/>
+      <c r="F34" s="41"/>
     </row>
     <row r="35" spans="1:6" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A35" s="15">
         <v>28</v>
       </c>
       <c r="B35" s="16" t="s">
+        <v>62</v>
+      </c>
+      <c r="C35" s="16" t="s">
+        <v>63</v>
+      </c>
+      <c r="D35" s="17" t="s">
         <v>64</v>
       </c>
-      <c r="C35" s="16" t="s">
-        <v>65</v>
-      </c>
-      <c r="D35" s="17" t="s">
-        <v>66</v>
-      </c>
       <c r="E35" s="18" t="s">
-        <v>437</v>
+        <v>435</v>
       </c>
       <c r="F35" s="16"/>
     </row>
@@ -3035,16 +3036,16 @@
         <v>29</v>
       </c>
       <c r="B36" s="16" t="s">
-        <v>64</v>
+        <v>62</v>
       </c>
       <c r="C36" s="16" t="s">
-        <v>67</v>
+        <v>65</v>
       </c>
       <c r="D36" s="17" t="s">
-        <v>68</v>
+        <v>66</v>
       </c>
       <c r="E36" s="18" t="s">
-        <v>437</v>
+        <v>435</v>
       </c>
       <c r="F36" s="16"/>
     </row>
@@ -3053,16 +3054,16 @@
         <v>30</v>
       </c>
       <c r="B37" s="16" t="s">
-        <v>64</v>
+        <v>62</v>
       </c>
       <c r="C37" s="16" t="s">
-        <v>69</v>
+        <v>67</v>
       </c>
       <c r="D37" s="17" t="s">
-        <v>70</v>
+        <v>68</v>
       </c>
       <c r="E37" s="18" t="s">
-        <v>437</v>
+        <v>435</v>
       </c>
       <c r="F37" s="16"/>
     </row>
@@ -3071,44 +3072,44 @@
         <v>31</v>
       </c>
       <c r="B38" s="16" t="s">
-        <v>64</v>
+        <v>62</v>
       </c>
       <c r="C38" s="16" t="s">
-        <v>71</v>
+        <v>69</v>
       </c>
       <c r="D38" s="17" t="s">
-        <v>438</v>
+        <v>436</v>
       </c>
       <c r="E38" s="18" t="s">
-        <v>437</v>
+        <v>435</v>
       </c>
       <c r="F38" s="16"/>
     </row>
     <row r="39" spans="1:6" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A39" s="33" t="s">
-        <v>72</v>
-      </c>
-      <c r="B39" s="33"/>
-      <c r="C39" s="33"/>
-      <c r="D39" s="33"/>
-      <c r="E39" s="33"/>
-      <c r="F39" s="33"/>
+      <c r="A39" s="41" t="s">
+        <v>70</v>
+      </c>
+      <c r="B39" s="41"/>
+      <c r="C39" s="41"/>
+      <c r="D39" s="41"/>
+      <c r="E39" s="41"/>
+      <c r="F39" s="41"/>
     </row>
     <row r="40" spans="1:6" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A40" s="15">
         <v>32</v>
       </c>
       <c r="B40" s="16" t="s">
+        <v>71</v>
+      </c>
+      <c r="C40" s="16" t="s">
+        <v>72</v>
+      </c>
+      <c r="D40" s="17" t="s">
         <v>73</v>
       </c>
-      <c r="C40" s="16" t="s">
-        <v>74</v>
-      </c>
-      <c r="D40" s="17" t="s">
-        <v>75</v>
-      </c>
       <c r="E40" s="18" t="s">
-        <v>437</v>
+        <v>435</v>
       </c>
       <c r="F40" s="16"/>
     </row>
@@ -3117,16 +3118,16 @@
         <v>33</v>
       </c>
       <c r="B41" s="16" t="s">
-        <v>73</v>
+        <v>71</v>
       </c>
       <c r="C41" s="16" t="s">
-        <v>76</v>
+        <v>74</v>
       </c>
       <c r="D41" s="17" t="s">
-        <v>77</v>
+        <v>75</v>
       </c>
       <c r="E41" s="18" t="s">
-        <v>437</v>
+        <v>435</v>
       </c>
       <c r="F41" s="16"/>
     </row>
@@ -3135,16 +3136,16 @@
         <v>34</v>
       </c>
       <c r="B42" s="16" t="s">
-        <v>73</v>
+        <v>71</v>
       </c>
       <c r="C42" s="16" t="s">
-        <v>78</v>
+        <v>76</v>
       </c>
       <c r="D42" s="17" t="s">
-        <v>79</v>
+        <v>77</v>
       </c>
       <c r="E42" s="18" t="s">
-        <v>437</v>
+        <v>435</v>
       </c>
       <c r="F42" s="16"/>
     </row>
@@ -3153,16 +3154,16 @@
         <v>35</v>
       </c>
       <c r="B43" s="16" t="s">
-        <v>73</v>
+        <v>71</v>
       </c>
       <c r="C43" s="16" t="s">
-        <v>80</v>
+        <v>78</v>
       </c>
       <c r="D43" s="17" t="s">
-        <v>81</v>
+        <v>79</v>
       </c>
       <c r="E43" s="18" t="s">
-        <v>437</v>
+        <v>435</v>
       </c>
       <c r="F43" s="16"/>
     </row>
@@ -3171,16 +3172,16 @@
         <v>36</v>
       </c>
       <c r="B44" s="16" t="s">
-        <v>73</v>
+        <v>71</v>
       </c>
       <c r="C44" s="16" t="s">
-        <v>82</v>
+        <v>80</v>
       </c>
       <c r="D44" s="17" t="s">
-        <v>83</v>
+        <v>81</v>
       </c>
       <c r="E44" s="18" t="s">
-        <v>437</v>
+        <v>435</v>
       </c>
       <c r="F44" s="16"/>
     </row>
@@ -3189,44 +3190,44 @@
         <v>37</v>
       </c>
       <c r="B45" s="16" t="s">
-        <v>73</v>
+        <v>71</v>
       </c>
       <c r="C45" s="16" t="s">
+        <v>82</v>
+      </c>
+      <c r="D45" s="17" t="s">
+        <v>83</v>
+      </c>
+      <c r="E45" s="18" t="s">
+        <v>435</v>
+      </c>
+      <c r="F45" s="16"/>
+    </row>
+    <row r="46" spans="1:6" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A46" s="41" t="s">
         <v>84</v>
       </c>
-      <c r="D45" s="17" t="s">
-        <v>85</v>
-      </c>
-      <c r="E45" s="18" t="s">
-        <v>437</v>
-      </c>
-      <c r="F45" s="16"/>
-    </row>
-    <row r="46" spans="1:6" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A46" s="33" t="s">
-        <v>86</v>
-      </c>
-      <c r="B46" s="33"/>
-      <c r="C46" s="33"/>
-      <c r="D46" s="33"/>
-      <c r="E46" s="33"/>
-      <c r="F46" s="33"/>
+      <c r="B46" s="41"/>
+      <c r="C46" s="41"/>
+      <c r="D46" s="41"/>
+      <c r="E46" s="41"/>
+      <c r="F46" s="41"/>
     </row>
     <row r="47" spans="1:6" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A47" s="15">
         <v>38</v>
       </c>
       <c r="B47" s="16" t="s">
+        <v>85</v>
+      </c>
+      <c r="C47" s="16" t="s">
+        <v>86</v>
+      </c>
+      <c r="D47" s="17" t="s">
         <v>87</v>
       </c>
-      <c r="C47" s="16" t="s">
-        <v>88</v>
-      </c>
-      <c r="D47" s="17" t="s">
-        <v>89</v>
-      </c>
       <c r="E47" s="18" t="s">
-        <v>437</v>
+        <v>435</v>
       </c>
       <c r="F47" s="16"/>
     </row>
@@ -3235,16 +3236,16 @@
         <v>39</v>
       </c>
       <c r="B48" s="16" t="s">
-        <v>87</v>
+        <v>85</v>
       </c>
       <c r="C48" s="16" t="s">
-        <v>90</v>
+        <v>88</v>
       </c>
       <c r="D48" s="17" t="s">
-        <v>91</v>
+        <v>89</v>
       </c>
       <c r="E48" s="18" t="s">
-        <v>437</v>
+        <v>435</v>
       </c>
       <c r="F48" s="16"/>
     </row>
@@ -3253,44 +3254,44 @@
         <v>40</v>
       </c>
       <c r="B49" s="16" t="s">
-        <v>87</v>
+        <v>85</v>
       </c>
       <c r="C49" s="19" t="s">
+        <v>90</v>
+      </c>
+      <c r="D49" s="17" t="s">
+        <v>91</v>
+      </c>
+      <c r="E49" s="18" t="s">
+        <v>435</v>
+      </c>
+      <c r="F49" s="16"/>
+    </row>
+    <row r="50" spans="1:6" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A50" s="41" t="s">
         <v>92</v>
       </c>
-      <c r="D49" s="17" t="s">
-        <v>93</v>
-      </c>
-      <c r="E49" s="18" t="s">
-        <v>437</v>
-      </c>
-      <c r="F49" s="16"/>
-    </row>
-    <row r="50" spans="1:6" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A50" s="33" t="s">
-        <v>94</v>
-      </c>
-      <c r="B50" s="33"/>
-      <c r="C50" s="33"/>
-      <c r="D50" s="33"/>
-      <c r="E50" s="33"/>
-      <c r="F50" s="33"/>
+      <c r="B50" s="41"/>
+      <c r="C50" s="41"/>
+      <c r="D50" s="41"/>
+      <c r="E50" s="41"/>
+      <c r="F50" s="41"/>
     </row>
     <row r="51" spans="1:6" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A51" s="15">
         <v>41</v>
       </c>
       <c r="B51" s="16" t="s">
+        <v>93</v>
+      </c>
+      <c r="C51" s="16" t="s">
+        <v>94</v>
+      </c>
+      <c r="D51" s="17" t="s">
         <v>95</v>
       </c>
-      <c r="C51" s="16" t="s">
-        <v>96</v>
-      </c>
-      <c r="D51" s="17" t="s">
-        <v>97</v>
-      </c>
       <c r="E51" s="18" t="s">
-        <v>437</v>
+        <v>435</v>
       </c>
       <c r="F51" s="16"/>
     </row>
@@ -3299,16 +3300,16 @@
         <v>42</v>
       </c>
       <c r="B52" s="16" t="s">
-        <v>95</v>
+        <v>93</v>
       </c>
       <c r="C52" s="16" t="s">
-        <v>98</v>
+        <v>96</v>
       </c>
       <c r="D52" s="17" t="s">
-        <v>99</v>
+        <v>97</v>
       </c>
       <c r="E52" s="18" t="s">
-        <v>437</v>
+        <v>435</v>
       </c>
       <c r="F52" s="16"/>
     </row>
@@ -3317,44 +3318,44 @@
         <v>43</v>
       </c>
       <c r="B53" s="16" t="s">
-        <v>95</v>
+        <v>93</v>
       </c>
       <c r="C53" s="16" t="s">
+        <v>98</v>
+      </c>
+      <c r="D53" s="17" t="s">
+        <v>99</v>
+      </c>
+      <c r="E53" s="18" t="s">
+        <v>435</v>
+      </c>
+      <c r="F53" s="16"/>
+    </row>
+    <row r="54" spans="1:6" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A54" s="41" t="s">
         <v>100</v>
       </c>
-      <c r="D53" s="17" t="s">
-        <v>101</v>
-      </c>
-      <c r="E53" s="18" t="s">
-        <v>437</v>
-      </c>
-      <c r="F53" s="16"/>
-    </row>
-    <row r="54" spans="1:6" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A54" s="33" t="s">
-        <v>102</v>
-      </c>
-      <c r="B54" s="33"/>
-      <c r="C54" s="33"/>
-      <c r="D54" s="33"/>
-      <c r="E54" s="33"/>
-      <c r="F54" s="33"/>
+      <c r="B54" s="41"/>
+      <c r="C54" s="41"/>
+      <c r="D54" s="41"/>
+      <c r="E54" s="41"/>
+      <c r="F54" s="41"/>
     </row>
     <row r="55" spans="1:6" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A55" s="15">
         <v>44</v>
       </c>
       <c r="B55" s="16" t="s">
+        <v>101</v>
+      </c>
+      <c r="C55" s="16" t="s">
+        <v>102</v>
+      </c>
+      <c r="D55" s="17" t="s">
         <v>103</v>
       </c>
-      <c r="C55" s="16" t="s">
-        <v>104</v>
-      </c>
-      <c r="D55" s="17" t="s">
-        <v>105</v>
-      </c>
       <c r="E55" s="18" t="s">
-        <v>437</v>
+        <v>435</v>
       </c>
       <c r="F55" s="16"/>
     </row>
@@ -3363,16 +3364,16 @@
         <v>45</v>
       </c>
       <c r="B56" s="16" t="s">
-        <v>103</v>
+        <v>101</v>
       </c>
       <c r="C56" s="16" t="s">
-        <v>106</v>
+        <v>104</v>
       </c>
       <c r="D56" s="17" t="s">
-        <v>107</v>
+        <v>105</v>
       </c>
       <c r="E56" s="18" t="s">
-        <v>437</v>
+        <v>435</v>
       </c>
       <c r="F56" s="16"/>
     </row>
@@ -3381,16 +3382,16 @@
         <v>46</v>
       </c>
       <c r="B57" s="16" t="s">
-        <v>103</v>
+        <v>101</v>
       </c>
       <c r="C57" s="16" t="s">
-        <v>108</v>
+        <v>106</v>
       </c>
       <c r="D57" s="17" t="s">
-        <v>109</v>
+        <v>107</v>
       </c>
       <c r="E57" s="18" t="s">
-        <v>437</v>
+        <v>435</v>
       </c>
       <c r="F57" s="16"/>
     </row>
@@ -3399,16 +3400,16 @@
         <v>47</v>
       </c>
       <c r="B58" s="16" t="s">
-        <v>103</v>
+        <v>101</v>
       </c>
       <c r="C58" s="16" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="D58" s="17" t="s">
-        <v>111</v>
+        <v>109</v>
       </c>
       <c r="E58" s="18" t="s">
-        <v>437</v>
+        <v>435</v>
       </c>
       <c r="F58" s="16"/>
     </row>
@@ -3417,44 +3418,44 @@
         <v>48</v>
       </c>
       <c r="B59" s="16" t="s">
-        <v>103</v>
+        <v>101</v>
       </c>
       <c r="C59" s="16" t="s">
+        <v>110</v>
+      </c>
+      <c r="D59" s="17" t="s">
+        <v>111</v>
+      </c>
+      <c r="E59" s="18" t="s">
+        <v>435</v>
+      </c>
+      <c r="F59" s="16"/>
+    </row>
+    <row r="60" spans="1:6" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A60" s="41" t="s">
         <v>112</v>
       </c>
-      <c r="D59" s="17" t="s">
-        <v>113</v>
-      </c>
-      <c r="E59" s="18" t="s">
-        <v>437</v>
-      </c>
-      <c r="F59" s="16"/>
-    </row>
-    <row r="60" spans="1:6" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A60" s="33" t="s">
-        <v>114</v>
-      </c>
-      <c r="B60" s="33"/>
-      <c r="C60" s="33"/>
-      <c r="D60" s="33"/>
-      <c r="E60" s="33"/>
-      <c r="F60" s="33"/>
+      <c r="B60" s="41"/>
+      <c r="C60" s="41"/>
+      <c r="D60" s="41"/>
+      <c r="E60" s="41"/>
+      <c r="F60" s="41"/>
     </row>
     <row r="61" spans="1:6" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A61" s="15">
         <v>49</v>
       </c>
       <c r="B61" s="16" t="s">
+        <v>113</v>
+      </c>
+      <c r="C61" s="16" t="s">
+        <v>114</v>
+      </c>
+      <c r="D61" s="17" t="s">
         <v>115</v>
       </c>
-      <c r="C61" s="16" t="s">
-        <v>116</v>
-      </c>
-      <c r="D61" s="17" t="s">
-        <v>117</v>
-      </c>
       <c r="E61" s="18" t="s">
-        <v>437</v>
+        <v>435</v>
       </c>
       <c r="F61" s="16"/>
     </row>
@@ -3463,16 +3464,16 @@
         <v>50</v>
       </c>
       <c r="B62" s="16" t="s">
-        <v>115</v>
+        <v>113</v>
       </c>
       <c r="C62" s="16" t="s">
-        <v>118</v>
+        <v>116</v>
       </c>
       <c r="D62" s="17" t="s">
-        <v>119</v>
+        <v>117</v>
       </c>
       <c r="E62" s="18" t="s">
-        <v>437</v>
+        <v>435</v>
       </c>
       <c r="F62" s="16"/>
     </row>
@@ -3481,44 +3482,44 @@
         <v>51</v>
       </c>
       <c r="B63" s="16" t="s">
-        <v>115</v>
+        <v>113</v>
       </c>
       <c r="C63" s="16" t="s">
-        <v>120</v>
+        <v>118</v>
       </c>
       <c r="D63" s="17" t="s">
-        <v>121</v>
+        <v>119</v>
       </c>
       <c r="E63" s="18" t="s">
-        <v>437</v>
+        <v>435</v>
       </c>
       <c r="F63" s="16"/>
     </row>
     <row r="64" spans="1:6" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A64" s="33" t="s">
-        <v>459</v>
-      </c>
-      <c r="B64" s="33"/>
-      <c r="C64" s="33"/>
-      <c r="D64" s="33"/>
-      <c r="E64" s="33"/>
-      <c r="F64" s="33"/>
+      <c r="A64" s="41" t="s">
+        <v>457</v>
+      </c>
+      <c r="B64" s="41"/>
+      <c r="C64" s="41"/>
+      <c r="D64" s="41"/>
+      <c r="E64" s="41"/>
+      <c r="F64" s="41"/>
     </row>
     <row r="65" spans="1:6" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A65" s="15">
         <v>52</v>
       </c>
       <c r="B65" s="16" t="s">
+        <v>120</v>
+      </c>
+      <c r="C65" s="16" t="s">
+        <v>121</v>
+      </c>
+      <c r="D65" s="17" t="s">
         <v>122</v>
       </c>
-      <c r="C65" s="16" t="s">
-        <v>123</v>
-      </c>
-      <c r="D65" s="17" t="s">
-        <v>124</v>
-      </c>
       <c r="E65" s="18" t="s">
-        <v>437</v>
+        <v>435</v>
       </c>
       <c r="F65" s="16"/>
     </row>
@@ -3527,16 +3528,16 @@
         <v>53</v>
       </c>
       <c r="B66" s="16" t="s">
-        <v>122</v>
+        <v>120</v>
       </c>
       <c r="C66" s="16" t="s">
-        <v>125</v>
+        <v>123</v>
       </c>
       <c r="D66" s="17" t="s">
-        <v>126</v>
+        <v>124</v>
       </c>
       <c r="E66" s="18" t="s">
-        <v>437</v>
+        <v>435</v>
       </c>
       <c r="F66" s="16"/>
     </row>
@@ -3545,16 +3546,16 @@
         <v>54</v>
       </c>
       <c r="B67" s="16" t="s">
-        <v>122</v>
+        <v>120</v>
       </c>
       <c r="C67" s="16" t="s">
-        <v>127</v>
+        <v>125</v>
       </c>
       <c r="D67" s="17" t="s">
-        <v>128</v>
+        <v>126</v>
       </c>
       <c r="E67" s="18" t="s">
-        <v>437</v>
+        <v>435</v>
       </c>
       <c r="F67" s="16"/>
     </row>
@@ -3563,44 +3564,44 @@
         <v>55</v>
       </c>
       <c r="B68" s="16" t="s">
-        <v>122</v>
+        <v>120</v>
       </c>
       <c r="C68" s="16" t="s">
-        <v>129</v>
+        <v>127</v>
       </c>
       <c r="D68" s="17" t="s">
-        <v>130</v>
+        <v>128</v>
       </c>
       <c r="E68" s="18" t="s">
-        <v>437</v>
+        <v>435</v>
       </c>
       <c r="F68" s="16"/>
     </row>
     <row r="69" spans="1:6" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A69" s="33" t="s">
-        <v>467</v>
-      </c>
-      <c r="B69" s="33"/>
-      <c r="C69" s="33"/>
-      <c r="D69" s="33"/>
-      <c r="E69" s="33"/>
-      <c r="F69" s="33"/>
+      <c r="A69" s="41" t="s">
+        <v>465</v>
+      </c>
+      <c r="B69" s="41"/>
+      <c r="C69" s="41"/>
+      <c r="D69" s="41"/>
+      <c r="E69" s="41"/>
+      <c r="F69" s="41"/>
     </row>
     <row r="70" spans="1:6" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A70" s="21">
         <v>56</v>
       </c>
       <c r="B70" s="22" t="s">
-        <v>460</v>
+        <v>458</v>
       </c>
       <c r="C70" s="22" t="s">
-        <v>461</v>
+        <v>459</v>
       </c>
       <c r="D70" s="23" t="s">
-        <v>464</v>
+        <v>462</v>
       </c>
       <c r="E70" s="18" t="s">
-        <v>437</v>
+        <v>435</v>
       </c>
       <c r="F70" s="22"/>
     </row>
@@ -3609,16 +3610,16 @@
         <v>57</v>
       </c>
       <c r="B71" s="22" t="s">
+        <v>458</v>
+      </c>
+      <c r="C71" s="22" t="s">
         <v>460</v>
       </c>
-      <c r="C71" s="22" t="s">
-        <v>462</v>
-      </c>
       <c r="D71" s="23" t="s">
-        <v>465</v>
+        <v>463</v>
       </c>
       <c r="E71" s="18" t="s">
-        <v>437</v>
+        <v>435</v>
       </c>
       <c r="F71" s="22"/>
     </row>
@@ -3627,44 +3628,44 @@
         <v>58</v>
       </c>
       <c r="B72" s="22" t="s">
-        <v>460</v>
+        <v>458</v>
       </c>
       <c r="C72" s="22" t="s">
-        <v>463</v>
+        <v>461</v>
       </c>
       <c r="D72" s="23" t="s">
+        <v>464</v>
+      </c>
+      <c r="E72" s="18" t="s">
+        <v>435</v>
+      </c>
+      <c r="F72" s="22"/>
+    </row>
+    <row r="73" spans="1:6" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A73" s="41" t="s">
         <v>466</v>
       </c>
-      <c r="E72" s="18" t="s">
-        <v>437</v>
-      </c>
-      <c r="F72" s="22"/>
-    </row>
-    <row r="73" spans="1:6" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A73" s="33" t="s">
-        <v>468</v>
-      </c>
-      <c r="B73" s="33"/>
-      <c r="C73" s="33"/>
-      <c r="D73" s="33"/>
-      <c r="E73" s="33"/>
-      <c r="F73" s="33"/>
+      <c r="B73" s="41"/>
+      <c r="C73" s="41"/>
+      <c r="D73" s="41"/>
+      <c r="E73" s="41"/>
+      <c r="F73" s="41"/>
     </row>
     <row r="74" spans="1:6" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A74" s="20">
         <v>59</v>
       </c>
       <c r="B74" s="13" t="s">
-        <v>469</v>
+        <v>467</v>
       </c>
       <c r="C74" s="24" t="s">
-        <v>470</v>
+        <v>468</v>
       </c>
       <c r="D74" s="14" t="s">
-        <v>473</v>
+        <v>471</v>
       </c>
       <c r="E74" s="18" t="s">
-        <v>437</v>
+        <v>435</v>
       </c>
       <c r="F74" s="13"/>
     </row>
@@ -3673,16 +3674,16 @@
         <v>60</v>
       </c>
       <c r="B75" s="13" t="s">
+        <v>467</v>
+      </c>
+      <c r="C75" s="24" t="s">
         <v>469</v>
       </c>
-      <c r="C75" s="24" t="s">
-        <v>471</v>
-      </c>
       <c r="D75" s="14" t="s">
-        <v>474</v>
+        <v>472</v>
       </c>
       <c r="E75" s="18" t="s">
-        <v>437</v>
+        <v>435</v>
       </c>
       <c r="F75" s="13"/>
     </row>
@@ -3691,116 +3692,116 @@
         <v>61</v>
       </c>
       <c r="B76" s="13" t="s">
-        <v>469</v>
+        <v>467</v>
       </c>
       <c r="C76" s="24" t="s">
-        <v>472</v>
+        <v>470</v>
       </c>
       <c r="D76" s="14" t="s">
-        <v>475</v>
+        <v>473</v>
       </c>
       <c r="E76" s="18" t="s">
-        <v>437</v>
+        <v>435</v>
       </c>
       <c r="F76" s="13"/>
     </row>
     <row r="77" spans="1:6" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A77" s="34" t="s">
-        <v>131</v>
-      </c>
-      <c r="B77" s="34"/>
-      <c r="C77" s="34"/>
-      <c r="D77" s="34"/>
-      <c r="E77" s="34"/>
-      <c r="F77" s="34"/>
+      <c r="A77" s="42" t="s">
+        <v>129</v>
+      </c>
+      <c r="B77" s="42"/>
+      <c r="C77" s="42"/>
+      <c r="D77" s="42"/>
+      <c r="E77" s="42"/>
+      <c r="F77" s="42"/>
     </row>
     <row r="78" spans="1:6" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A78" s="29" t="s">
-        <v>132</v>
-      </c>
-      <c r="B78" s="29"/>
-      <c r="C78" s="29"/>
-      <c r="D78" s="32">
+      <c r="A78" s="37" t="s">
+        <v>130</v>
+      </c>
+      <c r="B78" s="37"/>
+      <c r="C78" s="37"/>
+      <c r="D78" s="40">
         <f>COUNTA(E4:E76)</f>
         <v>61</v>
       </c>
-      <c r="E78" s="32"/>
-      <c r="F78" s="32"/>
+      <c r="E78" s="40"/>
+      <c r="F78" s="40"/>
     </row>
     <row r="79" spans="1:6" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A79" s="29" t="s">
-        <v>133</v>
-      </c>
-      <c r="B79" s="29"/>
-      <c r="C79" s="29"/>
-      <c r="D79" s="32">
+      <c r="A79" s="37" t="s">
+        <v>131</v>
+      </c>
+      <c r="B79" s="37"/>
+      <c r="C79" s="37"/>
+      <c r="D79" s="40">
         <f>COUNTIF(E4:E68,"PASS")</f>
         <v>0</v>
       </c>
-      <c r="E79" s="32"/>
-      <c r="F79" s="32"/>
+      <c r="E79" s="40"/>
+      <c r="F79" s="40"/>
     </row>
     <row r="80" spans="1:6" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A80" s="29" t="s">
-        <v>134</v>
-      </c>
-      <c r="B80" s="29"/>
-      <c r="C80" s="29"/>
-      <c r="D80" s="32">
+      <c r="A80" s="37" t="s">
+        <v>132</v>
+      </c>
+      <c r="B80" s="37"/>
+      <c r="C80" s="37"/>
+      <c r="D80" s="40">
         <f>COUNTIF(E4:E68,"FAIL")</f>
         <v>0</v>
       </c>
-      <c r="E80" s="32"/>
-      <c r="F80" s="32"/>
+      <c r="E80" s="40"/>
+      <c r="F80" s="40"/>
     </row>
     <row r="81" spans="1:6" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A81" s="29" t="s">
-        <v>135</v>
-      </c>
-      <c r="B81" s="29"/>
-      <c r="C81" s="29"/>
-      <c r="D81" s="32">
+      <c r="A81" s="37" t="s">
+        <v>133</v>
+      </c>
+      <c r="B81" s="37"/>
+      <c r="C81" s="37"/>
+      <c r="D81" s="40">
         <f>COUNTIF(E4:E76,"N/A")</f>
         <v>61</v>
       </c>
-      <c r="E81" s="32"/>
-      <c r="F81" s="32"/>
+      <c r="E81" s="40"/>
+      <c r="F81" s="40"/>
     </row>
     <row r="82" spans="1:6" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A82" s="29" t="s">
-        <v>136</v>
-      </c>
-      <c r="B82" s="29"/>
-      <c r="C82" s="29"/>
-      <c r="D82" s="30">
+      <c r="A82" s="37" t="s">
+        <v>134</v>
+      </c>
+      <c r="B82" s="37"/>
+      <c r="C82" s="37"/>
+      <c r="D82" s="38">
         <f>IFERROR(COUNTIF(E4:E68,"PASS")/(COUNTA(E4:E68)-COUNTIF(E4:E68,"N/A")),0)</f>
         <v>0</v>
       </c>
-      <c r="E82" s="30"/>
-      <c r="F82" s="30"/>
+      <c r="E82" s="38"/>
+      <c r="F82" s="38"/>
     </row>
     <row r="83" spans="1:6" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A83" s="29" t="s">
-        <v>137</v>
-      </c>
-      <c r="B83" s="29"/>
-      <c r="C83" s="29"/>
-      <c r="D83" s="30" t="str">
+      <c r="A83" s="37" t="s">
+        <v>135</v>
+      </c>
+      <c r="B83" s="37"/>
+      <c r="C83" s="37"/>
+      <c r="D83" s="38" t="str">
         <f>IF(IFERROR(COUNTIF(E4:E68,"PASS")/(COUNTA(E4:E68)-COUNTIF(E4:E68,"N/A")),0)=1,"ĐẠT YÊU CẦU","CHƯA ĐẠT - CẦN XỬ LÝ")</f>
         <v>CHƯA ĐẠT - CẦN XỬ LÝ</v>
       </c>
-      <c r="E83" s="30"/>
-      <c r="F83" s="30"/>
+      <c r="E83" s="38"/>
+      <c r="F83" s="38"/>
     </row>
     <row r="84" spans="1:6" ht="18.75" customHeight="1" x14ac:dyDescent="0.3"/>
     <row r="85" spans="1:6" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A85" s="31" t="s">
-        <v>138</v>
-      </c>
-      <c r="B85" s="31"/>
-      <c r="C85" s="31"/>
+      <c r="A85" s="39" t="s">
+        <v>136</v>
+      </c>
+      <c r="B85" s="39"/>
+      <c r="C85" s="39"/>
       <c r="D85" s="7" t="s">
-        <v>139</v>
+        <v>137</v>
       </c>
     </row>
   </sheetData>
@@ -3867,996 +3868,996 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:6" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A1" s="41" t="s">
+      <c r="A1" s="50" t="s">
+        <v>138</v>
+      </c>
+      <c r="B1" s="50"/>
+      <c r="C1" s="50"/>
+      <c r="D1" s="50"/>
+      <c r="E1" s="50"/>
+      <c r="F1" s="50"/>
+    </row>
+    <row r="2" spans="1:6" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A2" s="51" t="s">
+        <v>15</v>
+      </c>
+      <c r="B2" s="51"/>
+      <c r="C2" s="51"/>
+      <c r="D2" s="25" t="s">
+        <v>16</v>
+      </c>
+      <c r="E2" s="25" t="s">
+        <v>17</v>
+      </c>
+      <c r="F2" s="25" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="3" spans="1:6" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A3" s="26" t="s">
+        <v>19</v>
+      </c>
+      <c r="B3" s="26" t="s">
+        <v>20</v>
+      </c>
+      <c r="C3" s="26" t="s">
+        <v>21</v>
+      </c>
+      <c r="D3" s="26" t="s">
+        <v>22</v>
+      </c>
+      <c r="E3" s="26" t="s">
+        <v>23</v>
+      </c>
+      <c r="F3" s="26" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="4" spans="1:6" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A4" s="48" t="s">
+        <v>139</v>
+      </c>
+      <c r="B4" s="48"/>
+      <c r="C4" s="48"/>
+      <c r="D4" s="48"/>
+      <c r="E4" s="48"/>
+      <c r="F4" s="48"/>
+    </row>
+    <row r="5" spans="1:6" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A5" s="27">
+        <v>1</v>
+      </c>
+      <c r="B5" s="28" t="s">
+        <v>25</v>
+      </c>
+      <c r="C5" s="28" t="s">
         <v>140</v>
       </c>
-      <c r="B1" s="41"/>
-      <c r="C1" s="41"/>
-      <c r="D1" s="41"/>
-      <c r="E1" s="41"/>
-      <c r="F1" s="41"/>
-    </row>
-    <row r="2" spans="1:6" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A2" s="42" t="s">
+      <c r="D5" s="28" t="s">
+        <v>141</v>
+      </c>
+      <c r="E5" s="27" t="s">
+        <v>435</v>
+      </c>
+      <c r="F5" s="28"/>
+    </row>
+    <row r="6" spans="1:6" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A6" s="27">
+        <v>2</v>
+      </c>
+      <c r="B6" s="28" t="s">
+        <v>25</v>
+      </c>
+      <c r="C6" s="28" t="s">
+        <v>142</v>
+      </c>
+      <c r="D6" s="28" t="s">
+        <v>143</v>
+      </c>
+      <c r="E6" s="27" t="s">
+        <v>435</v>
+      </c>
+      <c r="F6" s="28"/>
+    </row>
+    <row r="7" spans="1:6" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A7" s="27">
+        <v>3</v>
+      </c>
+      <c r="B7" s="28" t="s">
+        <v>25</v>
+      </c>
+      <c r="C7" s="28" t="s">
+        <v>144</v>
+      </c>
+      <c r="D7" s="28" t="s">
+        <v>145</v>
+      </c>
+      <c r="E7" s="27" t="s">
+        <v>435</v>
+      </c>
+      <c r="F7" s="28"/>
+    </row>
+    <row r="8" spans="1:6" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A8" s="27">
+        <v>4</v>
+      </c>
+      <c r="B8" s="28" t="s">
+        <v>25</v>
+      </c>
+      <c r="C8" s="28" t="s">
+        <v>146</v>
+      </c>
+      <c r="D8" s="28" t="s">
+        <v>147</v>
+      </c>
+      <c r="E8" s="27" t="s">
+        <v>435</v>
+      </c>
+      <c r="F8" s="28"/>
+    </row>
+    <row r="9" spans="1:6" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A9" s="27">
+        <v>5</v>
+      </c>
+      <c r="B9" s="28" t="s">
+        <v>25</v>
+      </c>
+      <c r="C9" s="28" t="s">
+        <v>148</v>
+      </c>
+      <c r="D9" s="28" t="s">
+        <v>149</v>
+      </c>
+      <c r="E9" s="27" t="s">
+        <v>435</v>
+      </c>
+      <c r="F9" s="28"/>
+    </row>
+    <row r="10" spans="1:6" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A10" s="27">
+        <v>6</v>
+      </c>
+      <c r="B10" s="28" t="s">
+        <v>25</v>
+      </c>
+      <c r="C10" s="28" t="s">
+        <v>150</v>
+      </c>
+      <c r="D10" s="28" t="s">
+        <v>151</v>
+      </c>
+      <c r="E10" s="27" t="s">
+        <v>435</v>
+      </c>
+      <c r="F10" s="28"/>
+    </row>
+    <row r="11" spans="1:6" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A11" s="48" t="s">
+        <v>152</v>
+      </c>
+      <c r="B11" s="48"/>
+      <c r="C11" s="48"/>
+      <c r="D11" s="48"/>
+      <c r="E11" s="48"/>
+      <c r="F11" s="48"/>
+    </row>
+    <row r="12" spans="1:6" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A12" s="27">
+        <v>7</v>
+      </c>
+      <c r="B12" s="28" t="s">
+        <v>153</v>
+      </c>
+      <c r="C12" s="28" t="s">
+        <v>154</v>
+      </c>
+      <c r="D12" s="28" t="s">
+        <v>155</v>
+      </c>
+      <c r="E12" s="27" t="s">
+        <v>435</v>
+      </c>
+      <c r="F12" s="28"/>
+    </row>
+    <row r="13" spans="1:6" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A13" s="27">
+        <v>8</v>
+      </c>
+      <c r="B13" s="28" t="s">
+        <v>153</v>
+      </c>
+      <c r="C13" s="28" t="s">
+        <v>156</v>
+      </c>
+      <c r="D13" s="28" t="s">
+        <v>157</v>
+      </c>
+      <c r="E13" s="27" t="s">
+        <v>435</v>
+      </c>
+      <c r="F13" s="28"/>
+    </row>
+    <row r="14" spans="1:6" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A14" s="27">
+        <v>9</v>
+      </c>
+      <c r="B14" s="28" t="s">
+        <v>153</v>
+      </c>
+      <c r="C14" s="28" t="s">
+        <v>158</v>
+      </c>
+      <c r="D14" s="28" t="s">
+        <v>159</v>
+      </c>
+      <c r="E14" s="27" t="s">
+        <v>435</v>
+      </c>
+      <c r="F14" s="28"/>
+    </row>
+    <row r="15" spans="1:6" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A15" s="27">
+        <v>10</v>
+      </c>
+      <c r="B15" s="28" t="s">
+        <v>153</v>
+      </c>
+      <c r="C15" s="28" t="s">
+        <v>160</v>
+      </c>
+      <c r="D15" s="28" t="s">
+        <v>161</v>
+      </c>
+      <c r="E15" s="27" t="s">
+        <v>435</v>
+      </c>
+      <c r="F15" s="28"/>
+    </row>
+    <row r="16" spans="1:6" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A16" s="27">
+        <v>11</v>
+      </c>
+      <c r="B16" s="28" t="s">
+        <v>153</v>
+      </c>
+      <c r="C16" s="28" t="s">
+        <v>162</v>
+      </c>
+      <c r="D16" s="28" t="s">
+        <v>163</v>
+      </c>
+      <c r="E16" s="27" t="s">
+        <v>435</v>
+      </c>
+      <c r="F16" s="28"/>
+    </row>
+    <row r="17" spans="1:6" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A17" s="27">
+        <v>12</v>
+      </c>
+      <c r="B17" s="28" t="s">
+        <v>153</v>
+      </c>
+      <c r="C17" s="28" t="s">
+        <v>164</v>
+      </c>
+      <c r="D17" s="28" t="s">
+        <v>165</v>
+      </c>
+      <c r="E17" s="27" t="s">
+        <v>435</v>
+      </c>
+      <c r="F17" s="28"/>
+    </row>
+    <row r="18" spans="1:6" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A18" s="48" t="s">
+        <v>166</v>
+      </c>
+      <c r="B18" s="48"/>
+      <c r="C18" s="48"/>
+      <c r="D18" s="48"/>
+      <c r="E18" s="48"/>
+      <c r="F18" s="48"/>
+    </row>
+    <row r="19" spans="1:6" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A19" s="27">
+        <v>13</v>
+      </c>
+      <c r="B19" s="28" t="s">
+        <v>167</v>
+      </c>
+      <c r="C19" s="28" t="s">
+        <v>168</v>
+      </c>
+      <c r="D19" s="28" t="s">
+        <v>169</v>
+      </c>
+      <c r="E19" s="27" t="s">
+        <v>435</v>
+      </c>
+      <c r="F19" s="28"/>
+    </row>
+    <row r="20" spans="1:6" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A20" s="27">
+        <v>14</v>
+      </c>
+      <c r="B20" s="28" t="s">
+        <v>167</v>
+      </c>
+      <c r="C20" s="28" t="s">
+        <v>170</v>
+      </c>
+      <c r="D20" s="28" t="s">
+        <v>169</v>
+      </c>
+      <c r="E20" s="27" t="s">
+        <v>435</v>
+      </c>
+      <c r="F20" s="28"/>
+    </row>
+    <row r="21" spans="1:6" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A21" s="27">
         <v>15</v>
       </c>
-      <c r="B2" s="42"/>
-      <c r="C2" s="42"/>
-      <c r="D2" s="43" t="s">
+      <c r="B21" s="28" t="s">
+        <v>167</v>
+      </c>
+      <c r="C21" s="28" t="s">
+        <v>171</v>
+      </c>
+      <c r="D21" s="28" t="s">
+        <v>169</v>
+      </c>
+      <c r="E21" s="27" t="s">
+        <v>435</v>
+      </c>
+      <c r="F21" s="28"/>
+    </row>
+    <row r="22" spans="1:6" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A22" s="48" t="s">
+        <v>172</v>
+      </c>
+      <c r="B22" s="48"/>
+      <c r="C22" s="48"/>
+      <c r="D22" s="48"/>
+      <c r="E22" s="48"/>
+      <c r="F22" s="48"/>
+    </row>
+    <row r="23" spans="1:6" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A23" s="27">
         <v>16</v>
       </c>
-      <c r="E2" s="43" t="s">
+      <c r="B23" s="28" t="s">
+        <v>173</v>
+      </c>
+      <c r="C23" s="28" t="s">
+        <v>174</v>
+      </c>
+      <c r="D23" s="28" t="s">
+        <v>175</v>
+      </c>
+      <c r="E23" s="27" t="s">
+        <v>435</v>
+      </c>
+      <c r="F23" s="28"/>
+    </row>
+    <row r="24" spans="1:6" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A24" s="27">
         <v>17</v>
       </c>
-      <c r="F2" s="43" t="s">
+      <c r="B24" s="28" t="s">
+        <v>173</v>
+      </c>
+      <c r="C24" s="28" t="s">
+        <v>176</v>
+      </c>
+      <c r="D24" s="28" t="s">
+        <v>177</v>
+      </c>
+      <c r="E24" s="27" t="s">
+        <v>435</v>
+      </c>
+      <c r="F24" s="28"/>
+    </row>
+    <row r="25" spans="1:6" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A25" s="27">
         <v>18</v>
       </c>
-    </row>
-    <row r="3" spans="1:6" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A3" s="44" t="s">
+      <c r="B25" s="28" t="s">
+        <v>173</v>
+      </c>
+      <c r="C25" s="28" t="s">
+        <v>178</v>
+      </c>
+      <c r="D25" s="28" t="s">
+        <v>179</v>
+      </c>
+      <c r="E25" s="27" t="s">
+        <v>435</v>
+      </c>
+      <c r="F25" s="28"/>
+    </row>
+    <row r="26" spans="1:6" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A26" s="27">
         <v>19</v>
       </c>
-      <c r="B3" s="44" t="s">
+      <c r="B26" s="28" t="s">
+        <v>173</v>
+      </c>
+      <c r="C26" s="28" t="s">
+        <v>180</v>
+      </c>
+      <c r="D26" s="28" t="s">
+        <v>181</v>
+      </c>
+      <c r="E26" s="27" t="s">
+        <v>435</v>
+      </c>
+      <c r="F26" s="28"/>
+    </row>
+    <row r="27" spans="1:6" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A27" s="27">
         <v>20</v>
       </c>
-      <c r="C3" s="44" t="s">
+      <c r="B27" s="28" t="s">
+        <v>173</v>
+      </c>
+      <c r="C27" s="28" t="s">
+        <v>182</v>
+      </c>
+      <c r="D27" s="28" t="s">
+        <v>183</v>
+      </c>
+      <c r="E27" s="27" t="s">
+        <v>435</v>
+      </c>
+      <c r="F27" s="28"/>
+    </row>
+    <row r="28" spans="1:6" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A28" s="27">
         <v>21</v>
       </c>
-      <c r="D3" s="44" t="s">
+      <c r="B28" s="28" t="s">
+        <v>173</v>
+      </c>
+      <c r="C28" s="28" t="s">
+        <v>184</v>
+      </c>
+      <c r="D28" s="28" t="s">
+        <v>185</v>
+      </c>
+      <c r="E28" s="27" t="s">
+        <v>435</v>
+      </c>
+      <c r="F28" s="28"/>
+    </row>
+    <row r="29" spans="1:6" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A29" s="27">
         <v>22</v>
       </c>
-      <c r="E3" s="44" t="s">
+      <c r="B29" s="28" t="s">
+        <v>173</v>
+      </c>
+      <c r="C29" s="28" t="s">
+        <v>186</v>
+      </c>
+      <c r="D29" s="28" t="s">
+        <v>187</v>
+      </c>
+      <c r="E29" s="27" t="s">
+        <v>435</v>
+      </c>
+      <c r="F29" s="28"/>
+    </row>
+    <row r="30" spans="1:6" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A30" s="48" t="s">
+        <v>188</v>
+      </c>
+      <c r="B30" s="48"/>
+      <c r="C30" s="48"/>
+      <c r="D30" s="48"/>
+      <c r="E30" s="48"/>
+      <c r="F30" s="48"/>
+    </row>
+    <row r="31" spans="1:6" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A31" s="27">
         <v>23</v>
       </c>
-      <c r="F3" s="44" t="s">
+      <c r="B31" s="28" t="s">
+        <v>189</v>
+      </c>
+      <c r="C31" s="28" t="s">
+        <v>190</v>
+      </c>
+      <c r="D31" s="28" t="s">
+        <v>191</v>
+      </c>
+      <c r="E31" s="27" t="s">
+        <v>435</v>
+      </c>
+      <c r="F31" s="28"/>
+    </row>
+    <row r="32" spans="1:6" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A32" s="27">
         <v>24</v>
       </c>
-    </row>
-    <row r="4" spans="1:6" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A4" s="45" t="s">
-        <v>141</v>
-      </c>
-      <c r="B4" s="45"/>
-      <c r="C4" s="45"/>
-      <c r="D4" s="45"/>
-      <c r="E4" s="45"/>
-      <c r="F4" s="45"/>
-    </row>
-    <row r="5" spans="1:6" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A5" s="46">
-        <v>1</v>
-      </c>
-      <c r="B5" s="47" t="s">
+      <c r="B32" s="28" t="s">
+        <v>189</v>
+      </c>
+      <c r="C32" s="28" t="s">
+        <v>192</v>
+      </c>
+      <c r="D32" s="28" t="s">
+        <v>193</v>
+      </c>
+      <c r="E32" s="27" t="s">
+        <v>435</v>
+      </c>
+      <c r="F32" s="28"/>
+    </row>
+    <row r="33" spans="1:6" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A33" s="27">
         <v>25</v>
       </c>
-      <c r="C5" s="47" t="s">
-        <v>142</v>
-      </c>
-      <c r="D5" s="47" t="s">
-        <v>143</v>
-      </c>
-      <c r="E5" s="46" t="s">
-        <v>437</v>
-      </c>
-      <c r="F5" s="47"/>
-    </row>
-    <row r="6" spans="1:6" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A6" s="46">
-        <v>2</v>
-      </c>
-      <c r="B6" s="47" t="s">
-        <v>25</v>
-      </c>
-      <c r="C6" s="47" t="s">
-        <v>144</v>
-      </c>
-      <c r="D6" s="47" t="s">
-        <v>145</v>
-      </c>
-      <c r="E6" s="46" t="s">
-        <v>437</v>
-      </c>
-      <c r="F6" s="47"/>
-    </row>
-    <row r="7" spans="1:6" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A7" s="46">
-        <v>3</v>
-      </c>
-      <c r="B7" s="47" t="s">
-        <v>25</v>
-      </c>
-      <c r="C7" s="47" t="s">
-        <v>146</v>
-      </c>
-      <c r="D7" s="47" t="s">
-        <v>147</v>
-      </c>
-      <c r="E7" s="46" t="s">
-        <v>437</v>
-      </c>
-      <c r="F7" s="47"/>
-    </row>
-    <row r="8" spans="1:6" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A8" s="46">
-        <v>4</v>
-      </c>
-      <c r="B8" s="47" t="s">
-        <v>25</v>
-      </c>
-      <c r="C8" s="47" t="s">
-        <v>148</v>
-      </c>
-      <c r="D8" s="47" t="s">
-        <v>149</v>
-      </c>
-      <c r="E8" s="46" t="s">
-        <v>437</v>
-      </c>
-      <c r="F8" s="47"/>
-    </row>
-    <row r="9" spans="1:6" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A9" s="46">
-        <v>5</v>
-      </c>
-      <c r="B9" s="47" t="s">
-        <v>25</v>
-      </c>
-      <c r="C9" s="47" t="s">
-        <v>150</v>
-      </c>
-      <c r="D9" s="47" t="s">
-        <v>151</v>
-      </c>
-      <c r="E9" s="46" t="s">
-        <v>437</v>
-      </c>
-      <c r="F9" s="47"/>
-    </row>
-    <row r="10" spans="1:6" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A10" s="46">
-        <v>6</v>
-      </c>
-      <c r="B10" s="47" t="s">
-        <v>25</v>
-      </c>
-      <c r="C10" s="47" t="s">
-        <v>152</v>
-      </c>
-      <c r="D10" s="47" t="s">
-        <v>153</v>
-      </c>
-      <c r="E10" s="46" t="s">
-        <v>437</v>
-      </c>
-      <c r="F10" s="47"/>
-    </row>
-    <row r="11" spans="1:6" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A11" s="45" t="s">
-        <v>154</v>
-      </c>
-      <c r="B11" s="45"/>
-      <c r="C11" s="45"/>
-      <c r="D11" s="45"/>
-      <c r="E11" s="45"/>
-      <c r="F11" s="45"/>
-    </row>
-    <row r="12" spans="1:6" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A12" s="46">
-        <v>7</v>
-      </c>
-      <c r="B12" s="47" t="s">
-        <v>155</v>
-      </c>
-      <c r="C12" s="47" t="s">
-        <v>156</v>
-      </c>
-      <c r="D12" s="47" t="s">
-        <v>157</v>
-      </c>
-      <c r="E12" s="46" t="s">
-        <v>437</v>
-      </c>
-      <c r="F12" s="47"/>
-    </row>
-    <row r="13" spans="1:6" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A13" s="46">
-        <v>8</v>
-      </c>
-      <c r="B13" s="47" t="s">
-        <v>155</v>
-      </c>
-      <c r="C13" s="47" t="s">
-        <v>158</v>
-      </c>
-      <c r="D13" s="47" t="s">
-        <v>159</v>
-      </c>
-      <c r="E13" s="46" t="s">
-        <v>437</v>
-      </c>
-      <c r="F13" s="47"/>
-    </row>
-    <row r="14" spans="1:6" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A14" s="46">
-        <v>9</v>
-      </c>
-      <c r="B14" s="47" t="s">
-        <v>155</v>
-      </c>
-      <c r="C14" s="47" t="s">
-        <v>160</v>
-      </c>
-      <c r="D14" s="47" t="s">
-        <v>161</v>
-      </c>
-      <c r="E14" s="46" t="s">
-        <v>437</v>
-      </c>
-      <c r="F14" s="47"/>
-    </row>
-    <row r="15" spans="1:6" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A15" s="46">
-        <v>10</v>
-      </c>
-      <c r="B15" s="47" t="s">
-        <v>155</v>
-      </c>
-      <c r="C15" s="47" t="s">
-        <v>162</v>
-      </c>
-      <c r="D15" s="47" t="s">
-        <v>163</v>
-      </c>
-      <c r="E15" s="46" t="s">
-        <v>437</v>
-      </c>
-      <c r="F15" s="47"/>
-    </row>
-    <row r="16" spans="1:6" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A16" s="46">
-        <v>11</v>
-      </c>
-      <c r="B16" s="47" t="s">
-        <v>155</v>
-      </c>
-      <c r="C16" s="47" t="s">
-        <v>164</v>
-      </c>
-      <c r="D16" s="47" t="s">
-        <v>165</v>
-      </c>
-      <c r="E16" s="46" t="s">
-        <v>437</v>
-      </c>
-      <c r="F16" s="47"/>
-    </row>
-    <row r="17" spans="1:6" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A17" s="46">
-        <v>12</v>
-      </c>
-      <c r="B17" s="47" t="s">
-        <v>155</v>
-      </c>
-      <c r="C17" s="47" t="s">
-        <v>166</v>
-      </c>
-      <c r="D17" s="47" t="s">
-        <v>167</v>
-      </c>
-      <c r="E17" s="46" t="s">
-        <v>437</v>
-      </c>
-      <c r="F17" s="47"/>
-    </row>
-    <row r="18" spans="1:6" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A18" s="45" t="s">
-        <v>168</v>
-      </c>
-      <c r="B18" s="45"/>
-      <c r="C18" s="45"/>
-      <c r="D18" s="45"/>
-      <c r="E18" s="45"/>
-      <c r="F18" s="45"/>
-    </row>
-    <row r="19" spans="1:6" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A19" s="46">
-        <v>13</v>
-      </c>
-      <c r="B19" s="47" t="s">
-        <v>169</v>
-      </c>
-      <c r="C19" s="47" t="s">
-        <v>170</v>
-      </c>
-      <c r="D19" s="47" t="s">
-        <v>171</v>
-      </c>
-      <c r="E19" s="46" t="s">
-        <v>437</v>
-      </c>
-      <c r="F19" s="47"/>
-    </row>
-    <row r="20" spans="1:6" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A20" s="46">
-        <v>14</v>
-      </c>
-      <c r="B20" s="47" t="s">
-        <v>169</v>
-      </c>
-      <c r="C20" s="47" t="s">
-        <v>172</v>
-      </c>
-      <c r="D20" s="47" t="s">
-        <v>171</v>
-      </c>
-      <c r="E20" s="46" t="s">
-        <v>437</v>
-      </c>
-      <c r="F20" s="47"/>
-    </row>
-    <row r="21" spans="1:6" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A21" s="46">
-        <v>15</v>
-      </c>
-      <c r="B21" s="47" t="s">
-        <v>169</v>
-      </c>
-      <c r="C21" s="47" t="s">
-        <v>173</v>
-      </c>
-      <c r="D21" s="47" t="s">
-        <v>171</v>
-      </c>
-      <c r="E21" s="46" t="s">
-        <v>437</v>
-      </c>
-      <c r="F21" s="47"/>
-    </row>
-    <row r="22" spans="1:6" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A22" s="45" t="s">
-        <v>174</v>
-      </c>
-      <c r="B22" s="45"/>
-      <c r="C22" s="45"/>
-      <c r="D22" s="45"/>
-      <c r="E22" s="45"/>
-      <c r="F22" s="45"/>
-    </row>
-    <row r="23" spans="1:6" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A23" s="46">
-        <v>16</v>
-      </c>
-      <c r="B23" s="47" t="s">
-        <v>175</v>
-      </c>
-      <c r="C23" s="47" t="s">
-        <v>176</v>
-      </c>
-      <c r="D23" s="47" t="s">
-        <v>177</v>
-      </c>
-      <c r="E23" s="46" t="s">
-        <v>437</v>
-      </c>
-      <c r="F23" s="47"/>
-    </row>
-    <row r="24" spans="1:6" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A24" s="46">
-        <v>17</v>
-      </c>
-      <c r="B24" s="47" t="s">
-        <v>175</v>
-      </c>
-      <c r="C24" s="47" t="s">
-        <v>178</v>
-      </c>
-      <c r="D24" s="47" t="s">
-        <v>179</v>
-      </c>
-      <c r="E24" s="46" t="s">
-        <v>437</v>
-      </c>
-      <c r="F24" s="47"/>
-    </row>
-    <row r="25" spans="1:6" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A25" s="46">
-        <v>18</v>
-      </c>
-      <c r="B25" s="47" t="s">
-        <v>175</v>
-      </c>
-      <c r="C25" s="47" t="s">
-        <v>180</v>
-      </c>
-      <c r="D25" s="47" t="s">
-        <v>181</v>
-      </c>
-      <c r="E25" s="46" t="s">
-        <v>437</v>
-      </c>
-      <c r="F25" s="47"/>
-    </row>
-    <row r="26" spans="1:6" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A26" s="46">
-        <v>19</v>
-      </c>
-      <c r="B26" s="47" t="s">
-        <v>175</v>
-      </c>
-      <c r="C26" s="47" t="s">
-        <v>182</v>
-      </c>
-      <c r="D26" s="47" t="s">
-        <v>183</v>
-      </c>
-      <c r="E26" s="46" t="s">
-        <v>437</v>
-      </c>
-      <c r="F26" s="47"/>
-    </row>
-    <row r="27" spans="1:6" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A27" s="46">
-        <v>20</v>
-      </c>
-      <c r="B27" s="47" t="s">
-        <v>175</v>
-      </c>
-      <c r="C27" s="47" t="s">
-        <v>184</v>
-      </c>
-      <c r="D27" s="47" t="s">
-        <v>185</v>
-      </c>
-      <c r="E27" s="46" t="s">
-        <v>437</v>
-      </c>
-      <c r="F27" s="47"/>
-    </row>
-    <row r="28" spans="1:6" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A28" s="46">
-        <v>21</v>
-      </c>
-      <c r="B28" s="47" t="s">
-        <v>175</v>
-      </c>
-      <c r="C28" s="47" t="s">
-        <v>186</v>
-      </c>
-      <c r="D28" s="47" t="s">
-        <v>187</v>
-      </c>
-      <c r="E28" s="46" t="s">
-        <v>437</v>
-      </c>
-      <c r="F28" s="47"/>
-    </row>
-    <row r="29" spans="1:6" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A29" s="46">
-        <v>22</v>
-      </c>
-      <c r="B29" s="47" t="s">
-        <v>175</v>
-      </c>
-      <c r="C29" s="47" t="s">
-        <v>188</v>
-      </c>
-      <c r="D29" s="47" t="s">
+      <c r="B33" s="28" t="s">
         <v>189</v>
       </c>
-      <c r="E29" s="46" t="s">
-        <v>437</v>
-      </c>
-      <c r="F29" s="47"/>
-    </row>
-    <row r="30" spans="1:6" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A30" s="45" t="s">
-        <v>190</v>
-      </c>
-      <c r="B30" s="45"/>
-      <c r="C30" s="45"/>
-      <c r="D30" s="45"/>
-      <c r="E30" s="45"/>
-      <c r="F30" s="45"/>
-    </row>
-    <row r="31" spans="1:6" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A31" s="46">
-        <v>23</v>
-      </c>
-      <c r="B31" s="47" t="s">
-        <v>191</v>
-      </c>
-      <c r="C31" s="47" t="s">
-        <v>192</v>
-      </c>
-      <c r="D31" s="47" t="s">
-        <v>193</v>
-      </c>
-      <c r="E31" s="46" t="s">
-        <v>437</v>
-      </c>
-      <c r="F31" s="47"/>
-    </row>
-    <row r="32" spans="1:6" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A32" s="46">
-        <v>24</v>
-      </c>
-      <c r="B32" s="47" t="s">
-        <v>191</v>
-      </c>
-      <c r="C32" s="47" t="s">
+      <c r="C33" s="28" t="s">
         <v>194</v>
       </c>
-      <c r="D32" s="47" t="s">
+      <c r="D33" s="28" t="s">
         <v>195</v>
       </c>
-      <c r="E32" s="46" t="s">
-        <v>437</v>
-      </c>
-      <c r="F32" s="47"/>
-    </row>
-    <row r="33" spans="1:6" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A33" s="46">
-        <v>25</v>
-      </c>
-      <c r="B33" s="47" t="s">
-        <v>191</v>
-      </c>
-      <c r="C33" s="47" t="s">
+      <c r="E33" s="27" t="s">
+        <v>435</v>
+      </c>
+      <c r="F33" s="28"/>
+    </row>
+    <row r="34" spans="1:6" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A34" s="27">
+        <v>26</v>
+      </c>
+      <c r="B34" s="28" t="s">
+        <v>189</v>
+      </c>
+      <c r="C34" s="28" t="s">
         <v>196</v>
       </c>
-      <c r="D33" s="47" t="s">
+      <c r="D34" s="28" t="s">
         <v>197</v>
       </c>
-      <c r="E33" s="46" t="s">
-        <v>437</v>
-      </c>
-      <c r="F33" s="47"/>
-    </row>
-    <row r="34" spans="1:6" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A34" s="46">
-        <v>26</v>
-      </c>
-      <c r="B34" s="47" t="s">
-        <v>191</v>
-      </c>
-      <c r="C34" s="47" t="s">
+      <c r="E34" s="27" t="s">
+        <v>435</v>
+      </c>
+      <c r="F34" s="28"/>
+    </row>
+    <row r="35" spans="1:6" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A35" s="48" t="s">
         <v>198</v>
       </c>
-      <c r="D34" s="47" t="s">
+      <c r="B35" s="48"/>
+      <c r="C35" s="48"/>
+      <c r="D35" s="48"/>
+      <c r="E35" s="48"/>
+      <c r="F35" s="48"/>
+    </row>
+    <row r="36" spans="1:6" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A36" s="27">
+        <v>27</v>
+      </c>
+      <c r="B36" s="28" t="s">
         <v>199</v>
       </c>
-      <c r="E34" s="46" t="s">
-        <v>437</v>
-      </c>
-      <c r="F34" s="47"/>
-    </row>
-    <row r="35" spans="1:6" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A35" s="45" t="s">
+      <c r="C36" s="28" t="s">
         <v>200</v>
       </c>
-      <c r="B35" s="45"/>
-      <c r="C35" s="45"/>
-      <c r="D35" s="45"/>
-      <c r="E35" s="45"/>
-      <c r="F35" s="45"/>
-    </row>
-    <row r="36" spans="1:6" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A36" s="46">
-        <v>27</v>
-      </c>
-      <c r="B36" s="47" t="s">
+      <c r="D36" s="28" t="s">
         <v>201</v>
       </c>
-      <c r="C36" s="47" t="s">
+      <c r="E36" s="27" t="s">
+        <v>435</v>
+      </c>
+      <c r="F36" s="28"/>
+    </row>
+    <row r="37" spans="1:6" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A37" s="27">
+        <v>28</v>
+      </c>
+      <c r="B37" s="28" t="s">
+        <v>199</v>
+      </c>
+      <c r="C37" s="28" t="s">
         <v>202</v>
       </c>
-      <c r="D36" s="47" t="s">
+      <c r="D37" s="28" t="s">
         <v>203</v>
       </c>
-      <c r="E36" s="46" t="s">
-        <v>437</v>
-      </c>
-      <c r="F36" s="47"/>
-    </row>
-    <row r="37" spans="1:6" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A37" s="46">
-        <v>28</v>
-      </c>
-      <c r="B37" s="47" t="s">
-        <v>201</v>
-      </c>
-      <c r="C37" s="47" t="s">
+      <c r="E37" s="27" t="s">
+        <v>435</v>
+      </c>
+      <c r="F37" s="28"/>
+    </row>
+    <row r="38" spans="1:6" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A38" s="27">
+        <v>29</v>
+      </c>
+      <c r="B38" s="28" t="s">
+        <v>199</v>
+      </c>
+      <c r="C38" s="28" t="s">
         <v>204</v>
       </c>
-      <c r="D37" s="47" t="s">
+      <c r="D38" s="28" t="s">
         <v>205</v>
       </c>
-      <c r="E37" s="46" t="s">
-        <v>437</v>
-      </c>
-      <c r="F37" s="47"/>
-    </row>
-    <row r="38" spans="1:6" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A38" s="46">
-        <v>29</v>
-      </c>
-      <c r="B38" s="47" t="s">
-        <v>201</v>
-      </c>
-      <c r="C38" s="47" t="s">
+      <c r="E38" s="27" t="s">
+        <v>435</v>
+      </c>
+      <c r="F38" s="28"/>
+    </row>
+    <row r="39" spans="1:6" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A39" s="27">
+        <v>30</v>
+      </c>
+      <c r="B39" s="28" t="s">
+        <v>199</v>
+      </c>
+      <c r="C39" s="28" t="s">
         <v>206</v>
       </c>
-      <c r="D38" s="47" t="s">
+      <c r="D39" s="28" t="s">
         <v>207</v>
       </c>
-      <c r="E38" s="46" t="s">
-        <v>437</v>
-      </c>
-      <c r="F38" s="47"/>
-    </row>
-    <row r="39" spans="1:6" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A39" s="46">
-        <v>30</v>
-      </c>
-      <c r="B39" s="47" t="s">
-        <v>201</v>
-      </c>
-      <c r="C39" s="47" t="s">
+      <c r="E39" s="27" t="s">
+        <v>435</v>
+      </c>
+      <c r="F39" s="28"/>
+    </row>
+    <row r="40" spans="1:6" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A40" s="27">
+        <v>31</v>
+      </c>
+      <c r="B40" s="28" t="s">
+        <v>199</v>
+      </c>
+      <c r="C40" s="28" t="s">
         <v>208</v>
       </c>
-      <c r="D39" s="47" t="s">
+      <c r="D40" s="28" t="s">
         <v>209</v>
       </c>
-      <c r="E39" s="46" t="s">
-        <v>437</v>
-      </c>
-      <c r="F39" s="47"/>
-    </row>
-    <row r="40" spans="1:6" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A40" s="46">
-        <v>31</v>
-      </c>
-      <c r="B40" s="47" t="s">
-        <v>201</v>
-      </c>
-      <c r="C40" s="47" t="s">
+      <c r="E40" s="27" t="s">
+        <v>435</v>
+      </c>
+      <c r="F40" s="28"/>
+    </row>
+    <row r="41" spans="1:6" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A41" s="27">
+        <v>32</v>
+      </c>
+      <c r="B41" s="28" t="s">
+        <v>199</v>
+      </c>
+      <c r="C41" s="28" t="s">
         <v>210</v>
       </c>
-      <c r="D40" s="47" t="s">
+      <c r="D41" s="28" t="s">
         <v>211</v>
       </c>
-      <c r="E40" s="46" t="s">
-        <v>437</v>
-      </c>
-      <c r="F40" s="47"/>
-    </row>
-    <row r="41" spans="1:6" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A41" s="46">
-        <v>32</v>
-      </c>
-      <c r="B41" s="47" t="s">
-        <v>201</v>
-      </c>
-      <c r="C41" s="47" t="s">
+      <c r="E41" s="27" t="s">
+        <v>435</v>
+      </c>
+      <c r="F41" s="28"/>
+    </row>
+    <row r="42" spans="1:6" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A42" s="27">
+        <v>33</v>
+      </c>
+      <c r="B42" s="28" t="s">
+        <v>199</v>
+      </c>
+      <c r="C42" s="28" t="s">
         <v>212</v>
       </c>
-      <c r="D41" s="47" t="s">
+      <c r="D42" s="28" t="s">
         <v>213</v>
       </c>
-      <c r="E41" s="46" t="s">
-        <v>437</v>
-      </c>
-      <c r="F41" s="47"/>
-    </row>
-    <row r="42" spans="1:6" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A42" s="46">
-        <v>33</v>
-      </c>
-      <c r="B42" s="47" t="s">
-        <v>201</v>
-      </c>
-      <c r="C42" s="47" t="s">
+      <c r="E42" s="27" t="s">
+        <v>435</v>
+      </c>
+      <c r="F42" s="28"/>
+    </row>
+    <row r="43" spans="1:6" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A43" s="27">
+        <v>34</v>
+      </c>
+      <c r="B43" s="28" t="s">
+        <v>199</v>
+      </c>
+      <c r="C43" s="28" t="s">
         <v>214</v>
       </c>
-      <c r="D42" s="47" t="s">
+      <c r="D43" s="28" t="s">
         <v>215</v>
       </c>
-      <c r="E42" s="46" t="s">
-        <v>437</v>
-      </c>
-      <c r="F42" s="47"/>
-    </row>
-    <row r="43" spans="1:6" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A43" s="46">
-        <v>34</v>
-      </c>
-      <c r="B43" s="47" t="s">
-        <v>201</v>
-      </c>
-      <c r="C43" s="47" t="s">
+      <c r="E43" s="27" t="s">
+        <v>435</v>
+      </c>
+      <c r="F43" s="28"/>
+    </row>
+    <row r="44" spans="1:6" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A44" s="48" t="s">
         <v>216</v>
       </c>
-      <c r="D43" s="47" t="s">
+      <c r="B44" s="48"/>
+      <c r="C44" s="48"/>
+      <c r="D44" s="48"/>
+      <c r="E44" s="48"/>
+      <c r="F44" s="48"/>
+    </row>
+    <row r="45" spans="1:6" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A45" s="27">
+        <v>35</v>
+      </c>
+      <c r="B45" s="28" t="s">
         <v>217</v>
       </c>
-      <c r="E43" s="46" t="s">
-        <v>437</v>
-      </c>
-      <c r="F43" s="47"/>
-    </row>
-    <row r="44" spans="1:6" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A44" s="45" t="s">
+      <c r="C45" s="28" t="s">
         <v>218</v>
       </c>
-      <c r="B44" s="45"/>
-      <c r="C44" s="45"/>
-      <c r="D44" s="45"/>
-      <c r="E44" s="45"/>
-      <c r="F44" s="45"/>
-    </row>
-    <row r="45" spans="1:6" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A45" s="46">
-        <v>35</v>
-      </c>
-      <c r="B45" s="47" t="s">
+      <c r="D45" s="28" t="s">
         <v>219</v>
       </c>
-      <c r="C45" s="47" t="s">
+      <c r="E45" s="27" t="s">
+        <v>435</v>
+      </c>
+      <c r="F45" s="28"/>
+    </row>
+    <row r="46" spans="1:6" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A46" s="27">
+        <v>36</v>
+      </c>
+      <c r="B46" s="28" t="s">
+        <v>217</v>
+      </c>
+      <c r="C46" s="28" t="s">
         <v>220</v>
       </c>
-      <c r="D45" s="47" t="s">
+      <c r="D46" s="28" t="s">
         <v>221</v>
       </c>
-      <c r="E45" s="46" t="s">
-        <v>437</v>
-      </c>
-      <c r="F45" s="47"/>
-    </row>
-    <row r="46" spans="1:6" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A46" s="46">
-        <v>36</v>
-      </c>
-      <c r="B46" s="47" t="s">
-        <v>219</v>
-      </c>
-      <c r="C46" s="47" t="s">
+      <c r="E46" s="27" t="s">
+        <v>435</v>
+      </c>
+      <c r="F46" s="28"/>
+    </row>
+    <row r="47" spans="1:6" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A47" s="27">
+        <v>37</v>
+      </c>
+      <c r="B47" s="28" t="s">
+        <v>217</v>
+      </c>
+      <c r="C47" s="28" t="s">
         <v>222</v>
       </c>
-      <c r="D46" s="47" t="s">
+      <c r="D47" s="28" t="s">
         <v>223</v>
       </c>
-      <c r="E46" s="46" t="s">
-        <v>437</v>
-      </c>
-      <c r="F46" s="47"/>
-    </row>
-    <row r="47" spans="1:6" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A47" s="46">
-        <v>37</v>
-      </c>
-      <c r="B47" s="47" t="s">
-        <v>219</v>
-      </c>
-      <c r="C47" s="47" t="s">
+      <c r="E47" s="27" t="s">
+        <v>435</v>
+      </c>
+      <c r="F47" s="28"/>
+    </row>
+    <row r="48" spans="1:6" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A48" s="27">
+        <v>38</v>
+      </c>
+      <c r="B48" s="28" t="s">
+        <v>217</v>
+      </c>
+      <c r="C48" s="28" t="s">
         <v>224</v>
       </c>
-      <c r="D47" s="47" t="s">
+      <c r="D48" s="28" t="s">
+        <v>111</v>
+      </c>
+      <c r="E48" s="27" t="s">
+        <v>435</v>
+      </c>
+      <c r="F48" s="28"/>
+    </row>
+    <row r="49" spans="1:6" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A49" s="48" t="s">
         <v>225</v>
       </c>
-      <c r="E47" s="46" t="s">
-        <v>437</v>
-      </c>
-      <c r="F47" s="47"/>
-    </row>
-    <row r="48" spans="1:6" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A48" s="46">
-        <v>38</v>
-      </c>
-      <c r="B48" s="47" t="s">
-        <v>219</v>
-      </c>
-      <c r="C48" s="47" t="s">
+      <c r="B49" s="48"/>
+      <c r="C49" s="48"/>
+      <c r="D49" s="48"/>
+      <c r="E49" s="48"/>
+      <c r="F49" s="48"/>
+    </row>
+    <row r="50" spans="1:6" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A50" s="27">
+        <v>39</v>
+      </c>
+      <c r="B50" s="28" t="s">
         <v>226</v>
       </c>
-      <c r="D48" s="47" t="s">
-        <v>113</v>
-      </c>
-      <c r="E48" s="46" t="s">
-        <v>437</v>
-      </c>
-      <c r="F48" s="47"/>
-    </row>
-    <row r="49" spans="1:6" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A49" s="45" t="s">
+      <c r="C50" s="28" t="s">
         <v>227</v>
       </c>
-      <c r="B49" s="45"/>
-      <c r="C49" s="45"/>
-      <c r="D49" s="45"/>
-      <c r="E49" s="45"/>
-      <c r="F49" s="45"/>
-    </row>
-    <row r="50" spans="1:6" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A50" s="46">
-        <v>39</v>
-      </c>
-      <c r="B50" s="47" t="s">
+      <c r="D50" s="28" t="s">
         <v>228</v>
       </c>
-      <c r="C50" s="47" t="s">
+      <c r="E50" s="27" t="s">
+        <v>435</v>
+      </c>
+      <c r="F50" s="28"/>
+    </row>
+    <row r="51" spans="1:6" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A51" s="27">
+        <v>40</v>
+      </c>
+      <c r="B51" s="28" t="s">
+        <v>226</v>
+      </c>
+      <c r="C51" s="28" t="s">
         <v>229</v>
       </c>
-      <c r="D50" s="47" t="s">
+      <c r="D51" s="28" t="s">
         <v>230</v>
       </c>
-      <c r="E50" s="46" t="s">
-        <v>437</v>
-      </c>
-      <c r="F50" s="47"/>
-    </row>
-    <row r="51" spans="1:6" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A51" s="46">
-        <v>40</v>
-      </c>
-      <c r="B51" s="47" t="s">
-        <v>228</v>
-      </c>
-      <c r="C51" s="47" t="s">
+      <c r="E51" s="27" t="s">
+        <v>435</v>
+      </c>
+      <c r="F51" s="28"/>
+    </row>
+    <row r="52" spans="1:6" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A52" s="48" t="s">
         <v>231</v>
       </c>
-      <c r="D51" s="47" t="s">
+      <c r="B52" s="48"/>
+      <c r="C52" s="48"/>
+      <c r="D52" s="48"/>
+      <c r="E52" s="48"/>
+      <c r="F52" s="48"/>
+    </row>
+    <row r="53" spans="1:6" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A53" s="27">
+        <v>41</v>
+      </c>
+      <c r="B53" s="28" t="s">
         <v>232</v>
       </c>
-      <c r="E51" s="46" t="s">
-        <v>437</v>
-      </c>
-      <c r="F51" s="47"/>
-    </row>
-    <row r="52" spans="1:6" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A52" s="45" t="s">
+      <c r="C53" s="28" t="s">
         <v>233</v>
       </c>
-      <c r="B52" s="45"/>
-      <c r="C52" s="45"/>
-      <c r="D52" s="45"/>
-      <c r="E52" s="45"/>
-      <c r="F52" s="45"/>
-    </row>
-    <row r="53" spans="1:6" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A53" s="46">
-        <v>41</v>
-      </c>
-      <c r="B53" s="47" t="s">
+      <c r="D53" s="28" t="s">
         <v>234</v>
       </c>
-      <c r="C53" s="47" t="s">
+      <c r="E53" s="27" t="s">
+        <v>435</v>
+      </c>
+      <c r="F53" s="28"/>
+    </row>
+    <row r="54" spans="1:6" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A54" s="27">
+        <v>42</v>
+      </c>
+      <c r="B54" s="28" t="s">
+        <v>232</v>
+      </c>
+      <c r="C54" s="28" t="s">
         <v>235</v>
       </c>
-      <c r="D53" s="47" t="s">
+      <c r="D54" s="28" t="s">
         <v>236</v>
       </c>
-      <c r="E53" s="46" t="s">
-        <v>437</v>
-      </c>
-      <c r="F53" s="47"/>
-    </row>
-    <row r="54" spans="1:6" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A54" s="46">
-        <v>42</v>
-      </c>
-      <c r="B54" s="47" t="s">
-        <v>234</v>
-      </c>
-      <c r="C54" s="47" t="s">
-        <v>237</v>
-      </c>
-      <c r="D54" s="47" t="s">
-        <v>238</v>
-      </c>
-      <c r="E54" s="46" t="s">
-        <v>437</v>
-      </c>
-      <c r="F54" s="47"/>
+      <c r="E54" s="27" t="s">
+        <v>435</v>
+      </c>
+      <c r="F54" s="28"/>
     </row>
     <row r="56" spans="1:6" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A56" s="40" t="s">
-        <v>131</v>
-      </c>
-      <c r="B56" s="40"/>
-      <c r="C56" s="40"/>
-      <c r="D56" s="40"/>
-      <c r="E56" s="40"/>
-      <c r="F56" s="40"/>
+      <c r="A56" s="49" t="s">
+        <v>129</v>
+      </c>
+      <c r="B56" s="49"/>
+      <c r="C56" s="49"/>
+      <c r="D56" s="49"/>
+      <c r="E56" s="49"/>
+      <c r="F56" s="49"/>
     </row>
     <row r="57" spans="1:6" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A57" s="37" t="s">
-        <v>132</v>
-      </c>
-      <c r="B57" s="37"/>
-      <c r="C57" s="37"/>
-      <c r="D57" s="38">
+      <c r="A57" s="45" t="s">
+        <v>130</v>
+      </c>
+      <c r="B57" s="45"/>
+      <c r="C57" s="45"/>
+      <c r="D57" s="46">
         <f>COUNTA(E4:E54)</f>
         <v>42</v>
       </c>
-      <c r="E57" s="38"/>
-      <c r="F57" s="38"/>
+      <c r="E57" s="46"/>
+      <c r="F57" s="46"/>
     </row>
     <row r="58" spans="1:6" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A58" s="37" t="s">
-        <v>133</v>
-      </c>
-      <c r="B58" s="37"/>
-      <c r="C58" s="37"/>
-      <c r="D58" s="38">
+      <c r="A58" s="45" t="s">
+        <v>131</v>
+      </c>
+      <c r="B58" s="45"/>
+      <c r="C58" s="45"/>
+      <c r="D58" s="46">
         <f>COUNTIF(E4:E54,"PASS")</f>
         <v>0</v>
       </c>
-      <c r="E58" s="38"/>
-      <c r="F58" s="38"/>
+      <c r="E58" s="46"/>
+      <c r="F58" s="46"/>
     </row>
     <row r="59" spans="1:6" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A59" s="37" t="s">
-        <v>134</v>
-      </c>
-      <c r="B59" s="37"/>
-      <c r="C59" s="37"/>
-      <c r="D59" s="38">
+      <c r="A59" s="45" t="s">
+        <v>132</v>
+      </c>
+      <c r="B59" s="45"/>
+      <c r="C59" s="45"/>
+      <c r="D59" s="46">
         <f>COUNTIF(E4:E54,"FAIL")</f>
         <v>0</v>
       </c>
-      <c r="E59" s="38"/>
-      <c r="F59" s="38"/>
+      <c r="E59" s="46"/>
+      <c r="F59" s="46"/>
     </row>
     <row r="60" spans="1:6" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A60" s="37" t="s">
-        <v>135</v>
-      </c>
-      <c r="B60" s="37"/>
-      <c r="C60" s="37"/>
-      <c r="D60" s="38">
+      <c r="A60" s="45" t="s">
+        <v>133</v>
+      </c>
+      <c r="B60" s="45"/>
+      <c r="C60" s="45"/>
+      <c r="D60" s="46">
         <f>COUNTIF(E4:E54,"N/A")</f>
         <v>42</v>
       </c>
-      <c r="E60" s="38"/>
-      <c r="F60" s="38"/>
+      <c r="E60" s="46"/>
+      <c r="F60" s="46"/>
     </row>
     <row r="61" spans="1:6" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A61" s="37" t="s">
-        <v>136</v>
-      </c>
-      <c r="B61" s="37"/>
-      <c r="C61" s="37"/>
-      <c r="D61" s="39">
+      <c r="A61" s="45" t="s">
+        <v>134</v>
+      </c>
+      <c r="B61" s="45"/>
+      <c r="C61" s="45"/>
+      <c r="D61" s="47">
         <f>IFERROR(COUNTIF(E4:E54,"PASS")/(COUNTA(E4:E54)-COUNTIF(E4:E54,"N/A")),0)</f>
         <v>0</v>
       </c>
-      <c r="E61" s="39"/>
-      <c r="F61" s="39"/>
+      <c r="E61" s="47"/>
+      <c r="F61" s="47"/>
     </row>
     <row r="62" spans="1:6" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A62" s="37" t="s">
-        <v>137</v>
-      </c>
-      <c r="B62" s="37"/>
-      <c r="C62" s="37"/>
-      <c r="D62" s="38" t="str">
+      <c r="A62" s="45" t="s">
+        <v>135</v>
+      </c>
+      <c r="B62" s="45"/>
+      <c r="C62" s="45"/>
+      <c r="D62" s="46" t="str">
         <f>IF(IFERROR(COUNTIF(E4:E54,"PASS")/(COUNTA(E4:E54)-COUNTIF(E4:E54,"N/A")),0)=1,"ĐẠT YÊU CẦU","CHƯA ĐẠT - CẦN XỬ LÝ")</f>
         <v>CHƯA ĐẠT - CẦN XỬ LÝ</v>
       </c>
-      <c r="E62" s="38"/>
-      <c r="F62" s="38"/>
+      <c r="E62" s="46"/>
+      <c r="F62" s="46"/>
     </row>
     <row r="64" spans="1:6" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A64" s="37" t="s">
-        <v>138</v>
-      </c>
-      <c r="B64" s="37"/>
-      <c r="C64" s="37"/>
-      <c r="D64" s="37" t="s">
-        <v>139</v>
-      </c>
-      <c r="E64" s="37"/>
-      <c r="F64" s="37"/>
+      <c r="A64" s="45" t="s">
+        <v>136</v>
+      </c>
+      <c r="B64" s="45"/>
+      <c r="C64" s="45"/>
+      <c r="D64" s="45" t="s">
+        <v>137</v>
+      </c>
+      <c r="E64" s="45"/>
+      <c r="F64" s="45"/>
     </row>
   </sheetData>
   <mergeCells count="26">
@@ -4931,762 +4932,762 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:6" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A1" s="41" t="s">
+      <c r="A1" s="50" t="s">
+        <v>237</v>
+      </c>
+      <c r="B1" s="50"/>
+      <c r="C1" s="50"/>
+      <c r="D1" s="50"/>
+      <c r="E1" s="50"/>
+      <c r="F1" s="50"/>
+    </row>
+    <row r="2" spans="1:6" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A2" s="51" t="s">
+        <v>15</v>
+      </c>
+      <c r="B2" s="51"/>
+      <c r="C2" s="51"/>
+      <c r="D2" s="25" t="s">
+        <v>16</v>
+      </c>
+      <c r="E2" s="25" t="s">
+        <v>17</v>
+      </c>
+      <c r="F2" s="25" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="3" spans="1:6" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A3" s="26" t="s">
+        <v>19</v>
+      </c>
+      <c r="B3" s="26" t="s">
+        <v>20</v>
+      </c>
+      <c r="C3" s="26" t="s">
+        <v>21</v>
+      </c>
+      <c r="D3" s="26" t="s">
+        <v>22</v>
+      </c>
+      <c r="E3" s="26" t="s">
+        <v>23</v>
+      </c>
+      <c r="F3" s="26" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="4" spans="1:6" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A4" s="48" t="s">
+        <v>139</v>
+      </c>
+      <c r="B4" s="48"/>
+      <c r="C4" s="48"/>
+      <c r="D4" s="48"/>
+      <c r="E4" s="48"/>
+      <c r="F4" s="48"/>
+    </row>
+    <row r="5" spans="1:6" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A5" s="29">
+        <v>1</v>
+      </c>
+      <c r="B5" s="30" t="s">
+        <v>25</v>
+      </c>
+      <c r="C5" s="30" t="s">
+        <v>140</v>
+      </c>
+      <c r="D5" s="30" t="s">
+        <v>238</v>
+      </c>
+      <c r="E5" s="29" t="s">
+        <v>435</v>
+      </c>
+      <c r="F5" s="30"/>
+    </row>
+    <row r="6" spans="1:6" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A6" s="31">
+        <v>2</v>
+      </c>
+      <c r="B6" s="32" t="s">
+        <v>25</v>
+      </c>
+      <c r="C6" s="32" t="s">
         <v>239</v>
       </c>
-      <c r="B1" s="41"/>
-      <c r="C1" s="41"/>
-      <c r="D1" s="41"/>
-      <c r="E1" s="41"/>
-      <c r="F1" s="41"/>
-    </row>
-    <row r="2" spans="1:6" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A2" s="42" t="s">
+      <c r="D6" s="32" t="s">
+        <v>240</v>
+      </c>
+      <c r="E6" s="29" t="s">
+        <v>435</v>
+      </c>
+      <c r="F6" s="32"/>
+    </row>
+    <row r="7" spans="1:6" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A7" s="29">
+        <v>3</v>
+      </c>
+      <c r="B7" s="30" t="s">
+        <v>25</v>
+      </c>
+      <c r="C7" s="30" t="s">
+        <v>241</v>
+      </c>
+      <c r="D7" s="30" t="s">
+        <v>242</v>
+      </c>
+      <c r="E7" s="29" t="s">
+        <v>435</v>
+      </c>
+      <c r="F7" s="30"/>
+    </row>
+    <row r="8" spans="1:6" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A8" s="31">
+        <v>4</v>
+      </c>
+      <c r="B8" s="32" t="s">
+        <v>25</v>
+      </c>
+      <c r="C8" s="32" t="s">
+        <v>243</v>
+      </c>
+      <c r="D8" s="32" t="s">
+        <v>244</v>
+      </c>
+      <c r="E8" s="29" t="s">
+        <v>435</v>
+      </c>
+      <c r="F8" s="32"/>
+    </row>
+    <row r="9" spans="1:6" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A9" s="48" t="s">
+        <v>245</v>
+      </c>
+      <c r="B9" s="48"/>
+      <c r="C9" s="48"/>
+      <c r="D9" s="48"/>
+      <c r="E9" s="48"/>
+      <c r="F9" s="48"/>
+    </row>
+    <row r="10" spans="1:6" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A10" s="29">
+        <v>5</v>
+      </c>
+      <c r="B10" s="30" t="s">
+        <v>246</v>
+      </c>
+      <c r="C10" s="30" t="s">
+        <v>247</v>
+      </c>
+      <c r="D10" s="30" t="s">
+        <v>248</v>
+      </c>
+      <c r="E10" s="29" t="s">
+        <v>435</v>
+      </c>
+      <c r="F10" s="30"/>
+    </row>
+    <row r="11" spans="1:6" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A11" s="31">
+        <v>6</v>
+      </c>
+      <c r="B11" s="32" t="s">
+        <v>246</v>
+      </c>
+      <c r="C11" s="32" t="s">
+        <v>249</v>
+      </c>
+      <c r="D11" s="32" t="s">
+        <v>250</v>
+      </c>
+      <c r="E11" s="29" t="s">
+        <v>435</v>
+      </c>
+      <c r="F11" s="32"/>
+    </row>
+    <row r="12" spans="1:6" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A12" s="29">
+        <v>7</v>
+      </c>
+      <c r="B12" s="30" t="s">
+        <v>246</v>
+      </c>
+      <c r="C12" s="30" t="s">
+        <v>251</v>
+      </c>
+      <c r="D12" s="30" t="s">
+        <v>252</v>
+      </c>
+      <c r="E12" s="29" t="s">
+        <v>435</v>
+      </c>
+      <c r="F12" s="30"/>
+    </row>
+    <row r="13" spans="1:6" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A13" s="31">
+        <v>8</v>
+      </c>
+      <c r="B13" s="32" t="s">
+        <v>246</v>
+      </c>
+      <c r="C13" s="32" t="s">
+        <v>253</v>
+      </c>
+      <c r="D13" s="32" t="s">
+        <v>254</v>
+      </c>
+      <c r="E13" s="29" t="s">
+        <v>435</v>
+      </c>
+      <c r="F13" s="32"/>
+    </row>
+    <row r="14" spans="1:6" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A14" s="29">
+        <v>9</v>
+      </c>
+      <c r="B14" s="30" t="s">
+        <v>246</v>
+      </c>
+      <c r="C14" s="30" t="s">
+        <v>255</v>
+      </c>
+      <c r="D14" s="30" t="s">
+        <v>256</v>
+      </c>
+      <c r="E14" s="29" t="s">
+        <v>435</v>
+      </c>
+      <c r="F14" s="30"/>
+    </row>
+    <row r="15" spans="1:6" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A15" s="48" t="s">
+        <v>257</v>
+      </c>
+      <c r="B15" s="48"/>
+      <c r="C15" s="48"/>
+      <c r="D15" s="48"/>
+      <c r="E15" s="48"/>
+      <c r="F15" s="48"/>
+    </row>
+    <row r="16" spans="1:6" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A16" s="31">
+        <v>10</v>
+      </c>
+      <c r="B16" s="32" t="s">
+        <v>258</v>
+      </c>
+      <c r="C16" s="32" t="s">
+        <v>154</v>
+      </c>
+      <c r="D16" s="32" t="s">
+        <v>259</v>
+      </c>
+      <c r="E16" s="29" t="s">
+        <v>435</v>
+      </c>
+      <c r="F16" s="32"/>
+    </row>
+    <row r="17" spans="1:6" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A17" s="29">
+        <v>11</v>
+      </c>
+      <c r="B17" s="30" t="s">
+        <v>258</v>
+      </c>
+      <c r="C17" s="30" t="s">
+        <v>260</v>
+      </c>
+      <c r="D17" s="30" t="s">
+        <v>261</v>
+      </c>
+      <c r="E17" s="29" t="s">
+        <v>435</v>
+      </c>
+      <c r="F17" s="30"/>
+    </row>
+    <row r="18" spans="1:6" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A18" s="48" t="s">
+        <v>262</v>
+      </c>
+      <c r="B18" s="48"/>
+      <c r="C18" s="48"/>
+      <c r="D18" s="48"/>
+      <c r="E18" s="48"/>
+      <c r="F18" s="48"/>
+    </row>
+    <row r="19" spans="1:6" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A19" s="31">
+        <v>12</v>
+      </c>
+      <c r="B19" s="32" t="s">
+        <v>263</v>
+      </c>
+      <c r="C19" s="32" t="s">
+        <v>264</v>
+      </c>
+      <c r="D19" s="32" t="s">
+        <v>265</v>
+      </c>
+      <c r="E19" s="29" t="s">
+        <v>435</v>
+      </c>
+      <c r="F19" s="32"/>
+    </row>
+    <row r="20" spans="1:6" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A20" s="29">
+        <v>13</v>
+      </c>
+      <c r="B20" s="30" t="s">
+        <v>263</v>
+      </c>
+      <c r="C20" s="30" t="s">
+        <v>266</v>
+      </c>
+      <c r="D20" s="30" t="s">
+        <v>267</v>
+      </c>
+      <c r="E20" s="29" t="s">
+        <v>435</v>
+      </c>
+      <c r="F20" s="30"/>
+    </row>
+    <row r="21" spans="1:6" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A21" s="31">
+        <v>14</v>
+      </c>
+      <c r="B21" s="32" t="s">
+        <v>263</v>
+      </c>
+      <c r="C21" s="32" t="s">
+        <v>268</v>
+      </c>
+      <c r="D21" s="32" t="s">
+        <v>269</v>
+      </c>
+      <c r="E21" s="29" t="s">
+        <v>435</v>
+      </c>
+      <c r="F21" s="32"/>
+    </row>
+    <row r="22" spans="1:6" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A22" s="29">
         <v>15</v>
       </c>
-      <c r="B2" s="42"/>
-      <c r="C2" s="42"/>
-      <c r="D2" s="43" t="s">
+      <c r="B22" s="30" t="s">
+        <v>263</v>
+      </c>
+      <c r="C22" s="30" t="s">
+        <v>270</v>
+      </c>
+      <c r="D22" s="30" t="s">
+        <v>271</v>
+      </c>
+      <c r="E22" s="29" t="s">
+        <v>435</v>
+      </c>
+      <c r="F22" s="30"/>
+    </row>
+    <row r="23" spans="1:6" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A23" s="31">
         <v>16</v>
       </c>
-      <c r="E2" s="43" t="s">
+      <c r="B23" s="32" t="s">
+        <v>263</v>
+      </c>
+      <c r="C23" s="32" t="s">
+        <v>272</v>
+      </c>
+      <c r="D23" s="32" t="s">
+        <v>273</v>
+      </c>
+      <c r="E23" s="29" t="s">
+        <v>435</v>
+      </c>
+      <c r="F23" s="32"/>
+    </row>
+    <row r="24" spans="1:6" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A24" s="48" t="s">
+        <v>274</v>
+      </c>
+      <c r="B24" s="48"/>
+      <c r="C24" s="48"/>
+      <c r="D24" s="48"/>
+      <c r="E24" s="48"/>
+      <c r="F24" s="48"/>
+    </row>
+    <row r="25" spans="1:6" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A25" s="29">
         <v>17</v>
       </c>
-      <c r="F2" s="43" t="s">
+      <c r="B25" s="30" t="s">
+        <v>275</v>
+      </c>
+      <c r="C25" s="30" t="s">
+        <v>276</v>
+      </c>
+      <c r="D25" s="30" t="s">
+        <v>277</v>
+      </c>
+      <c r="E25" s="29" t="s">
+        <v>435</v>
+      </c>
+      <c r="F25" s="30"/>
+    </row>
+    <row r="26" spans="1:6" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A26" s="31">
         <v>18</v>
       </c>
-    </row>
-    <row r="3" spans="1:6" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A3" s="44" t="s">
+      <c r="B26" s="32" t="s">
+        <v>275</v>
+      </c>
+      <c r="C26" s="32" t="s">
+        <v>278</v>
+      </c>
+      <c r="D26" s="32" t="s">
+        <v>279</v>
+      </c>
+      <c r="E26" s="29" t="s">
+        <v>435</v>
+      </c>
+      <c r="F26" s="32"/>
+    </row>
+    <row r="27" spans="1:6" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A27" s="48" t="s">
+        <v>280</v>
+      </c>
+      <c r="B27" s="48"/>
+      <c r="C27" s="48"/>
+      <c r="D27" s="48"/>
+      <c r="E27" s="48"/>
+      <c r="F27" s="48"/>
+    </row>
+    <row r="28" spans="1:6" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A28" s="29">
         <v>19</v>
       </c>
-      <c r="B3" s="44" t="s">
+      <c r="B28" s="30" t="s">
+        <v>281</v>
+      </c>
+      <c r="C28" s="30" t="s">
+        <v>282</v>
+      </c>
+      <c r="D28" s="30" t="s">
+        <v>283</v>
+      </c>
+      <c r="E28" s="29" t="s">
+        <v>435</v>
+      </c>
+      <c r="F28" s="30"/>
+    </row>
+    <row r="29" spans="1:6" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A29" s="31">
         <v>20</v>
       </c>
-      <c r="C3" s="44" t="s">
+      <c r="B29" s="32" t="s">
+        <v>281</v>
+      </c>
+      <c r="C29" s="32" t="s">
+        <v>284</v>
+      </c>
+      <c r="D29" s="32" t="s">
+        <v>285</v>
+      </c>
+      <c r="E29" s="29" t="s">
+        <v>435</v>
+      </c>
+      <c r="F29" s="32"/>
+    </row>
+    <row r="30" spans="1:6" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A30" s="29">
         <v>21</v>
       </c>
-      <c r="D3" s="44" t="s">
+      <c r="B30" s="30" t="s">
+        <v>281</v>
+      </c>
+      <c r="C30" s="30" t="s">
+        <v>98</v>
+      </c>
+      <c r="D30" s="30" t="s">
+        <v>286</v>
+      </c>
+      <c r="E30" s="29" t="s">
+        <v>435</v>
+      </c>
+      <c r="F30" s="30"/>
+    </row>
+    <row r="31" spans="1:6" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A31" s="48" t="s">
+        <v>287</v>
+      </c>
+      <c r="B31" s="48"/>
+      <c r="C31" s="48"/>
+      <c r="D31" s="48"/>
+      <c r="E31" s="48"/>
+      <c r="F31" s="48"/>
+    </row>
+    <row r="32" spans="1:6" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A32" s="31">
         <v>22</v>
       </c>
-      <c r="E3" s="44" t="s">
+      <c r="B32" s="32" t="s">
+        <v>288</v>
+      </c>
+      <c r="C32" s="32" t="s">
+        <v>289</v>
+      </c>
+      <c r="D32" s="32" t="s">
+        <v>290</v>
+      </c>
+      <c r="E32" s="29" t="s">
+        <v>435</v>
+      </c>
+      <c r="F32" s="32"/>
+    </row>
+    <row r="33" spans="1:6" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A33" s="29">
         <v>23</v>
       </c>
-      <c r="F3" s="44" t="s">
+      <c r="B33" s="30" t="s">
+        <v>288</v>
+      </c>
+      <c r="C33" s="30" t="s">
+        <v>291</v>
+      </c>
+      <c r="D33" s="30" t="s">
+        <v>292</v>
+      </c>
+      <c r="E33" s="29" t="s">
+        <v>435</v>
+      </c>
+      <c r="F33" s="30"/>
+    </row>
+    <row r="34" spans="1:6" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A34" s="48" t="s">
+        <v>293</v>
+      </c>
+      <c r="B34" s="48"/>
+      <c r="C34" s="48"/>
+      <c r="D34" s="48"/>
+      <c r="E34" s="48"/>
+      <c r="F34" s="48"/>
+    </row>
+    <row r="35" spans="1:6" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A35" s="31">
         <v>24</v>
       </c>
-    </row>
-    <row r="4" spans="1:6" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A4" s="45" t="s">
-        <v>141</v>
-      </c>
-      <c r="B4" s="45"/>
-      <c r="C4" s="45"/>
-      <c r="D4" s="45"/>
-      <c r="E4" s="45"/>
-      <c r="F4" s="45"/>
-    </row>
-    <row r="5" spans="1:6" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A5" s="48">
-        <v>1</v>
-      </c>
-      <c r="B5" s="49" t="s">
+      <c r="B35" s="32" t="s">
+        <v>294</v>
+      </c>
+      <c r="C35" s="32" t="s">
+        <v>295</v>
+      </c>
+      <c r="D35" s="32" t="s">
+        <v>296</v>
+      </c>
+      <c r="E35" s="29" t="s">
+        <v>435</v>
+      </c>
+      <c r="F35" s="32"/>
+    </row>
+    <row r="36" spans="1:6" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A36" s="29">
         <v>25</v>
       </c>
-      <c r="C5" s="49" t="s">
-        <v>142</v>
-      </c>
-      <c r="D5" s="49" t="s">
-        <v>240</v>
-      </c>
-      <c r="E5" s="48" t="s">
-        <v>437</v>
-      </c>
-      <c r="F5" s="49"/>
-    </row>
-    <row r="6" spans="1:6" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A6" s="50">
-        <v>2</v>
-      </c>
-      <c r="B6" s="51" t="s">
-        <v>25</v>
-      </c>
-      <c r="C6" s="51" t="s">
-        <v>241</v>
-      </c>
-      <c r="D6" s="51" t="s">
-        <v>242</v>
-      </c>
-      <c r="E6" s="48" t="s">
-        <v>437</v>
-      </c>
-      <c r="F6" s="51"/>
-    </row>
-    <row r="7" spans="1:6" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A7" s="48">
-        <v>3</v>
-      </c>
-      <c r="B7" s="49" t="s">
-        <v>25</v>
-      </c>
-      <c r="C7" s="49" t="s">
-        <v>243</v>
-      </c>
-      <c r="D7" s="49" t="s">
-        <v>244</v>
-      </c>
-      <c r="E7" s="48" t="s">
-        <v>437</v>
-      </c>
-      <c r="F7" s="49"/>
-    </row>
-    <row r="8" spans="1:6" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A8" s="50">
-        <v>4</v>
-      </c>
-      <c r="B8" s="51" t="s">
-        <v>25</v>
-      </c>
-      <c r="C8" s="51" t="s">
-        <v>245</v>
-      </c>
-      <c r="D8" s="51" t="s">
-        <v>246</v>
-      </c>
-      <c r="E8" s="48" t="s">
-        <v>437</v>
-      </c>
-      <c r="F8" s="51"/>
-    </row>
-    <row r="9" spans="1:6" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A9" s="45" t="s">
-        <v>247</v>
-      </c>
-      <c r="B9" s="45"/>
-      <c r="C9" s="45"/>
-      <c r="D9" s="45"/>
-      <c r="E9" s="45"/>
-      <c r="F9" s="45"/>
-    </row>
-    <row r="10" spans="1:6" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A10" s="48">
-        <v>5</v>
-      </c>
-      <c r="B10" s="49" t="s">
-        <v>248</v>
-      </c>
-      <c r="C10" s="49" t="s">
-        <v>249</v>
-      </c>
-      <c r="D10" s="49" t="s">
-        <v>250</v>
-      </c>
-      <c r="E10" s="48" t="s">
-        <v>437</v>
-      </c>
-      <c r="F10" s="49"/>
-    </row>
-    <row r="11" spans="1:6" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A11" s="50">
-        <v>6</v>
-      </c>
-      <c r="B11" s="51" t="s">
-        <v>248</v>
-      </c>
-      <c r="C11" s="51" t="s">
-        <v>251</v>
-      </c>
-      <c r="D11" s="51" t="s">
-        <v>252</v>
-      </c>
-      <c r="E11" s="48" t="s">
-        <v>437</v>
-      </c>
-      <c r="F11" s="51"/>
-    </row>
-    <row r="12" spans="1:6" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A12" s="48">
-        <v>7</v>
-      </c>
-      <c r="B12" s="49" t="s">
-        <v>248</v>
-      </c>
-      <c r="C12" s="49" t="s">
-        <v>253</v>
-      </c>
-      <c r="D12" s="49" t="s">
-        <v>254</v>
-      </c>
-      <c r="E12" s="48" t="s">
-        <v>437</v>
-      </c>
-      <c r="F12" s="49"/>
-    </row>
-    <row r="13" spans="1:6" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A13" s="50">
-        <v>8</v>
-      </c>
-      <c r="B13" s="51" t="s">
-        <v>248</v>
-      </c>
-      <c r="C13" s="51" t="s">
-        <v>255</v>
-      </c>
-      <c r="D13" s="51" t="s">
-        <v>256</v>
-      </c>
-      <c r="E13" s="48" t="s">
-        <v>437</v>
-      </c>
-      <c r="F13" s="51"/>
-    </row>
-    <row r="14" spans="1:6" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A14" s="48">
-        <v>9</v>
-      </c>
-      <c r="B14" s="49" t="s">
-        <v>248</v>
-      </c>
-      <c r="C14" s="49" t="s">
-        <v>257</v>
-      </c>
-      <c r="D14" s="49" t="s">
-        <v>258</v>
-      </c>
-      <c r="E14" s="48" t="s">
-        <v>437</v>
-      </c>
-      <c r="F14" s="49"/>
-    </row>
-    <row r="15" spans="1:6" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A15" s="45" t="s">
-        <v>259</v>
-      </c>
-      <c r="B15" s="45"/>
-      <c r="C15" s="45"/>
-      <c r="D15" s="45"/>
-      <c r="E15" s="45"/>
-      <c r="F15" s="45"/>
-    </row>
-    <row r="16" spans="1:6" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A16" s="50">
-        <v>10</v>
-      </c>
-      <c r="B16" s="51" t="s">
-        <v>260</v>
-      </c>
-      <c r="C16" s="51" t="s">
-        <v>156</v>
-      </c>
-      <c r="D16" s="51" t="s">
-        <v>261</v>
-      </c>
-      <c r="E16" s="48" t="s">
-        <v>437</v>
-      </c>
-      <c r="F16" s="51"/>
-    </row>
-    <row r="17" spans="1:6" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A17" s="48">
-        <v>11</v>
-      </c>
-      <c r="B17" s="49" t="s">
-        <v>260</v>
-      </c>
-      <c r="C17" s="49" t="s">
-        <v>262</v>
-      </c>
-      <c r="D17" s="49" t="s">
-        <v>263</v>
-      </c>
-      <c r="E17" s="48" t="s">
-        <v>437</v>
-      </c>
-      <c r="F17" s="49"/>
-    </row>
-    <row r="18" spans="1:6" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A18" s="45" t="s">
-        <v>264</v>
-      </c>
-      <c r="B18" s="45"/>
-      <c r="C18" s="45"/>
-      <c r="D18" s="45"/>
-      <c r="E18" s="45"/>
-      <c r="F18" s="45"/>
-    </row>
-    <row r="19" spans="1:6" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A19" s="50">
-        <v>12</v>
-      </c>
-      <c r="B19" s="51" t="s">
-        <v>265</v>
-      </c>
-      <c r="C19" s="51" t="s">
-        <v>266</v>
-      </c>
-      <c r="D19" s="51" t="s">
-        <v>267</v>
-      </c>
-      <c r="E19" s="48" t="s">
-        <v>437</v>
-      </c>
-      <c r="F19" s="51"/>
-    </row>
-    <row r="20" spans="1:6" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A20" s="48">
-        <v>13</v>
-      </c>
-      <c r="B20" s="49" t="s">
-        <v>265</v>
-      </c>
-      <c r="C20" s="49" t="s">
-        <v>268</v>
-      </c>
-      <c r="D20" s="49" t="s">
-        <v>269</v>
-      </c>
-      <c r="E20" s="48" t="s">
-        <v>437</v>
-      </c>
-      <c r="F20" s="49"/>
-    </row>
-    <row r="21" spans="1:6" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A21" s="50">
-        <v>14</v>
-      </c>
-      <c r="B21" s="51" t="s">
-        <v>265</v>
-      </c>
-      <c r="C21" s="51" t="s">
-        <v>270</v>
-      </c>
-      <c r="D21" s="51" t="s">
-        <v>271</v>
-      </c>
-      <c r="E21" s="48" t="s">
-        <v>437</v>
-      </c>
-      <c r="F21" s="51"/>
-    </row>
-    <row r="22" spans="1:6" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A22" s="48">
-        <v>15</v>
-      </c>
-      <c r="B22" s="49" t="s">
-        <v>265</v>
-      </c>
-      <c r="C22" s="49" t="s">
-        <v>272</v>
-      </c>
-      <c r="D22" s="49" t="s">
-        <v>273</v>
-      </c>
-      <c r="E22" s="48" t="s">
-        <v>437</v>
-      </c>
-      <c r="F22" s="49"/>
-    </row>
-    <row r="23" spans="1:6" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A23" s="50">
-        <v>16</v>
-      </c>
-      <c r="B23" s="51" t="s">
-        <v>265</v>
-      </c>
-      <c r="C23" s="51" t="s">
-        <v>274</v>
-      </c>
-      <c r="D23" s="51" t="s">
-        <v>275</v>
-      </c>
-      <c r="E23" s="48" t="s">
-        <v>437</v>
-      </c>
-      <c r="F23" s="51"/>
-    </row>
-    <row r="24" spans="1:6" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A24" s="45" t="s">
-        <v>276</v>
-      </c>
-      <c r="B24" s="45"/>
-      <c r="C24" s="45"/>
-      <c r="D24" s="45"/>
-      <c r="E24" s="45"/>
-      <c r="F24" s="45"/>
-    </row>
-    <row r="25" spans="1:6" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A25" s="48">
-        <v>17</v>
-      </c>
-      <c r="B25" s="49" t="s">
-        <v>277</v>
-      </c>
-      <c r="C25" s="49" t="s">
-        <v>278</v>
-      </c>
-      <c r="D25" s="49" t="s">
-        <v>279</v>
-      </c>
-      <c r="E25" s="48" t="s">
-        <v>437</v>
-      </c>
-      <c r="F25" s="49"/>
-    </row>
-    <row r="26" spans="1:6" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A26" s="50">
-        <v>18</v>
-      </c>
-      <c r="B26" s="51" t="s">
-        <v>277</v>
-      </c>
-      <c r="C26" s="51" t="s">
-        <v>280</v>
-      </c>
-      <c r="D26" s="51" t="s">
-        <v>281</v>
-      </c>
-      <c r="E26" s="48" t="s">
-        <v>437</v>
-      </c>
-      <c r="F26" s="51"/>
-    </row>
-    <row r="27" spans="1:6" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A27" s="45" t="s">
-        <v>282</v>
-      </c>
-      <c r="B27" s="45"/>
-      <c r="C27" s="45"/>
-      <c r="D27" s="45"/>
-      <c r="E27" s="45"/>
-      <c r="F27" s="45"/>
-    </row>
-    <row r="28" spans="1:6" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A28" s="48">
-        <v>19</v>
-      </c>
-      <c r="B28" s="49" t="s">
-        <v>283</v>
-      </c>
-      <c r="C28" s="49" t="s">
-        <v>284</v>
-      </c>
-      <c r="D28" s="49" t="s">
-        <v>285</v>
-      </c>
-      <c r="E28" s="48" t="s">
-        <v>437</v>
-      </c>
-      <c r="F28" s="49"/>
-    </row>
-    <row r="29" spans="1:6" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A29" s="50">
-        <v>20</v>
-      </c>
-      <c r="B29" s="51" t="s">
-        <v>283</v>
-      </c>
-      <c r="C29" s="51" t="s">
-        <v>286</v>
-      </c>
-      <c r="D29" s="51" t="s">
-        <v>287</v>
-      </c>
-      <c r="E29" s="48" t="s">
-        <v>437</v>
-      </c>
-      <c r="F29" s="51"/>
-    </row>
-    <row r="30" spans="1:6" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A30" s="48">
-        <v>21</v>
-      </c>
-      <c r="B30" s="49" t="s">
-        <v>283</v>
-      </c>
-      <c r="C30" s="49" t="s">
-        <v>100</v>
-      </c>
-      <c r="D30" s="49" t="s">
-        <v>288</v>
-      </c>
-      <c r="E30" s="48" t="s">
-        <v>437</v>
-      </c>
-      <c r="F30" s="49"/>
-    </row>
-    <row r="31" spans="1:6" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A31" s="45" t="s">
-        <v>289</v>
-      </c>
-      <c r="B31" s="45"/>
-      <c r="C31" s="45"/>
-      <c r="D31" s="45"/>
-      <c r="E31" s="45"/>
-      <c r="F31" s="45"/>
-    </row>
-    <row r="32" spans="1:6" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A32" s="50">
-        <v>22</v>
-      </c>
-      <c r="B32" s="51" t="s">
-        <v>290</v>
-      </c>
-      <c r="C32" s="51" t="s">
-        <v>291</v>
-      </c>
-      <c r="D32" s="51" t="s">
-        <v>292</v>
-      </c>
-      <c r="E32" s="48" t="s">
-        <v>437</v>
-      </c>
-      <c r="F32" s="51"/>
-    </row>
-    <row r="33" spans="1:6" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A33" s="48">
-        <v>23</v>
-      </c>
-      <c r="B33" s="49" t="s">
-        <v>290</v>
-      </c>
-      <c r="C33" s="49" t="s">
-        <v>293</v>
-      </c>
-      <c r="D33" s="49" t="s">
+      <c r="B36" s="30" t="s">
         <v>294</v>
       </c>
-      <c r="E33" s="48" t="s">
-        <v>437</v>
-      </c>
-      <c r="F33" s="49"/>
-    </row>
-    <row r="34" spans="1:6" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A34" s="45" t="s">
-        <v>295</v>
-      </c>
-      <c r="B34" s="45"/>
-      <c r="C34" s="45"/>
-      <c r="D34" s="45"/>
-      <c r="E34" s="45"/>
-      <c r="F34" s="45"/>
-    </row>
-    <row r="35" spans="1:6" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A35" s="50">
-        <v>24</v>
-      </c>
-      <c r="B35" s="51" t="s">
-        <v>296</v>
-      </c>
-      <c r="C35" s="51" t="s">
+      <c r="C36" s="30" t="s">
         <v>297</v>
       </c>
-      <c r="D35" s="51" t="s">
+      <c r="D36" s="30" t="s">
         <v>298</v>
       </c>
-      <c r="E35" s="48" t="s">
-        <v>437</v>
-      </c>
-      <c r="F35" s="51"/>
-    </row>
-    <row r="36" spans="1:6" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A36" s="48">
-        <v>25</v>
-      </c>
-      <c r="B36" s="49" t="s">
-        <v>296</v>
-      </c>
-      <c r="C36" s="49" t="s">
+      <c r="E36" s="29" t="s">
+        <v>435</v>
+      </c>
+      <c r="F36" s="30"/>
+    </row>
+    <row r="37" spans="1:6" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A37" s="48" t="s">
         <v>299</v>
       </c>
-      <c r="D36" s="49" t="s">
+      <c r="B37" s="48"/>
+      <c r="C37" s="48"/>
+      <c r="D37" s="48"/>
+      <c r="E37" s="48"/>
+      <c r="F37" s="48"/>
+    </row>
+    <row r="38" spans="1:6" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A38" s="31">
+        <v>26</v>
+      </c>
+      <c r="B38" s="32" t="s">
         <v>300</v>
       </c>
-      <c r="E36" s="48" t="s">
-        <v>437</v>
-      </c>
-      <c r="F36" s="49"/>
-    </row>
-    <row r="37" spans="1:6" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A37" s="45" t="s">
+      <c r="C38" s="32" t="s">
         <v>301</v>
       </c>
-      <c r="B37" s="45"/>
-      <c r="C37" s="45"/>
-      <c r="D37" s="45"/>
-      <c r="E37" s="45"/>
-      <c r="F37" s="45"/>
-    </row>
-    <row r="38" spans="1:6" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A38" s="50">
-        <v>26</v>
-      </c>
-      <c r="B38" s="51" t="s">
+      <c r="D38" s="32" t="s">
         <v>302</v>
       </c>
-      <c r="C38" s="51" t="s">
+      <c r="E38" s="29" t="s">
+        <v>435</v>
+      </c>
+      <c r="F38" s="32"/>
+    </row>
+    <row r="39" spans="1:6" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A39" s="29">
+        <v>27</v>
+      </c>
+      <c r="B39" s="30" t="s">
+        <v>300</v>
+      </c>
+      <c r="C39" s="30" t="s">
         <v>303</v>
       </c>
-      <c r="D38" s="51" t="s">
+      <c r="D39" s="30" t="s">
         <v>304</v>
       </c>
-      <c r="E38" s="48" t="s">
-        <v>437</v>
-      </c>
-      <c r="F38" s="51"/>
-    </row>
-    <row r="39" spans="1:6" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A39" s="48">
-        <v>27</v>
-      </c>
-      <c r="B39" s="49" t="s">
-        <v>302</v>
-      </c>
-      <c r="C39" s="49" t="s">
+      <c r="E39" s="29" t="s">
+        <v>435</v>
+      </c>
+      <c r="F39" s="30"/>
+    </row>
+    <row r="40" spans="1:6" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A40" s="31">
+        <v>28</v>
+      </c>
+      <c r="B40" s="32" t="s">
+        <v>300</v>
+      </c>
+      <c r="C40" s="32" t="s">
         <v>305</v>
       </c>
-      <c r="D39" s="49" t="s">
+      <c r="D40" s="32" t="s">
         <v>306</v>
       </c>
-      <c r="E39" s="48" t="s">
-        <v>437</v>
-      </c>
-      <c r="F39" s="49"/>
-    </row>
-    <row r="40" spans="1:6" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A40" s="50">
-        <v>28</v>
-      </c>
-      <c r="B40" s="51" t="s">
-        <v>302</v>
-      </c>
-      <c r="C40" s="51" t="s">
+      <c r="E40" s="29" t="s">
+        <v>435</v>
+      </c>
+      <c r="F40" s="32"/>
+    </row>
+    <row r="41" spans="1:6" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A41" s="29">
+        <v>29</v>
+      </c>
+      <c r="B41" s="30" t="s">
+        <v>300</v>
+      </c>
+      <c r="C41" s="30" t="s">
         <v>307</v>
       </c>
-      <c r="D40" s="51" t="s">
+      <c r="D41" s="30" t="s">
         <v>308</v>
       </c>
-      <c r="E40" s="48" t="s">
-        <v>437</v>
-      </c>
-      <c r="F40" s="51"/>
-    </row>
-    <row r="41" spans="1:6" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A41" s="48">
-        <v>29</v>
-      </c>
-      <c r="B41" s="49" t="s">
-        <v>302</v>
-      </c>
-      <c r="C41" s="49" t="s">
-        <v>309</v>
-      </c>
-      <c r="D41" s="49" t="s">
-        <v>310</v>
-      </c>
-      <c r="E41" s="48" t="s">
-        <v>437</v>
-      </c>
-      <c r="F41" s="49"/>
+      <c r="E41" s="29" t="s">
+        <v>435</v>
+      </c>
+      <c r="F41" s="30"/>
     </row>
     <row r="43" spans="1:6" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A43" s="40" t="s">
-        <v>131</v>
-      </c>
-      <c r="B43" s="40"/>
-      <c r="C43" s="40"/>
-      <c r="D43" s="40"/>
-      <c r="E43" s="40"/>
-      <c r="F43" s="40"/>
+      <c r="A43" s="49" t="s">
+        <v>129</v>
+      </c>
+      <c r="B43" s="49"/>
+      <c r="C43" s="49"/>
+      <c r="D43" s="49"/>
+      <c r="E43" s="49"/>
+      <c r="F43" s="49"/>
     </row>
     <row r="44" spans="1:6" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A44" s="37" t="s">
-        <v>132</v>
-      </c>
-      <c r="B44" s="37"/>
-      <c r="C44" s="37"/>
-      <c r="D44" s="38">
+      <c r="A44" s="45" t="s">
+        <v>130</v>
+      </c>
+      <c r="B44" s="45"/>
+      <c r="C44" s="45"/>
+      <c r="D44" s="46">
         <f>COUNTA(E4:E41)</f>
         <v>29</v>
       </c>
-      <c r="E44" s="38"/>
-      <c r="F44" s="38"/>
+      <c r="E44" s="46"/>
+      <c r="F44" s="46"/>
     </row>
     <row r="45" spans="1:6" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A45" s="37" t="s">
-        <v>133</v>
-      </c>
-      <c r="B45" s="37"/>
-      <c r="C45" s="37"/>
-      <c r="D45" s="38">
+      <c r="A45" s="45" t="s">
+        <v>131</v>
+      </c>
+      <c r="B45" s="45"/>
+      <c r="C45" s="45"/>
+      <c r="D45" s="46">
         <f>COUNTIF(E4:E41,"PASS")</f>
         <v>0</v>
       </c>
-      <c r="E45" s="38"/>
-      <c r="F45" s="38"/>
+      <c r="E45" s="46"/>
+      <c r="F45" s="46"/>
     </row>
     <row r="46" spans="1:6" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A46" s="37" t="s">
-        <v>134</v>
-      </c>
-      <c r="B46" s="37"/>
-      <c r="C46" s="37"/>
-      <c r="D46" s="38">
+      <c r="A46" s="45" t="s">
+        <v>132</v>
+      </c>
+      <c r="B46" s="45"/>
+      <c r="C46" s="45"/>
+      <c r="D46" s="46">
         <f>COUNTIF(E4:E41,"FAIL")</f>
         <v>0</v>
       </c>
-      <c r="E46" s="38"/>
-      <c r="F46" s="38"/>
+      <c r="E46" s="46"/>
+      <c r="F46" s="46"/>
     </row>
     <row r="47" spans="1:6" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A47" s="37" t="s">
-        <v>135</v>
-      </c>
-      <c r="B47" s="37"/>
-      <c r="C47" s="37"/>
-      <c r="D47" s="38">
+      <c r="A47" s="45" t="s">
+        <v>133</v>
+      </c>
+      <c r="B47" s="45"/>
+      <c r="C47" s="45"/>
+      <c r="D47" s="46">
         <f>COUNTIF(E4:E41,"N/A")</f>
         <v>29</v>
       </c>
-      <c r="E47" s="38"/>
-      <c r="F47" s="38"/>
+      <c r="E47" s="46"/>
+      <c r="F47" s="46"/>
     </row>
     <row r="48" spans="1:6" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A48" s="37" t="s">
-        <v>136</v>
-      </c>
-      <c r="B48" s="37"/>
-      <c r="C48" s="37"/>
-      <c r="D48" s="39">
+      <c r="A48" s="45" t="s">
+        <v>134</v>
+      </c>
+      <c r="B48" s="45"/>
+      <c r="C48" s="45"/>
+      <c r="D48" s="47">
         <f>IFERROR(COUNTIF(E4:E41,"PASS")/(COUNTA(E4:E41)-COUNTIF(E4:E41,"N/A")),0)</f>
         <v>0</v>
       </c>
-      <c r="E48" s="39"/>
-      <c r="F48" s="39"/>
+      <c r="E48" s="47"/>
+      <c r="F48" s="47"/>
     </row>
     <row r="49" spans="1:6" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A49" s="37" t="s">
-        <v>137</v>
-      </c>
-      <c r="B49" s="37"/>
-      <c r="C49" s="37"/>
-      <c r="D49" s="38" t="str">
+      <c r="A49" s="45" t="s">
+        <v>135</v>
+      </c>
+      <c r="B49" s="45"/>
+      <c r="C49" s="45"/>
+      <c r="D49" s="46" t="str">
         <f>IF(IFERROR(COUNTIF(E4:E41,"PASS")/(COUNTA(E4:E41)-COUNTIF(E4:E41,"N/A")),0)=1,"ĐẠT YÊU CẦU","CHƯA ĐẠT - CẦN XỬ LÝ")</f>
         <v>CHƯA ĐẠT - CẦN XỬ LÝ</v>
       </c>
-      <c r="E49" s="38"/>
-      <c r="F49" s="38"/>
+      <c r="E49" s="46"/>
+      <c r="F49" s="46"/>
     </row>
     <row r="51" spans="1:6" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A51" s="37" t="s">
-        <v>138</v>
-      </c>
-      <c r="B51" s="37"/>
-      <c r="C51" s="37"/>
-      <c r="D51" s="37" t="s">
-        <v>139</v>
-      </c>
-      <c r="E51" s="37"/>
-      <c r="F51" s="37"/>
+      <c r="A51" s="45" t="s">
+        <v>136</v>
+      </c>
+      <c r="B51" s="45"/>
+      <c r="C51" s="45"/>
+      <c r="D51" s="45" t="s">
+        <v>137</v>
+      </c>
+      <c r="E51" s="45"/>
+      <c r="F51" s="45"/>
     </row>
   </sheetData>
   <mergeCells count="26">
@@ -5761,736 +5762,736 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:6" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A1" s="41" t="s">
+      <c r="A1" s="50" t="s">
+        <v>309</v>
+      </c>
+      <c r="B1" s="50"/>
+      <c r="C1" s="50"/>
+      <c r="D1" s="50"/>
+      <c r="E1" s="50"/>
+      <c r="F1" s="50"/>
+    </row>
+    <row r="2" spans="1:6" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A2" s="51" t="s">
+        <v>15</v>
+      </c>
+      <c r="B2" s="51"/>
+      <c r="C2" s="51"/>
+      <c r="D2" s="25" t="s">
+        <v>16</v>
+      </c>
+      <c r="E2" s="25" t="s">
+        <v>17</v>
+      </c>
+      <c r="F2" s="25" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="3" spans="1:6" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A3" s="26" t="s">
+        <v>19</v>
+      </c>
+      <c r="B3" s="26" t="s">
+        <v>20</v>
+      </c>
+      <c r="C3" s="26" t="s">
+        <v>21</v>
+      </c>
+      <c r="D3" s="26" t="s">
+        <v>22</v>
+      </c>
+      <c r="E3" s="26" t="s">
+        <v>23</v>
+      </c>
+      <c r="F3" s="26" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="4" spans="1:6" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A4" s="48" t="s">
+        <v>139</v>
+      </c>
+      <c r="B4" s="48"/>
+      <c r="C4" s="48"/>
+      <c r="D4" s="48"/>
+      <c r="E4" s="48"/>
+      <c r="F4" s="48"/>
+    </row>
+    <row r="5" spans="1:6" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A5" s="29">
+        <v>1</v>
+      </c>
+      <c r="B5" s="30" t="s">
+        <v>25</v>
+      </c>
+      <c r="C5" s="30" t="s">
+        <v>140</v>
+      </c>
+      <c r="D5" s="30" t="s">
+        <v>310</v>
+      </c>
+      <c r="E5" s="29" t="s">
+        <v>435</v>
+      </c>
+      <c r="F5" s="30"/>
+    </row>
+    <row r="6" spans="1:6" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A6" s="31">
+        <v>2</v>
+      </c>
+      <c r="B6" s="32" t="s">
+        <v>25</v>
+      </c>
+      <c r="C6" s="32" t="s">
+        <v>239</v>
+      </c>
+      <c r="D6" s="32" t="s">
         <v>311</v>
       </c>
-      <c r="B1" s="41"/>
-      <c r="C1" s="41"/>
-      <c r="D1" s="41"/>
-      <c r="E1" s="41"/>
-      <c r="F1" s="41"/>
-    </row>
-    <row r="2" spans="1:6" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A2" s="42" t="s">
+      <c r="E6" s="31"/>
+      <c r="F6" s="32"/>
+    </row>
+    <row r="7" spans="1:6" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A7" s="29">
+        <v>3</v>
+      </c>
+      <c r="B7" s="30" t="s">
+        <v>25</v>
+      </c>
+      <c r="C7" s="30" t="s">
+        <v>241</v>
+      </c>
+      <c r="D7" s="30" t="s">
+        <v>312</v>
+      </c>
+      <c r="E7" s="29"/>
+      <c r="F7" s="30"/>
+    </row>
+    <row r="8" spans="1:6" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A8" s="31">
+        <v>4</v>
+      </c>
+      <c r="B8" s="32" t="s">
+        <v>25</v>
+      </c>
+      <c r="C8" s="32" t="s">
+        <v>313</v>
+      </c>
+      <c r="D8" s="32" t="s">
+        <v>244</v>
+      </c>
+      <c r="E8" s="31"/>
+      <c r="F8" s="32"/>
+    </row>
+    <row r="9" spans="1:6" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A9" s="48" t="s">
+        <v>245</v>
+      </c>
+      <c r="B9" s="48"/>
+      <c r="C9" s="48"/>
+      <c r="D9" s="48"/>
+      <c r="E9" s="48"/>
+      <c r="F9" s="48"/>
+    </row>
+    <row r="10" spans="1:6" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A10" s="29">
+        <v>5</v>
+      </c>
+      <c r="B10" s="30" t="s">
+        <v>246</v>
+      </c>
+      <c r="C10" s="30" t="s">
+        <v>247</v>
+      </c>
+      <c r="D10" s="30" t="s">
+        <v>314</v>
+      </c>
+      <c r="E10" s="29"/>
+      <c r="F10" s="30"/>
+    </row>
+    <row r="11" spans="1:6" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A11" s="31">
+        <v>6</v>
+      </c>
+      <c r="B11" s="32" t="s">
+        <v>246</v>
+      </c>
+      <c r="C11" s="32" t="s">
+        <v>315</v>
+      </c>
+      <c r="D11" s="32" t="s">
+        <v>316</v>
+      </c>
+      <c r="E11" s="31"/>
+      <c r="F11" s="32"/>
+    </row>
+    <row r="12" spans="1:6" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A12" s="29">
+        <v>7</v>
+      </c>
+      <c r="B12" s="30" t="s">
+        <v>246</v>
+      </c>
+      <c r="C12" s="30" t="s">
+        <v>317</v>
+      </c>
+      <c r="D12" s="30" t="s">
+        <v>318</v>
+      </c>
+      <c r="E12" s="29"/>
+      <c r="F12" s="30"/>
+    </row>
+    <row r="13" spans="1:6" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A13" s="31">
+        <v>8</v>
+      </c>
+      <c r="B13" s="32" t="s">
+        <v>246</v>
+      </c>
+      <c r="C13" s="32" t="s">
+        <v>253</v>
+      </c>
+      <c r="D13" s="32" t="s">
+        <v>254</v>
+      </c>
+      <c r="E13" s="31"/>
+      <c r="F13" s="32"/>
+    </row>
+    <row r="14" spans="1:6" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A14" s="48" t="s">
+        <v>257</v>
+      </c>
+      <c r="B14" s="48"/>
+      <c r="C14" s="48"/>
+      <c r="D14" s="48"/>
+      <c r="E14" s="48"/>
+      <c r="F14" s="48"/>
+    </row>
+    <row r="15" spans="1:6" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A15" s="29">
+        <v>9</v>
+      </c>
+      <c r="B15" s="30" t="s">
+        <v>258</v>
+      </c>
+      <c r="C15" s="30" t="s">
+        <v>154</v>
+      </c>
+      <c r="D15" s="30" t="s">
+        <v>319</v>
+      </c>
+      <c r="E15" s="29"/>
+      <c r="F15" s="30"/>
+    </row>
+    <row r="16" spans="1:6" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A16" s="31">
+        <v>10</v>
+      </c>
+      <c r="B16" s="32" t="s">
+        <v>258</v>
+      </c>
+      <c r="C16" s="32" t="s">
+        <v>320</v>
+      </c>
+      <c r="D16" s="32" t="s">
+        <v>319</v>
+      </c>
+      <c r="E16" s="31"/>
+      <c r="F16" s="32"/>
+    </row>
+    <row r="17" spans="1:6" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A17" s="29">
+        <v>11</v>
+      </c>
+      <c r="B17" s="30" t="s">
+        <v>258</v>
+      </c>
+      <c r="C17" s="30" t="s">
+        <v>321</v>
+      </c>
+      <c r="D17" s="30" t="s">
+        <v>322</v>
+      </c>
+      <c r="E17" s="29"/>
+      <c r="F17" s="30"/>
+    </row>
+    <row r="18" spans="1:6" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A18" s="31">
+        <v>12</v>
+      </c>
+      <c r="B18" s="32" t="s">
+        <v>258</v>
+      </c>
+      <c r="C18" s="32" t="s">
+        <v>158</v>
+      </c>
+      <c r="D18" s="32" t="s">
+        <v>319</v>
+      </c>
+      <c r="E18" s="31"/>
+      <c r="F18" s="32"/>
+    </row>
+    <row r="19" spans="1:6" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A19" s="48" t="s">
+        <v>262</v>
+      </c>
+      <c r="B19" s="48"/>
+      <c r="C19" s="48"/>
+      <c r="D19" s="48"/>
+      <c r="E19" s="48"/>
+      <c r="F19" s="48"/>
+    </row>
+    <row r="20" spans="1:6" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A20" s="29">
+        <v>13</v>
+      </c>
+      <c r="B20" s="30" t="s">
+        <v>263</v>
+      </c>
+      <c r="C20" s="30" t="s">
+        <v>264</v>
+      </c>
+      <c r="D20" s="30" t="s">
+        <v>323</v>
+      </c>
+      <c r="E20" s="29"/>
+      <c r="F20" s="30"/>
+    </row>
+    <row r="21" spans="1:6" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A21" s="31">
+        <v>14</v>
+      </c>
+      <c r="B21" s="32" t="s">
+        <v>263</v>
+      </c>
+      <c r="C21" s="32" t="s">
+        <v>324</v>
+      </c>
+      <c r="D21" s="32" t="s">
+        <v>325</v>
+      </c>
+      <c r="E21" s="31"/>
+      <c r="F21" s="32"/>
+    </row>
+    <row r="22" spans="1:6" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A22" s="29">
         <v>15</v>
       </c>
-      <c r="B2" s="42"/>
-      <c r="C2" s="42"/>
-      <c r="D2" s="43" t="s">
+      <c r="B22" s="30" t="s">
+        <v>263</v>
+      </c>
+      <c r="C22" s="30" t="s">
+        <v>326</v>
+      </c>
+      <c r="D22" s="30" t="s">
+        <v>327</v>
+      </c>
+      <c r="E22" s="29" t="s">
+        <v>435</v>
+      </c>
+      <c r="F22" s="30"/>
+    </row>
+    <row r="23" spans="1:6" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A23" s="31">
         <v>16</v>
       </c>
-      <c r="E2" s="43" t="s">
+      <c r="B23" s="32" t="s">
+        <v>263</v>
+      </c>
+      <c r="C23" s="32" t="s">
+        <v>328</v>
+      </c>
+      <c r="D23" s="32" t="s">
+        <v>329</v>
+      </c>
+      <c r="E23" s="29" t="s">
+        <v>435</v>
+      </c>
+      <c r="F23" s="32"/>
+    </row>
+    <row r="24" spans="1:6" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A24" s="48" t="s">
+        <v>330</v>
+      </c>
+      <c r="B24" s="48"/>
+      <c r="C24" s="48"/>
+      <c r="D24" s="48"/>
+      <c r="E24" s="48"/>
+      <c r="F24" s="48"/>
+    </row>
+    <row r="25" spans="1:6" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A25" s="29">
         <v>17</v>
       </c>
-      <c r="F2" s="43" t="s">
+      <c r="B25" s="30" t="s">
+        <v>331</v>
+      </c>
+      <c r="C25" s="30" t="s">
+        <v>282</v>
+      </c>
+      <c r="D25" s="30" t="s">
+        <v>283</v>
+      </c>
+      <c r="E25" s="29" t="s">
+        <v>435</v>
+      </c>
+      <c r="F25" s="30"/>
+    </row>
+    <row r="26" spans="1:6" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A26" s="31">
         <v>18</v>
       </c>
-    </row>
-    <row r="3" spans="1:6" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A3" s="44" t="s">
+      <c r="B26" s="32" t="s">
+        <v>331</v>
+      </c>
+      <c r="C26" s="32" t="s">
+        <v>284</v>
+      </c>
+      <c r="D26" s="32" t="s">
+        <v>332</v>
+      </c>
+      <c r="E26" s="29" t="s">
+        <v>435</v>
+      </c>
+      <c r="F26" s="32"/>
+    </row>
+    <row r="27" spans="1:6" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A27" s="29">
         <v>19</v>
       </c>
-      <c r="B3" s="44" t="s">
+      <c r="B27" s="30" t="s">
+        <v>331</v>
+      </c>
+      <c r="C27" s="30" t="s">
+        <v>333</v>
+      </c>
+      <c r="D27" s="30" t="s">
+        <v>334</v>
+      </c>
+      <c r="E27" s="29" t="s">
+        <v>435</v>
+      </c>
+      <c r="F27" s="30"/>
+    </row>
+    <row r="28" spans="1:6" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A28" s="48" t="s">
+        <v>335</v>
+      </c>
+      <c r="B28" s="48"/>
+      <c r="C28" s="48"/>
+      <c r="D28" s="48"/>
+      <c r="E28" s="48"/>
+      <c r="F28" s="48"/>
+    </row>
+    <row r="29" spans="1:6" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A29" s="31">
         <v>20</v>
       </c>
-      <c r="C3" s="44" t="s">
+      <c r="B29" s="32" t="s">
+        <v>336</v>
+      </c>
+      <c r="C29" s="32" t="s">
+        <v>289</v>
+      </c>
+      <c r="D29" s="32" t="s">
+        <v>337</v>
+      </c>
+      <c r="E29" s="29" t="s">
+        <v>435</v>
+      </c>
+      <c r="F29" s="32"/>
+    </row>
+    <row r="30" spans="1:6" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A30" s="48" t="s">
+        <v>338</v>
+      </c>
+      <c r="B30" s="48"/>
+      <c r="C30" s="48"/>
+      <c r="D30" s="48"/>
+      <c r="E30" s="48"/>
+      <c r="F30" s="48"/>
+    </row>
+    <row r="31" spans="1:6" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A31" s="29">
         <v>21</v>
       </c>
-      <c r="D3" s="44" t="s">
+      <c r="B31" s="30" t="s">
+        <v>339</v>
+      </c>
+      <c r="C31" s="30" t="s">
+        <v>295</v>
+      </c>
+      <c r="D31" s="30" t="s">
+        <v>340</v>
+      </c>
+      <c r="E31" s="29" t="s">
+        <v>435</v>
+      </c>
+      <c r="F31" s="30"/>
+    </row>
+    <row r="32" spans="1:6" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A32" s="31">
         <v>22</v>
       </c>
-      <c r="E3" s="44" t="s">
+      <c r="B32" s="32" t="s">
+        <v>339</v>
+      </c>
+      <c r="C32" s="32" t="s">
+        <v>297</v>
+      </c>
+      <c r="D32" s="32" t="s">
+        <v>341</v>
+      </c>
+      <c r="E32" s="29" t="s">
+        <v>435</v>
+      </c>
+      <c r="F32" s="32"/>
+    </row>
+    <row r="33" spans="1:6" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A33" s="48" t="s">
+        <v>342</v>
+      </c>
+      <c r="B33" s="48"/>
+      <c r="C33" s="48"/>
+      <c r="D33" s="48"/>
+      <c r="E33" s="48"/>
+      <c r="F33" s="48"/>
+    </row>
+    <row r="34" spans="1:6" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A34" s="29">
         <v>23</v>
       </c>
-      <c r="F3" s="44" t="s">
+      <c r="B34" s="30" t="s">
+        <v>343</v>
+      </c>
+      <c r="C34" s="30" t="s">
+        <v>344</v>
+      </c>
+      <c r="D34" s="30" t="s">
+        <v>345</v>
+      </c>
+      <c r="E34" s="29" t="s">
+        <v>435</v>
+      </c>
+      <c r="F34" s="30"/>
+    </row>
+    <row r="35" spans="1:6" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A35" s="31">
         <v>24</v>
       </c>
-    </row>
-    <row r="4" spans="1:6" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A4" s="45" t="s">
-        <v>141</v>
-      </c>
-      <c r="B4" s="45"/>
-      <c r="C4" s="45"/>
-      <c r="D4" s="45"/>
-      <c r="E4" s="45"/>
-      <c r="F4" s="45"/>
-    </row>
-    <row r="5" spans="1:6" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A5" s="48">
-        <v>1</v>
-      </c>
-      <c r="B5" s="49" t="s">
+      <c r="B35" s="32" t="s">
+        <v>343</v>
+      </c>
+      <c r="C35" s="32" t="s">
+        <v>346</v>
+      </c>
+      <c r="D35" s="32" t="s">
+        <v>347</v>
+      </c>
+      <c r="E35" s="29" t="s">
+        <v>435</v>
+      </c>
+      <c r="F35" s="32"/>
+    </row>
+    <row r="36" spans="1:6" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A36" s="29">
         <v>25</v>
       </c>
-      <c r="C5" s="49" t="s">
-        <v>142</v>
-      </c>
-      <c r="D5" s="49" t="s">
-        <v>312</v>
-      </c>
-      <c r="E5" s="48" t="s">
-        <v>437</v>
-      </c>
-      <c r="F5" s="49"/>
-    </row>
-    <row r="6" spans="1:6" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A6" s="50">
-        <v>2</v>
-      </c>
-      <c r="B6" s="51" t="s">
-        <v>25</v>
-      </c>
-      <c r="C6" s="51" t="s">
-        <v>241</v>
-      </c>
-      <c r="D6" s="51" t="s">
-        <v>313</v>
-      </c>
-      <c r="E6" s="50"/>
-      <c r="F6" s="51"/>
-    </row>
-    <row r="7" spans="1:6" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A7" s="48">
-        <v>3</v>
-      </c>
-      <c r="B7" s="49" t="s">
-        <v>25</v>
-      </c>
-      <c r="C7" s="49" t="s">
-        <v>243</v>
-      </c>
-      <c r="D7" s="49" t="s">
-        <v>314</v>
-      </c>
-      <c r="E7" s="48"/>
-      <c r="F7" s="49"/>
-    </row>
-    <row r="8" spans="1:6" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A8" s="50">
-        <v>4</v>
-      </c>
-      <c r="B8" s="51" t="s">
-        <v>25</v>
-      </c>
-      <c r="C8" s="51" t="s">
-        <v>315</v>
-      </c>
-      <c r="D8" s="51" t="s">
-        <v>246</v>
-      </c>
-      <c r="E8" s="50"/>
-      <c r="F8" s="51"/>
-    </row>
-    <row r="9" spans="1:6" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A9" s="45" t="s">
-        <v>247</v>
-      </c>
-      <c r="B9" s="45"/>
-      <c r="C9" s="45"/>
-      <c r="D9" s="45"/>
-      <c r="E9" s="45"/>
-      <c r="F9" s="45"/>
-    </row>
-    <row r="10" spans="1:6" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A10" s="48">
-        <v>5</v>
-      </c>
-      <c r="B10" s="49" t="s">
-        <v>248</v>
-      </c>
-      <c r="C10" s="49" t="s">
-        <v>249</v>
-      </c>
-      <c r="D10" s="49" t="s">
-        <v>316</v>
-      </c>
-      <c r="E10" s="48"/>
-      <c r="F10" s="49"/>
-    </row>
-    <row r="11" spans="1:6" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A11" s="50">
-        <v>6</v>
-      </c>
-      <c r="B11" s="51" t="s">
-        <v>248</v>
-      </c>
-      <c r="C11" s="51" t="s">
-        <v>317</v>
-      </c>
-      <c r="D11" s="51" t="s">
-        <v>318</v>
-      </c>
-      <c r="E11" s="50"/>
-      <c r="F11" s="51"/>
-    </row>
-    <row r="12" spans="1:6" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A12" s="48">
-        <v>7</v>
-      </c>
-      <c r="B12" s="49" t="s">
-        <v>248</v>
-      </c>
-      <c r="C12" s="49" t="s">
-        <v>319</v>
-      </c>
-      <c r="D12" s="49" t="s">
-        <v>320</v>
-      </c>
-      <c r="E12" s="48"/>
-      <c r="F12" s="49"/>
-    </row>
-    <row r="13" spans="1:6" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A13" s="50">
-        <v>8</v>
-      </c>
-      <c r="B13" s="51" t="s">
-        <v>248</v>
-      </c>
-      <c r="C13" s="51" t="s">
-        <v>255</v>
-      </c>
-      <c r="D13" s="51" t="s">
-        <v>256</v>
-      </c>
-      <c r="E13" s="50"/>
-      <c r="F13" s="51"/>
-    </row>
-    <row r="14" spans="1:6" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A14" s="45" t="s">
-        <v>259</v>
-      </c>
-      <c r="B14" s="45"/>
-      <c r="C14" s="45"/>
-      <c r="D14" s="45"/>
-      <c r="E14" s="45"/>
-      <c r="F14" s="45"/>
-    </row>
-    <row r="15" spans="1:6" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A15" s="48">
-        <v>9</v>
-      </c>
-      <c r="B15" s="49" t="s">
-        <v>260</v>
-      </c>
-      <c r="C15" s="49" t="s">
-        <v>156</v>
-      </c>
-      <c r="D15" s="49" t="s">
-        <v>321</v>
-      </c>
-      <c r="E15" s="48"/>
-      <c r="F15" s="49"/>
-    </row>
-    <row r="16" spans="1:6" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A16" s="50">
-        <v>10</v>
-      </c>
-      <c r="B16" s="51" t="s">
-        <v>260</v>
-      </c>
-      <c r="C16" s="51" t="s">
-        <v>322</v>
-      </c>
-      <c r="D16" s="51" t="s">
-        <v>321</v>
-      </c>
-      <c r="E16" s="50"/>
-      <c r="F16" s="51"/>
-    </row>
-    <row r="17" spans="1:6" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A17" s="48">
-        <v>11</v>
-      </c>
-      <c r="B17" s="49" t="s">
-        <v>260</v>
-      </c>
-      <c r="C17" s="49" t="s">
-        <v>323</v>
-      </c>
-      <c r="D17" s="49" t="s">
-        <v>324</v>
-      </c>
-      <c r="E17" s="48"/>
-      <c r="F17" s="49"/>
-    </row>
-    <row r="18" spans="1:6" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A18" s="50">
-        <v>12</v>
-      </c>
-      <c r="B18" s="51" t="s">
-        <v>260</v>
-      </c>
-      <c r="C18" s="51" t="s">
-        <v>160</v>
-      </c>
-      <c r="D18" s="51" t="s">
-        <v>321</v>
-      </c>
-      <c r="E18" s="50"/>
-      <c r="F18" s="51"/>
-    </row>
-    <row r="19" spans="1:6" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A19" s="45" t="s">
-        <v>264</v>
-      </c>
-      <c r="B19" s="45"/>
-      <c r="C19" s="45"/>
-      <c r="D19" s="45"/>
-      <c r="E19" s="45"/>
-      <c r="F19" s="45"/>
-    </row>
-    <row r="20" spans="1:6" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A20" s="48">
-        <v>13</v>
-      </c>
-      <c r="B20" s="49" t="s">
-        <v>265</v>
-      </c>
-      <c r="C20" s="49" t="s">
-        <v>266</v>
-      </c>
-      <c r="D20" s="49" t="s">
-        <v>325</v>
-      </c>
-      <c r="E20" s="48"/>
-      <c r="F20" s="49"/>
-    </row>
-    <row r="21" spans="1:6" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A21" s="50">
-        <v>14</v>
-      </c>
-      <c r="B21" s="51" t="s">
-        <v>265</v>
-      </c>
-      <c r="C21" s="51" t="s">
-        <v>326</v>
-      </c>
-      <c r="D21" s="51" t="s">
-        <v>327</v>
-      </c>
-      <c r="E21" s="50"/>
-      <c r="F21" s="51"/>
-    </row>
-    <row r="22" spans="1:6" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A22" s="48">
-        <v>15</v>
-      </c>
-      <c r="B22" s="49" t="s">
-        <v>265</v>
-      </c>
-      <c r="C22" s="49" t="s">
-        <v>328</v>
-      </c>
-      <c r="D22" s="49" t="s">
-        <v>329</v>
-      </c>
-      <c r="E22" s="48" t="s">
-        <v>437</v>
-      </c>
-      <c r="F22" s="49"/>
-    </row>
-    <row r="23" spans="1:6" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A23" s="50">
-        <v>16</v>
-      </c>
-      <c r="B23" s="51" t="s">
-        <v>265</v>
-      </c>
-      <c r="C23" s="51" t="s">
-        <v>330</v>
-      </c>
-      <c r="D23" s="51" t="s">
-        <v>331</v>
-      </c>
-      <c r="E23" s="48" t="s">
-        <v>437</v>
-      </c>
-      <c r="F23" s="51"/>
-    </row>
-    <row r="24" spans="1:6" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A24" s="45" t="s">
-        <v>332</v>
-      </c>
-      <c r="B24" s="45"/>
-      <c r="C24" s="45"/>
-      <c r="D24" s="45"/>
-      <c r="E24" s="45"/>
-      <c r="F24" s="45"/>
-    </row>
-    <row r="25" spans="1:6" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A25" s="48">
-        <v>17</v>
-      </c>
-      <c r="B25" s="49" t="s">
-        <v>333</v>
-      </c>
-      <c r="C25" s="49" t="s">
-        <v>284</v>
-      </c>
-      <c r="D25" s="49" t="s">
-        <v>285</v>
-      </c>
-      <c r="E25" s="48" t="s">
-        <v>437</v>
-      </c>
-      <c r="F25" s="49"/>
-    </row>
-    <row r="26" spans="1:6" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A26" s="50">
-        <v>18</v>
-      </c>
-      <c r="B26" s="51" t="s">
-        <v>333</v>
-      </c>
-      <c r="C26" s="51" t="s">
-        <v>286</v>
-      </c>
-      <c r="D26" s="51" t="s">
-        <v>334</v>
-      </c>
-      <c r="E26" s="48" t="s">
-        <v>437</v>
-      </c>
-      <c r="F26" s="51"/>
-    </row>
-    <row r="27" spans="1:6" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A27" s="48">
-        <v>19</v>
-      </c>
-      <c r="B27" s="49" t="s">
-        <v>333</v>
-      </c>
-      <c r="C27" s="49" t="s">
-        <v>335</v>
-      </c>
-      <c r="D27" s="49" t="s">
-        <v>336</v>
-      </c>
-      <c r="E27" s="48" t="s">
-        <v>437</v>
-      </c>
-      <c r="F27" s="49"/>
-    </row>
-    <row r="28" spans="1:6" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A28" s="45" t="s">
-        <v>337</v>
-      </c>
-      <c r="B28" s="45"/>
-      <c r="C28" s="45"/>
-      <c r="D28" s="45"/>
-      <c r="E28" s="45"/>
-      <c r="F28" s="45"/>
-    </row>
-    <row r="29" spans="1:6" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A29" s="50">
-        <v>20</v>
-      </c>
-      <c r="B29" s="51" t="s">
-        <v>338</v>
-      </c>
-      <c r="C29" s="51" t="s">
-        <v>291</v>
-      </c>
-      <c r="D29" s="51" t="s">
-        <v>339</v>
-      </c>
-      <c r="E29" s="48" t="s">
-        <v>437</v>
-      </c>
-      <c r="F29" s="51"/>
-    </row>
-    <row r="30" spans="1:6" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A30" s="45" t="s">
-        <v>340</v>
-      </c>
-      <c r="B30" s="45"/>
-      <c r="C30" s="45"/>
-      <c r="D30" s="45"/>
-      <c r="E30" s="45"/>
-      <c r="F30" s="45"/>
-    </row>
-    <row r="31" spans="1:6" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A31" s="48">
-        <v>21</v>
-      </c>
-      <c r="B31" s="49" t="s">
-        <v>341</v>
-      </c>
-      <c r="C31" s="49" t="s">
-        <v>297</v>
-      </c>
-      <c r="D31" s="49" t="s">
-        <v>342</v>
-      </c>
-      <c r="E31" s="48" t="s">
-        <v>437</v>
-      </c>
-      <c r="F31" s="49"/>
-    </row>
-    <row r="32" spans="1:6" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A32" s="50">
-        <v>22</v>
-      </c>
-      <c r="B32" s="51" t="s">
-        <v>341</v>
-      </c>
-      <c r="C32" s="51" t="s">
-        <v>299</v>
-      </c>
-      <c r="D32" s="51" t="s">
+      <c r="B36" s="30" t="s">
         <v>343</v>
       </c>
-      <c r="E32" s="48" t="s">
-        <v>437</v>
-      </c>
-      <c r="F32" s="51"/>
-    </row>
-    <row r="33" spans="1:6" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A33" s="45" t="s">
-        <v>344</v>
-      </c>
-      <c r="B33" s="45"/>
-      <c r="C33" s="45"/>
-      <c r="D33" s="45"/>
-      <c r="E33" s="45"/>
-      <c r="F33" s="45"/>
-    </row>
-    <row r="34" spans="1:6" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A34" s="48">
-        <v>23</v>
-      </c>
-      <c r="B34" s="49" t="s">
-        <v>345</v>
-      </c>
-      <c r="C34" s="49" t="s">
-        <v>346</v>
-      </c>
-      <c r="D34" s="49" t="s">
-        <v>347</v>
-      </c>
-      <c r="E34" s="48" t="s">
-        <v>437</v>
-      </c>
-      <c r="F34" s="49"/>
-    </row>
-    <row r="35" spans="1:6" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A35" s="50">
-        <v>24</v>
-      </c>
-      <c r="B35" s="51" t="s">
-        <v>345</v>
-      </c>
-      <c r="C35" s="51" t="s">
+      <c r="C36" s="30" t="s">
+        <v>305</v>
+      </c>
+      <c r="D36" s="30" t="s">
         <v>348</v>
       </c>
-      <c r="D35" s="51" t="s">
+      <c r="E36" s="29" t="s">
+        <v>435</v>
+      </c>
+      <c r="F36" s="30"/>
+    </row>
+    <row r="37" spans="1:6" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A37" s="31">
+        <v>26</v>
+      </c>
+      <c r="B37" s="32" t="s">
+        <v>343</v>
+      </c>
+      <c r="C37" s="32" t="s">
         <v>349</v>
       </c>
-      <c r="E35" s="48" t="s">
-        <v>437</v>
-      </c>
-      <c r="F35" s="51"/>
-    </row>
-    <row r="36" spans="1:6" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A36" s="48">
-        <v>25</v>
-      </c>
-      <c r="B36" s="49" t="s">
-        <v>345</v>
-      </c>
-      <c r="C36" s="49" t="s">
-        <v>307</v>
-      </c>
-      <c r="D36" s="49" t="s">
+      <c r="D37" s="32" t="s">
         <v>350</v>
       </c>
-      <c r="E36" s="48" t="s">
-        <v>437</v>
-      </c>
-      <c r="F36" s="49"/>
-    </row>
-    <row r="37" spans="1:6" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A37" s="50">
-        <v>26</v>
-      </c>
-      <c r="B37" s="51" t="s">
-        <v>345</v>
-      </c>
-      <c r="C37" s="51" t="s">
+      <c r="E37" s="29" t="s">
+        <v>435</v>
+      </c>
+      <c r="F37" s="32"/>
+    </row>
+    <row r="38" spans="1:6" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A38" s="29">
+        <v>27</v>
+      </c>
+      <c r="B38" s="30" t="s">
+        <v>343</v>
+      </c>
+      <c r="C38" s="30" t="s">
         <v>351</v>
       </c>
-      <c r="D37" s="51" t="s">
+      <c r="D38" s="30" t="s">
         <v>352</v>
       </c>
-      <c r="E37" s="48" t="s">
-        <v>437</v>
-      </c>
-      <c r="F37" s="51"/>
-    </row>
-    <row r="38" spans="1:6" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A38" s="48">
-        <v>27</v>
-      </c>
-      <c r="B38" s="49" t="s">
-        <v>345</v>
-      </c>
-      <c r="C38" s="49" t="s">
+      <c r="E38" s="29" t="s">
+        <v>435</v>
+      </c>
+      <c r="F38" s="30"/>
+    </row>
+    <row r="39" spans="1:6" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A39" s="31">
+        <v>28</v>
+      </c>
+      <c r="B39" s="32" t="s">
+        <v>343</v>
+      </c>
+      <c r="C39" s="32" t="s">
         <v>353</v>
       </c>
-      <c r="D38" s="49" t="s">
+      <c r="D39" s="32" t="s">
         <v>354</v>
       </c>
-      <c r="E38" s="48" t="s">
-        <v>437</v>
-      </c>
-      <c r="F38" s="49"/>
-    </row>
-    <row r="39" spans="1:6" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A39" s="50">
-        <v>28</v>
-      </c>
-      <c r="B39" s="51" t="s">
-        <v>345</v>
-      </c>
-      <c r="C39" s="51" t="s">
+      <c r="E39" s="29" t="s">
+        <v>435</v>
+      </c>
+      <c r="F39" s="32"/>
+    </row>
+    <row r="40" spans="1:6" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A40" s="48" t="s">
         <v>355</v>
       </c>
-      <c r="D39" s="51" t="s">
+      <c r="B40" s="48"/>
+      <c r="C40" s="48"/>
+      <c r="D40" s="48"/>
+      <c r="E40" s="48"/>
+      <c r="F40" s="48"/>
+    </row>
+    <row r="41" spans="1:6" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A41" s="29">
+        <v>29</v>
+      </c>
+      <c r="B41" s="30" t="s">
         <v>356</v>
       </c>
-      <c r="E39" s="48" t="s">
-        <v>437</v>
-      </c>
-      <c r="F39" s="51"/>
-    </row>
-    <row r="40" spans="1:6" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A40" s="45" t="s">
+      <c r="C41" s="30" t="s">
         <v>357</v>
       </c>
-      <c r="B40" s="45"/>
-      <c r="C40" s="45"/>
-      <c r="D40" s="45"/>
-      <c r="E40" s="45"/>
-      <c r="F40" s="45"/>
-    </row>
-    <row r="41" spans="1:6" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A41" s="48">
-        <v>29</v>
-      </c>
-      <c r="B41" s="49" t="s">
+      <c r="D41" s="30" t="s">
         <v>358</v>
       </c>
-      <c r="C41" s="49" t="s">
-        <v>359</v>
-      </c>
-      <c r="D41" s="49" t="s">
-        <v>360</v>
-      </c>
-      <c r="E41" s="48" t="s">
-        <v>437</v>
-      </c>
-      <c r="F41" s="49"/>
+      <c r="E41" s="29" t="s">
+        <v>435</v>
+      </c>
+      <c r="F41" s="30"/>
     </row>
     <row r="43" spans="1:6" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A43" s="40" t="s">
-        <v>131</v>
-      </c>
-      <c r="B43" s="40"/>
-      <c r="C43" s="40"/>
-      <c r="D43" s="40"/>
-      <c r="E43" s="40"/>
-      <c r="F43" s="40"/>
+      <c r="A43" s="49" t="s">
+        <v>129</v>
+      </c>
+      <c r="B43" s="49"/>
+      <c r="C43" s="49"/>
+      <c r="D43" s="49"/>
+      <c r="E43" s="49"/>
+      <c r="F43" s="49"/>
     </row>
     <row r="44" spans="1:6" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A44" s="37" t="s">
-        <v>132</v>
-      </c>
-      <c r="B44" s="37"/>
-      <c r="C44" s="37"/>
-      <c r="D44" s="38">
+      <c r="A44" s="45" t="s">
+        <v>130</v>
+      </c>
+      <c r="B44" s="45"/>
+      <c r="C44" s="45"/>
+      <c r="D44" s="46">
         <f>COUNTA(E4:E41)</f>
         <v>16</v>
       </c>
-      <c r="E44" s="38"/>
-      <c r="F44" s="38"/>
+      <c r="E44" s="46"/>
+      <c r="F44" s="46"/>
     </row>
     <row r="45" spans="1:6" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A45" s="37" t="s">
-        <v>133</v>
-      </c>
-      <c r="B45" s="37"/>
-      <c r="C45" s="37"/>
-      <c r="D45" s="38">
+      <c r="A45" s="45" t="s">
+        <v>131</v>
+      </c>
+      <c r="B45" s="45"/>
+      <c r="C45" s="45"/>
+      <c r="D45" s="46">
         <f>COUNTIF(E4:E41,"PASS")</f>
         <v>0</v>
       </c>
-      <c r="E45" s="38"/>
-      <c r="F45" s="38"/>
+      <c r="E45" s="46"/>
+      <c r="F45" s="46"/>
     </row>
     <row r="46" spans="1:6" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A46" s="37" t="s">
-        <v>134</v>
-      </c>
-      <c r="B46" s="37"/>
-      <c r="C46" s="37"/>
-      <c r="D46" s="38">
+      <c r="A46" s="45" t="s">
+        <v>132</v>
+      </c>
+      <c r="B46" s="45"/>
+      <c r="C46" s="45"/>
+      <c r="D46" s="46">
         <f>COUNTIF(E4:E41,"FAIL")</f>
         <v>0</v>
       </c>
-      <c r="E46" s="38"/>
-      <c r="F46" s="38"/>
+      <c r="E46" s="46"/>
+      <c r="F46" s="46"/>
     </row>
     <row r="47" spans="1:6" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A47" s="37" t="s">
-        <v>135</v>
-      </c>
-      <c r="B47" s="37"/>
-      <c r="C47" s="37"/>
-      <c r="D47" s="38">
+      <c r="A47" s="45" t="s">
+        <v>133</v>
+      </c>
+      <c r="B47" s="45"/>
+      <c r="C47" s="45"/>
+      <c r="D47" s="46">
         <f>COUNTIF(E4:E41,"N/A")</f>
         <v>16</v>
       </c>
-      <c r="E47" s="38"/>
-      <c r="F47" s="38"/>
+      <c r="E47" s="46"/>
+      <c r="F47" s="46"/>
     </row>
     <row r="48" spans="1:6" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A48" s="37" t="s">
-        <v>136</v>
-      </c>
-      <c r="B48" s="37"/>
-      <c r="C48" s="37"/>
-      <c r="D48" s="39">
+      <c r="A48" s="45" t="s">
+        <v>134</v>
+      </c>
+      <c r="B48" s="45"/>
+      <c r="C48" s="45"/>
+      <c r="D48" s="47">
         <f>IFERROR(COUNTIF(E4:E41,"PASS")/(COUNTA(E4:E41)-COUNTIF(E4:E41,"N/A")),0)</f>
         <v>0</v>
       </c>
-      <c r="E48" s="39"/>
-      <c r="F48" s="39"/>
+      <c r="E48" s="47"/>
+      <c r="F48" s="47"/>
     </row>
     <row r="49" spans="1:6" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A49" s="37" t="s">
-        <v>137</v>
-      </c>
-      <c r="B49" s="37"/>
-      <c r="C49" s="37"/>
-      <c r="D49" s="38" t="str">
+      <c r="A49" s="45" t="s">
+        <v>135</v>
+      </c>
+      <c r="B49" s="45"/>
+      <c r="C49" s="45"/>
+      <c r="D49" s="46" t="str">
         <f>IF(IFERROR(COUNTIF(E4:E41,"PASS")/(COUNTA(E4:E41)-COUNTIF(E4:E41,"N/A")),0)=1,"ĐẠT YÊU CẦU","CHƯA ĐẠT - CẦN XỬ LÝ")</f>
         <v>CHƯA ĐẠT - CẦN XỬ LÝ</v>
       </c>
-      <c r="E49" s="38"/>
-      <c r="F49" s="38"/>
+      <c r="E49" s="46"/>
+      <c r="F49" s="46"/>
     </row>
     <row r="51" spans="1:6" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A51" s="37" t="s">
-        <v>138</v>
-      </c>
-      <c r="B51" s="37"/>
-      <c r="C51" s="37"/>
-      <c r="D51" s="37" t="s">
-        <v>139</v>
-      </c>
-      <c r="E51" s="37"/>
-      <c r="F51" s="37"/>
+      <c r="A51" s="45" t="s">
+        <v>136</v>
+      </c>
+      <c r="B51" s="45"/>
+      <c r="C51" s="45"/>
+      <c r="D51" s="45" t="s">
+        <v>137</v>
+      </c>
+      <c r="E51" s="45"/>
+      <c r="F51" s="45"/>
     </row>
   </sheetData>
   <mergeCells count="26">
@@ -6565,770 +6566,770 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:6" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A1" s="41" t="s">
+      <c r="A1" s="50" t="s">
+        <v>359</v>
+      </c>
+      <c r="B1" s="50"/>
+      <c r="C1" s="50"/>
+      <c r="D1" s="50"/>
+      <c r="E1" s="50"/>
+      <c r="F1" s="50"/>
+    </row>
+    <row r="2" spans="1:6" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A2" s="51" t="s">
+        <v>15</v>
+      </c>
+      <c r="B2" s="51"/>
+      <c r="C2" s="51"/>
+      <c r="D2" s="25" t="s">
+        <v>16</v>
+      </c>
+      <c r="E2" s="25" t="s">
+        <v>17</v>
+      </c>
+      <c r="F2" s="25" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="3" spans="1:6" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A3" s="26" t="s">
+        <v>19</v>
+      </c>
+      <c r="B3" s="26" t="s">
+        <v>20</v>
+      </c>
+      <c r="C3" s="26" t="s">
+        <v>21</v>
+      </c>
+      <c r="D3" s="26" t="s">
+        <v>22</v>
+      </c>
+      <c r="E3" s="26" t="s">
+        <v>23</v>
+      </c>
+      <c r="F3" s="26" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="4" spans="1:6" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A4" s="48" t="s">
+        <v>360</v>
+      </c>
+      <c r="B4" s="48"/>
+      <c r="C4" s="48"/>
+      <c r="D4" s="48"/>
+      <c r="E4" s="48"/>
+      <c r="F4" s="48"/>
+    </row>
+    <row r="5" spans="1:6" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A5" s="29">
+        <v>1</v>
+      </c>
+      <c r="B5" s="30" t="s">
         <v>361</v>
       </c>
-      <c r="B1" s="41"/>
-      <c r="C1" s="41"/>
-      <c r="D1" s="41"/>
-      <c r="E1" s="41"/>
-      <c r="F1" s="41"/>
-    </row>
-    <row r="2" spans="1:6" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A2" s="42" t="s">
+      <c r="C5" s="30" t="s">
+        <v>362</v>
+      </c>
+      <c r="D5" s="30" t="s">
+        <v>363</v>
+      </c>
+      <c r="E5" s="29" t="s">
+        <v>435</v>
+      </c>
+      <c r="F5" s="30"/>
+    </row>
+    <row r="6" spans="1:6" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A6" s="31">
+        <v>2</v>
+      </c>
+      <c r="B6" s="32" t="s">
+        <v>361</v>
+      </c>
+      <c r="C6" s="32" t="s">
+        <v>364</v>
+      </c>
+      <c r="D6" s="32" t="s">
+        <v>365</v>
+      </c>
+      <c r="E6" s="29" t="s">
+        <v>435</v>
+      </c>
+      <c r="F6" s="32"/>
+    </row>
+    <row r="7" spans="1:6" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A7" s="29">
+        <v>3</v>
+      </c>
+      <c r="B7" s="30" t="s">
+        <v>361</v>
+      </c>
+      <c r="C7" s="30" t="s">
+        <v>366</v>
+      </c>
+      <c r="D7" s="30" t="s">
+        <v>367</v>
+      </c>
+      <c r="E7" s="29" t="s">
+        <v>435</v>
+      </c>
+      <c r="F7" s="30"/>
+    </row>
+    <row r="8" spans="1:6" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A8" s="31">
+        <v>4</v>
+      </c>
+      <c r="B8" s="32" t="s">
+        <v>361</v>
+      </c>
+      <c r="C8" s="32" t="s">
+        <v>368</v>
+      </c>
+      <c r="D8" s="32" t="s">
+        <v>369</v>
+      </c>
+      <c r="E8" s="29" t="s">
+        <v>435</v>
+      </c>
+      <c r="F8" s="32"/>
+    </row>
+    <row r="9" spans="1:6" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A9" s="29">
+        <v>5</v>
+      </c>
+      <c r="B9" s="30" t="s">
+        <v>361</v>
+      </c>
+      <c r="C9" s="30" t="s">
+        <v>370</v>
+      </c>
+      <c r="D9" s="30" t="s">
+        <v>371</v>
+      </c>
+      <c r="E9" s="29" t="s">
+        <v>435</v>
+      </c>
+      <c r="F9" s="30"/>
+    </row>
+    <row r="10" spans="1:6" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A10" s="48" t="s">
+        <v>372</v>
+      </c>
+      <c r="B10" s="48"/>
+      <c r="C10" s="48"/>
+      <c r="D10" s="48"/>
+      <c r="E10" s="48"/>
+      <c r="F10" s="48"/>
+    </row>
+    <row r="11" spans="1:6" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A11" s="31">
+        <v>6</v>
+      </c>
+      <c r="B11" s="32" t="s">
+        <v>373</v>
+      </c>
+      <c r="C11" s="32" t="s">
+        <v>374</v>
+      </c>
+      <c r="D11" s="32" t="s">
+        <v>375</v>
+      </c>
+      <c r="E11" s="29" t="s">
+        <v>435</v>
+      </c>
+      <c r="F11" s="32"/>
+    </row>
+    <row r="12" spans="1:6" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A12" s="29">
+        <v>7</v>
+      </c>
+      <c r="B12" s="30" t="s">
+        <v>373</v>
+      </c>
+      <c r="C12" s="30" t="s">
+        <v>154</v>
+      </c>
+      <c r="D12" s="30" t="s">
+        <v>376</v>
+      </c>
+      <c r="E12" s="29" t="s">
+        <v>435</v>
+      </c>
+      <c r="F12" s="30"/>
+    </row>
+    <row r="13" spans="1:6" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A13" s="31">
+        <v>8</v>
+      </c>
+      <c r="B13" s="32" t="s">
+        <v>373</v>
+      </c>
+      <c r="C13" s="32" t="s">
+        <v>377</v>
+      </c>
+      <c r="D13" s="32" t="s">
+        <v>378</v>
+      </c>
+      <c r="E13" s="29" t="s">
+        <v>435</v>
+      </c>
+      <c r="F13" s="32"/>
+    </row>
+    <row r="14" spans="1:6" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A14" s="29">
+        <v>9</v>
+      </c>
+      <c r="B14" s="30" t="s">
+        <v>373</v>
+      </c>
+      <c r="C14" s="30" t="s">
+        <v>379</v>
+      </c>
+      <c r="D14" s="30" t="s">
+        <v>380</v>
+      </c>
+      <c r="E14" s="29" t="s">
+        <v>435</v>
+      </c>
+      <c r="F14" s="30"/>
+    </row>
+    <row r="15" spans="1:6" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A15" s="31">
+        <v>10</v>
+      </c>
+      <c r="B15" s="32" t="s">
+        <v>373</v>
+      </c>
+      <c r="C15" s="32" t="s">
+        <v>381</v>
+      </c>
+      <c r="D15" s="32" t="s">
+        <v>382</v>
+      </c>
+      <c r="E15" s="29" t="s">
+        <v>435</v>
+      </c>
+      <c r="F15" s="32"/>
+    </row>
+    <row r="16" spans="1:6" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A16" s="48" t="s">
+        <v>383</v>
+      </c>
+      <c r="B16" s="48"/>
+      <c r="C16" s="48"/>
+      <c r="D16" s="48"/>
+      <c r="E16" s="48"/>
+      <c r="F16" s="48"/>
+    </row>
+    <row r="17" spans="1:6" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A17" s="29">
+        <v>11</v>
+      </c>
+      <c r="B17" s="30" t="s">
+        <v>384</v>
+      </c>
+      <c r="C17" s="30" t="s">
+        <v>385</v>
+      </c>
+      <c r="D17" s="30" t="s">
+        <v>386</v>
+      </c>
+      <c r="E17" s="29" t="s">
+        <v>435</v>
+      </c>
+      <c r="F17" s="30"/>
+    </row>
+    <row r="18" spans="1:6" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A18" s="31">
+        <v>12</v>
+      </c>
+      <c r="B18" s="32" t="s">
+        <v>384</v>
+      </c>
+      <c r="C18" s="32" t="s">
+        <v>387</v>
+      </c>
+      <c r="D18" s="32" t="s">
+        <v>388</v>
+      </c>
+      <c r="E18" s="29" t="s">
+        <v>435</v>
+      </c>
+      <c r="F18" s="32"/>
+    </row>
+    <row r="19" spans="1:6" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A19" s="29">
+        <v>13</v>
+      </c>
+      <c r="B19" s="30" t="s">
+        <v>384</v>
+      </c>
+      <c r="C19" s="30" t="s">
+        <v>389</v>
+      </c>
+      <c r="D19" s="30" t="s">
+        <v>390</v>
+      </c>
+      <c r="E19" s="29" t="s">
+        <v>435</v>
+      </c>
+      <c r="F19" s="30"/>
+    </row>
+    <row r="20" spans="1:6" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A20" s="31">
+        <v>14</v>
+      </c>
+      <c r="B20" s="32" t="s">
+        <v>384</v>
+      </c>
+      <c r="C20" s="32" t="s">
+        <v>391</v>
+      </c>
+      <c r="D20" s="32" t="s">
+        <v>392</v>
+      </c>
+      <c r="E20" s="29" t="s">
+        <v>435</v>
+      </c>
+      <c r="F20" s="32"/>
+    </row>
+    <row r="21" spans="1:6" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A21" s="48" t="s">
+        <v>393</v>
+      </c>
+      <c r="B21" s="48"/>
+      <c r="C21" s="48"/>
+      <c r="D21" s="48"/>
+      <c r="E21" s="48"/>
+      <c r="F21" s="48"/>
+    </row>
+    <row r="22" spans="1:6" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A22" s="29">
         <v>15</v>
       </c>
-      <c r="B2" s="42"/>
-      <c r="C2" s="42"/>
-      <c r="D2" s="43" t="s">
+      <c r="B22" s="30" t="s">
+        <v>394</v>
+      </c>
+      <c r="C22" s="30" t="s">
+        <v>282</v>
+      </c>
+      <c r="D22" s="30" t="s">
+        <v>395</v>
+      </c>
+      <c r="E22" s="29" t="s">
+        <v>435</v>
+      </c>
+      <c r="F22" s="30"/>
+    </row>
+    <row r="23" spans="1:6" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A23" s="31">
         <v>16</v>
       </c>
-      <c r="E2" s="43" t="s">
+      <c r="B23" s="32" t="s">
+        <v>394</v>
+      </c>
+      <c r="C23" s="32" t="s">
+        <v>284</v>
+      </c>
+      <c r="D23" s="32" t="s">
+        <v>396</v>
+      </c>
+      <c r="E23" s="29" t="s">
+        <v>435</v>
+      </c>
+      <c r="F23" s="32"/>
+    </row>
+    <row r="24" spans="1:6" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A24" s="29">
         <v>17</v>
       </c>
-      <c r="F2" s="43" t="s">
+      <c r="B24" s="30" t="s">
+        <v>394</v>
+      </c>
+      <c r="C24" s="30" t="s">
+        <v>397</v>
+      </c>
+      <c r="D24" s="30" t="s">
+        <v>398</v>
+      </c>
+      <c r="E24" s="29" t="s">
+        <v>435</v>
+      </c>
+      <c r="F24" s="30"/>
+    </row>
+    <row r="25" spans="1:6" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A25" s="48" t="s">
+        <v>399</v>
+      </c>
+      <c r="B25" s="48"/>
+      <c r="C25" s="48"/>
+      <c r="D25" s="48"/>
+      <c r="E25" s="48"/>
+      <c r="F25" s="48"/>
+    </row>
+    <row r="26" spans="1:6" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A26" s="31">
         <v>18</v>
       </c>
-    </row>
-    <row r="3" spans="1:6" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A3" s="44" t="s">
+      <c r="B26" s="32" t="s">
+        <v>400</v>
+      </c>
+      <c r="C26" s="32" t="s">
+        <v>401</v>
+      </c>
+      <c r="D26" s="32" t="s">
+        <v>402</v>
+      </c>
+      <c r="E26" s="29" t="s">
+        <v>435</v>
+      </c>
+      <c r="F26" s="32"/>
+    </row>
+    <row r="27" spans="1:6" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A27" s="29">
         <v>19</v>
       </c>
-      <c r="B3" s="44" t="s">
+      <c r="B27" s="30" t="s">
+        <v>400</v>
+      </c>
+      <c r="C27" s="30" t="s">
+        <v>403</v>
+      </c>
+      <c r="D27" s="30" t="s">
+        <v>404</v>
+      </c>
+      <c r="E27" s="29" t="s">
+        <v>435</v>
+      </c>
+      <c r="F27" s="30"/>
+    </row>
+    <row r="28" spans="1:6" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A28" s="31">
         <v>20</v>
       </c>
-      <c r="C3" s="44" t="s">
+      <c r="B28" s="32" t="s">
+        <v>400</v>
+      </c>
+      <c r="C28" s="32" t="s">
+        <v>405</v>
+      </c>
+      <c r="D28" s="32" t="s">
+        <v>406</v>
+      </c>
+      <c r="E28" s="29" t="s">
+        <v>435</v>
+      </c>
+      <c r="F28" s="32"/>
+    </row>
+    <row r="29" spans="1:6" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A29" s="29">
         <v>21</v>
       </c>
-      <c r="D3" s="44" t="s">
+      <c r="B29" s="30" t="s">
+        <v>400</v>
+      </c>
+      <c r="C29" s="30" t="s">
+        <v>407</v>
+      </c>
+      <c r="D29" s="30" t="s">
+        <v>408</v>
+      </c>
+      <c r="E29" s="29" t="s">
+        <v>435</v>
+      </c>
+      <c r="F29" s="30"/>
+    </row>
+    <row r="30" spans="1:6" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A30" s="48" t="s">
+        <v>409</v>
+      </c>
+      <c r="B30" s="48"/>
+      <c r="C30" s="48"/>
+      <c r="D30" s="48"/>
+      <c r="E30" s="48"/>
+      <c r="F30" s="48"/>
+    </row>
+    <row r="31" spans="1:6" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A31" s="31">
         <v>22</v>
       </c>
-      <c r="E3" s="44" t="s">
+      <c r="B31" s="32" t="s">
+        <v>410</v>
+      </c>
+      <c r="C31" s="32" t="s">
+        <v>411</v>
+      </c>
+      <c r="D31" s="32" t="s">
+        <v>412</v>
+      </c>
+      <c r="E31" s="29" t="s">
+        <v>435</v>
+      </c>
+      <c r="F31" s="32"/>
+    </row>
+    <row r="32" spans="1:6" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A32" s="29">
         <v>23</v>
       </c>
-      <c r="F3" s="44" t="s">
+      <c r="B32" s="30" t="s">
+        <v>410</v>
+      </c>
+      <c r="C32" s="30" t="s">
+        <v>413</v>
+      </c>
+      <c r="D32" s="30" t="s">
+        <v>414</v>
+      </c>
+      <c r="E32" s="29" t="s">
+        <v>435</v>
+      </c>
+      <c r="F32" s="30"/>
+    </row>
+    <row r="33" spans="1:6" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A33" s="31">
         <v>24</v>
       </c>
-    </row>
-    <row r="4" spans="1:6" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A4" s="45" t="s">
-        <v>362</v>
-      </c>
-      <c r="B4" s="45"/>
-      <c r="C4" s="45"/>
-      <c r="D4" s="45"/>
-      <c r="E4" s="45"/>
-      <c r="F4" s="45"/>
-    </row>
-    <row r="5" spans="1:6" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A5" s="48">
-        <v>1</v>
-      </c>
-      <c r="B5" s="49" t="s">
-        <v>363</v>
-      </c>
-      <c r="C5" s="49" t="s">
-        <v>364</v>
-      </c>
-      <c r="D5" s="49" t="s">
-        <v>365</v>
-      </c>
-      <c r="E5" s="48" t="s">
-        <v>437</v>
-      </c>
-      <c r="F5" s="49"/>
-    </row>
-    <row r="6" spans="1:6" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A6" s="50">
-        <v>2</v>
-      </c>
-      <c r="B6" s="51" t="s">
-        <v>363</v>
-      </c>
-      <c r="C6" s="51" t="s">
-        <v>366</v>
-      </c>
-      <c r="D6" s="51" t="s">
-        <v>367</v>
-      </c>
-      <c r="E6" s="48" t="s">
-        <v>437</v>
-      </c>
-      <c r="F6" s="51"/>
-    </row>
-    <row r="7" spans="1:6" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A7" s="48">
-        <v>3</v>
-      </c>
-      <c r="B7" s="49" t="s">
-        <v>363</v>
-      </c>
-      <c r="C7" s="49" t="s">
-        <v>368</v>
-      </c>
-      <c r="D7" s="49" t="s">
-        <v>369</v>
-      </c>
-      <c r="E7" s="48" t="s">
-        <v>437</v>
-      </c>
-      <c r="F7" s="49"/>
-    </row>
-    <row r="8" spans="1:6" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A8" s="50">
-        <v>4</v>
-      </c>
-      <c r="B8" s="51" t="s">
-        <v>363</v>
-      </c>
-      <c r="C8" s="51" t="s">
-        <v>370</v>
-      </c>
-      <c r="D8" s="51" t="s">
-        <v>371</v>
-      </c>
-      <c r="E8" s="48" t="s">
-        <v>437</v>
-      </c>
-      <c r="F8" s="51"/>
-    </row>
-    <row r="9" spans="1:6" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A9" s="48">
-        <v>5</v>
-      </c>
-      <c r="B9" s="49" t="s">
-        <v>363</v>
-      </c>
-      <c r="C9" s="49" t="s">
-        <v>372</v>
-      </c>
-      <c r="D9" s="49" t="s">
-        <v>373</v>
-      </c>
-      <c r="E9" s="48" t="s">
-        <v>437</v>
-      </c>
-      <c r="F9" s="49"/>
-    </row>
-    <row r="10" spans="1:6" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A10" s="45" t="s">
-        <v>374</v>
-      </c>
-      <c r="B10" s="45"/>
-      <c r="C10" s="45"/>
-      <c r="D10" s="45"/>
-      <c r="E10" s="45"/>
-      <c r="F10" s="45"/>
-    </row>
-    <row r="11" spans="1:6" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A11" s="50">
-        <v>6</v>
-      </c>
-      <c r="B11" s="51" t="s">
-        <v>375</v>
-      </c>
-      <c r="C11" s="51" t="s">
-        <v>376</v>
-      </c>
-      <c r="D11" s="51" t="s">
-        <v>377</v>
-      </c>
-      <c r="E11" s="48" t="s">
-        <v>437</v>
-      </c>
-      <c r="F11" s="51"/>
-    </row>
-    <row r="12" spans="1:6" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A12" s="48">
-        <v>7</v>
-      </c>
-      <c r="B12" s="49" t="s">
-        <v>375</v>
-      </c>
-      <c r="C12" s="49" t="s">
-        <v>156</v>
-      </c>
-      <c r="D12" s="49" t="s">
-        <v>378</v>
-      </c>
-      <c r="E12" s="48" t="s">
-        <v>437</v>
-      </c>
-      <c r="F12" s="49"/>
-    </row>
-    <row r="13" spans="1:6" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A13" s="50">
-        <v>8</v>
-      </c>
-      <c r="B13" s="51" t="s">
-        <v>375</v>
-      </c>
-      <c r="C13" s="51" t="s">
-        <v>379</v>
-      </c>
-      <c r="D13" s="51" t="s">
-        <v>380</v>
-      </c>
-      <c r="E13" s="48" t="s">
-        <v>437</v>
-      </c>
-      <c r="F13" s="51"/>
-    </row>
-    <row r="14" spans="1:6" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A14" s="48">
-        <v>9</v>
-      </c>
-      <c r="B14" s="49" t="s">
-        <v>375</v>
-      </c>
-      <c r="C14" s="49" t="s">
-        <v>381</v>
-      </c>
-      <c r="D14" s="49" t="s">
-        <v>382</v>
-      </c>
-      <c r="E14" s="48" t="s">
-        <v>437</v>
-      </c>
-      <c r="F14" s="49"/>
-    </row>
-    <row r="15" spans="1:6" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A15" s="50">
-        <v>10</v>
-      </c>
-      <c r="B15" s="51" t="s">
-        <v>375</v>
-      </c>
-      <c r="C15" s="51" t="s">
-        <v>383</v>
-      </c>
-      <c r="D15" s="51" t="s">
-        <v>384</v>
-      </c>
-      <c r="E15" s="48" t="s">
-        <v>437</v>
-      </c>
-      <c r="F15" s="51"/>
-    </row>
-    <row r="16" spans="1:6" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A16" s="45" t="s">
-        <v>385</v>
-      </c>
-      <c r="B16" s="45"/>
-      <c r="C16" s="45"/>
-      <c r="D16" s="45"/>
-      <c r="E16" s="45"/>
-      <c r="F16" s="45"/>
-    </row>
-    <row r="17" spans="1:6" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A17" s="48">
-        <v>11</v>
-      </c>
-      <c r="B17" s="49" t="s">
-        <v>386</v>
-      </c>
-      <c r="C17" s="49" t="s">
-        <v>387</v>
-      </c>
-      <c r="D17" s="49" t="s">
-        <v>388</v>
-      </c>
-      <c r="E17" s="48" t="s">
-        <v>437</v>
-      </c>
-      <c r="F17" s="49"/>
-    </row>
-    <row r="18" spans="1:6" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A18" s="50">
-        <v>12</v>
-      </c>
-      <c r="B18" s="51" t="s">
-        <v>386</v>
-      </c>
-      <c r="C18" s="51" t="s">
-        <v>389</v>
-      </c>
-      <c r="D18" s="51" t="s">
-        <v>390</v>
-      </c>
-      <c r="E18" s="48" t="s">
-        <v>437</v>
-      </c>
-      <c r="F18" s="51"/>
-    </row>
-    <row r="19" spans="1:6" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A19" s="48">
-        <v>13</v>
-      </c>
-      <c r="B19" s="49" t="s">
-        <v>386</v>
-      </c>
-      <c r="C19" s="49" t="s">
-        <v>391</v>
-      </c>
-      <c r="D19" s="49" t="s">
-        <v>392</v>
-      </c>
-      <c r="E19" s="48" t="s">
-        <v>437</v>
-      </c>
-      <c r="F19" s="49"/>
-    </row>
-    <row r="20" spans="1:6" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A20" s="50">
-        <v>14</v>
-      </c>
-      <c r="B20" s="51" t="s">
-        <v>386</v>
-      </c>
-      <c r="C20" s="51" t="s">
-        <v>393</v>
-      </c>
-      <c r="D20" s="51" t="s">
-        <v>394</v>
-      </c>
-      <c r="E20" s="48" t="s">
-        <v>437</v>
-      </c>
-      <c r="F20" s="51"/>
-    </row>
-    <row r="21" spans="1:6" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A21" s="45" t="s">
-        <v>395</v>
-      </c>
-      <c r="B21" s="45"/>
-      <c r="C21" s="45"/>
-      <c r="D21" s="45"/>
-      <c r="E21" s="45"/>
-      <c r="F21" s="45"/>
-    </row>
-    <row r="22" spans="1:6" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A22" s="48">
-        <v>15</v>
-      </c>
-      <c r="B22" s="49" t="s">
-        <v>396</v>
-      </c>
-      <c r="C22" s="49" t="s">
-        <v>284</v>
-      </c>
-      <c r="D22" s="49" t="s">
-        <v>397</v>
-      </c>
-      <c r="E22" s="48" t="s">
-        <v>437</v>
-      </c>
-      <c r="F22" s="49"/>
-    </row>
-    <row r="23" spans="1:6" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A23" s="50">
-        <v>16</v>
-      </c>
-      <c r="B23" s="51" t="s">
-        <v>396</v>
-      </c>
-      <c r="C23" s="51" t="s">
-        <v>286</v>
-      </c>
-      <c r="D23" s="51" t="s">
-        <v>398</v>
-      </c>
-      <c r="E23" s="48" t="s">
-        <v>437</v>
-      </c>
-      <c r="F23" s="51"/>
-    </row>
-    <row r="24" spans="1:6" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A24" s="48">
-        <v>17</v>
-      </c>
-      <c r="B24" s="49" t="s">
-        <v>396</v>
-      </c>
-      <c r="C24" s="49" t="s">
-        <v>399</v>
-      </c>
-      <c r="D24" s="49" t="s">
-        <v>400</v>
-      </c>
-      <c r="E24" s="48" t="s">
-        <v>437</v>
-      </c>
-      <c r="F24" s="49"/>
-    </row>
-    <row r="25" spans="1:6" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A25" s="45" t="s">
-        <v>401</v>
-      </c>
-      <c r="B25" s="45"/>
-      <c r="C25" s="45"/>
-      <c r="D25" s="45"/>
-      <c r="E25" s="45"/>
-      <c r="F25" s="45"/>
-    </row>
-    <row r="26" spans="1:6" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A26" s="50">
-        <v>18</v>
-      </c>
-      <c r="B26" s="51" t="s">
-        <v>402</v>
-      </c>
-      <c r="C26" s="51" t="s">
-        <v>403</v>
-      </c>
-      <c r="D26" s="51" t="s">
-        <v>404</v>
-      </c>
-      <c r="E26" s="48" t="s">
-        <v>437</v>
-      </c>
-      <c r="F26" s="51"/>
-    </row>
-    <row r="27" spans="1:6" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A27" s="48">
-        <v>19</v>
-      </c>
-      <c r="B27" s="49" t="s">
-        <v>402</v>
-      </c>
-      <c r="C27" s="49" t="s">
-        <v>405</v>
-      </c>
-      <c r="D27" s="49" t="s">
-        <v>406</v>
-      </c>
-      <c r="E27" s="48" t="s">
-        <v>437</v>
-      </c>
-      <c r="F27" s="49"/>
-    </row>
-    <row r="28" spans="1:6" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A28" s="50">
-        <v>20</v>
-      </c>
-      <c r="B28" s="51" t="s">
-        <v>402</v>
-      </c>
-      <c r="C28" s="51" t="s">
-        <v>407</v>
-      </c>
-      <c r="D28" s="51" t="s">
-        <v>408</v>
-      </c>
-      <c r="E28" s="48" t="s">
-        <v>437</v>
-      </c>
-      <c r="F28" s="51"/>
-    </row>
-    <row r="29" spans="1:6" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A29" s="48">
-        <v>21</v>
-      </c>
-      <c r="B29" s="49" t="s">
-        <v>402</v>
-      </c>
-      <c r="C29" s="49" t="s">
-        <v>409</v>
-      </c>
-      <c r="D29" s="49" t="s">
+      <c r="B33" s="32" t="s">
         <v>410</v>
       </c>
-      <c r="E29" s="48" t="s">
-        <v>437</v>
-      </c>
-      <c r="F29" s="49"/>
-    </row>
-    <row r="30" spans="1:6" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A30" s="45" t="s">
-        <v>411</v>
-      </c>
-      <c r="B30" s="45"/>
-      <c r="C30" s="45"/>
-      <c r="D30" s="45"/>
-      <c r="E30" s="45"/>
-      <c r="F30" s="45"/>
-    </row>
-    <row r="31" spans="1:6" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A31" s="50">
-        <v>22</v>
-      </c>
-      <c r="B31" s="51" t="s">
-        <v>412</v>
-      </c>
-      <c r="C31" s="51" t="s">
-        <v>413</v>
-      </c>
-      <c r="D31" s="51" t="s">
-        <v>414</v>
-      </c>
-      <c r="E31" s="48" t="s">
-        <v>437</v>
-      </c>
-      <c r="F31" s="51"/>
-    </row>
-    <row r="32" spans="1:6" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A32" s="48">
-        <v>23</v>
-      </c>
-      <c r="B32" s="49" t="s">
-        <v>412</v>
-      </c>
-      <c r="C32" s="49" t="s">
+      <c r="C33" s="32" t="s">
         <v>415</v>
       </c>
-      <c r="D32" s="49" t="s">
+      <c r="D33" s="32" t="s">
         <v>416</v>
       </c>
-      <c r="E32" s="48" t="s">
-        <v>437</v>
-      </c>
-      <c r="F32" s="49"/>
-    </row>
-    <row r="33" spans="1:6" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A33" s="50">
-        <v>24</v>
-      </c>
-      <c r="B33" s="51" t="s">
-        <v>412</v>
-      </c>
-      <c r="C33" s="51" t="s">
+      <c r="E33" s="29" t="s">
+        <v>435</v>
+      </c>
+      <c r="F33" s="32"/>
+    </row>
+    <row r="34" spans="1:6" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A34" s="48" t="s">
         <v>417</v>
       </c>
-      <c r="D33" s="51" t="s">
+      <c r="B34" s="48"/>
+      <c r="C34" s="48"/>
+      <c r="D34" s="48"/>
+      <c r="E34" s="48"/>
+      <c r="F34" s="48"/>
+    </row>
+    <row r="35" spans="1:6" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A35" s="29">
+        <v>25</v>
+      </c>
+      <c r="B35" s="30" t="s">
         <v>418</v>
       </c>
-      <c r="E33" s="48" t="s">
-        <v>437</v>
-      </c>
-      <c r="F33" s="51"/>
-    </row>
-    <row r="34" spans="1:6" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A34" s="45" t="s">
+      <c r="C35" s="30" t="s">
         <v>419</v>
       </c>
-      <c r="B34" s="45"/>
-      <c r="C34" s="45"/>
-      <c r="D34" s="45"/>
-      <c r="E34" s="45"/>
-      <c r="F34" s="45"/>
-    </row>
-    <row r="35" spans="1:6" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A35" s="48">
-        <v>25</v>
-      </c>
-      <c r="B35" s="49" t="s">
+      <c r="D35" s="30" t="s">
         <v>420</v>
       </c>
-      <c r="C35" s="49" t="s">
+      <c r="E35" s="29" t="s">
+        <v>435</v>
+      </c>
+      <c r="F35" s="30"/>
+    </row>
+    <row r="36" spans="1:6" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A36" s="31">
+        <v>26</v>
+      </c>
+      <c r="B36" s="32" t="s">
+        <v>418</v>
+      </c>
+      <c r="C36" s="32" t="s">
         <v>421</v>
       </c>
-      <c r="D35" s="49" t="s">
+      <c r="D36" s="32" t="s">
         <v>422</v>
       </c>
-      <c r="E35" s="48" t="s">
-        <v>437</v>
-      </c>
-      <c r="F35" s="49"/>
-    </row>
-    <row r="36" spans="1:6" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A36" s="50">
-        <v>26</v>
-      </c>
-      <c r="B36" s="51" t="s">
-        <v>420</v>
-      </c>
-      <c r="C36" s="51" t="s">
+      <c r="E36" s="29" t="s">
+        <v>435</v>
+      </c>
+      <c r="F36" s="32"/>
+    </row>
+    <row r="37" spans="1:6" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A37" s="29">
+        <v>27</v>
+      </c>
+      <c r="B37" s="30" t="s">
+        <v>418</v>
+      </c>
+      <c r="C37" s="30" t="s">
         <v>423</v>
       </c>
-      <c r="D36" s="51" t="s">
+      <c r="D37" s="30" t="s">
         <v>424</v>
       </c>
-      <c r="E36" s="48" t="s">
-        <v>437</v>
-      </c>
-      <c r="F36" s="51"/>
-    </row>
-    <row r="37" spans="1:6" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A37" s="48">
-        <v>27</v>
-      </c>
-      <c r="B37" s="49" t="s">
-        <v>420</v>
-      </c>
-      <c r="C37" s="49" t="s">
+      <c r="E37" s="29" t="s">
+        <v>435</v>
+      </c>
+      <c r="F37" s="30"/>
+    </row>
+    <row r="38" spans="1:6" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A38" s="48" t="s">
         <v>425</v>
       </c>
-      <c r="D37" s="49" t="s">
+      <c r="B38" s="48"/>
+      <c r="C38" s="48"/>
+      <c r="D38" s="48"/>
+      <c r="E38" s="48"/>
+      <c r="F38" s="48"/>
+    </row>
+    <row r="39" spans="1:6" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A39" s="31">
+        <v>28</v>
+      </c>
+      <c r="B39" s="32" t="s">
         <v>426</v>
       </c>
-      <c r="E37" s="48" t="s">
-        <v>437</v>
-      </c>
-      <c r="F37" s="49"/>
-    </row>
-    <row r="38" spans="1:6" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A38" s="45" t="s">
+      <c r="C39" s="32" t="s">
         <v>427</v>
       </c>
-      <c r="B38" s="45"/>
-      <c r="C38" s="45"/>
-      <c r="D38" s="45"/>
-      <c r="E38" s="45"/>
-      <c r="F38" s="45"/>
-    </row>
-    <row r="39" spans="1:6" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A39" s="50">
-        <v>28</v>
-      </c>
-      <c r="B39" s="51" t="s">
+      <c r="D39" s="32" t="s">
         <v>428</v>
       </c>
-      <c r="C39" s="51" t="s">
+      <c r="E39" s="29" t="s">
+        <v>435</v>
+      </c>
+      <c r="F39" s="32"/>
+    </row>
+    <row r="40" spans="1:6" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A40" s="29">
+        <v>29</v>
+      </c>
+      <c r="B40" s="30" t="s">
+        <v>426</v>
+      </c>
+      <c r="C40" s="30" t="s">
         <v>429</v>
       </c>
-      <c r="D39" s="51" t="s">
+      <c r="D40" s="30" t="s">
         <v>430</v>
       </c>
-      <c r="E39" s="48" t="s">
-        <v>437</v>
-      </c>
-      <c r="F39" s="51"/>
-    </row>
-    <row r="40" spans="1:6" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A40" s="48">
-        <v>29</v>
-      </c>
-      <c r="B40" s="49" t="s">
-        <v>428</v>
-      </c>
-      <c r="C40" s="49" t="s">
+      <c r="E40" s="29" t="s">
+        <v>435</v>
+      </c>
+      <c r="F40" s="30"/>
+    </row>
+    <row r="41" spans="1:6" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A41" s="31">
+        <v>30</v>
+      </c>
+      <c r="B41" s="32" t="s">
+        <v>426</v>
+      </c>
+      <c r="C41" s="32" t="s">
+        <v>140</v>
+      </c>
+      <c r="D41" s="32" t="s">
         <v>431</v>
       </c>
-      <c r="D40" s="49" t="s">
-        <v>432</v>
-      </c>
-      <c r="E40" s="48" t="s">
-        <v>437</v>
-      </c>
-      <c r="F40" s="49"/>
-    </row>
-    <row r="41" spans="1:6" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A41" s="50">
-        <v>30</v>
-      </c>
-      <c r="B41" s="51" t="s">
-        <v>428</v>
-      </c>
-      <c r="C41" s="51" t="s">
-        <v>142</v>
-      </c>
-      <c r="D41" s="51" t="s">
-        <v>433</v>
-      </c>
-      <c r="E41" s="48" t="s">
-        <v>437</v>
-      </c>
-      <c r="F41" s="51"/>
+      <c r="E41" s="29" t="s">
+        <v>435</v>
+      </c>
+      <c r="F41" s="32"/>
     </row>
     <row r="43" spans="1:6" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A43" s="40" t="s">
-        <v>131</v>
-      </c>
-      <c r="B43" s="40"/>
-      <c r="C43" s="40"/>
-      <c r="D43" s="40"/>
-      <c r="E43" s="40"/>
-      <c r="F43" s="40"/>
+      <c r="A43" s="49" t="s">
+        <v>129</v>
+      </c>
+      <c r="B43" s="49"/>
+      <c r="C43" s="49"/>
+      <c r="D43" s="49"/>
+      <c r="E43" s="49"/>
+      <c r="F43" s="49"/>
     </row>
     <row r="44" spans="1:6" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A44" s="37" t="s">
-        <v>132</v>
-      </c>
-      <c r="B44" s="37"/>
-      <c r="C44" s="37"/>
-      <c r="D44" s="38">
+      <c r="A44" s="45" t="s">
+        <v>130</v>
+      </c>
+      <c r="B44" s="45"/>
+      <c r="C44" s="45"/>
+      <c r="D44" s="46">
         <f>COUNTA(E4:E41)</f>
         <v>30</v>
       </c>
-      <c r="E44" s="38"/>
-      <c r="F44" s="38"/>
+      <c r="E44" s="46"/>
+      <c r="F44" s="46"/>
     </row>
     <row r="45" spans="1:6" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A45" s="37" t="s">
-        <v>133</v>
-      </c>
-      <c r="B45" s="37"/>
-      <c r="C45" s="37"/>
-      <c r="D45" s="38">
+      <c r="A45" s="45" t="s">
+        <v>131</v>
+      </c>
+      <c r="B45" s="45"/>
+      <c r="C45" s="45"/>
+      <c r="D45" s="46">
         <f>COUNTIF(E4:E41,"PASS")</f>
         <v>0</v>
       </c>
-      <c r="E45" s="38"/>
-      <c r="F45" s="38"/>
+      <c r="E45" s="46"/>
+      <c r="F45" s="46"/>
     </row>
     <row r="46" spans="1:6" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A46" s="37" t="s">
-        <v>134</v>
-      </c>
-      <c r="B46" s="37"/>
-      <c r="C46" s="37"/>
-      <c r="D46" s="38">
+      <c r="A46" s="45" t="s">
+        <v>132</v>
+      </c>
+      <c r="B46" s="45"/>
+      <c r="C46" s="45"/>
+      <c r="D46" s="46">
         <f>COUNTIF(E4:E41,"FAIL")</f>
         <v>0</v>
       </c>
-      <c r="E46" s="38"/>
-      <c r="F46" s="38"/>
+      <c r="E46" s="46"/>
+      <c r="F46" s="46"/>
     </row>
     <row r="47" spans="1:6" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A47" s="37" t="s">
-        <v>135</v>
-      </c>
-      <c r="B47" s="37"/>
-      <c r="C47" s="37"/>
-      <c r="D47" s="38">
+      <c r="A47" s="45" t="s">
+        <v>133</v>
+      </c>
+      <c r="B47" s="45"/>
+      <c r="C47" s="45"/>
+      <c r="D47" s="46">
         <f>COUNTIF(E4:E41,"N/A")</f>
         <v>30</v>
       </c>
-      <c r="E47" s="38"/>
-      <c r="F47" s="38"/>
+      <c r="E47" s="46"/>
+      <c r="F47" s="46"/>
     </row>
     <row r="48" spans="1:6" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A48" s="37" t="s">
-        <v>136</v>
-      </c>
-      <c r="B48" s="37"/>
-      <c r="C48" s="37"/>
-      <c r="D48" s="39">
+      <c r="A48" s="45" t="s">
+        <v>134</v>
+      </c>
+      <c r="B48" s="45"/>
+      <c r="C48" s="45"/>
+      <c r="D48" s="47">
         <f>IFERROR(COUNTIF(E4:E41,"PASS")/(COUNTA(E4:E41)-COUNTIF(E4:E41,"N/A")),0)</f>
         <v>0</v>
       </c>
-      <c r="E48" s="39"/>
-      <c r="F48" s="39"/>
+      <c r="E48" s="47"/>
+      <c r="F48" s="47"/>
     </row>
     <row r="49" spans="1:6" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A49" s="37" t="s">
-        <v>137</v>
-      </c>
-      <c r="B49" s="37"/>
-      <c r="C49" s="37"/>
-      <c r="D49" s="38" t="str">
+      <c r="A49" s="45" t="s">
+        <v>135</v>
+      </c>
+      <c r="B49" s="45"/>
+      <c r="C49" s="45"/>
+      <c r="D49" s="46" t="str">
         <f>IF(IFERROR(COUNTIF(E4:E41,"PASS")/(COUNTA(E4:E41)-COUNTIF(E4:E41,"N/A")),0)=1,"ĐẠT YÊU CẦU","CHƯA ĐẠT - CẦN XỬ LÝ")</f>
         <v>CHƯA ĐẠT - CẦN XỬ LÝ</v>
       </c>
-      <c r="E49" s="38"/>
-      <c r="F49" s="38"/>
+      <c r="E49" s="46"/>
+      <c r="F49" s="46"/>
     </row>
     <row r="51" spans="1:6" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A51" s="37" t="s">
-        <v>138</v>
-      </c>
-      <c r="B51" s="37"/>
-      <c r="C51" s="37"/>
-      <c r="D51" s="37" t="s">
-        <v>139</v>
-      </c>
-      <c r="E51" s="37"/>
-      <c r="F51" s="37"/>
+      <c r="A51" s="45" t="s">
+        <v>136</v>
+      </c>
+      <c r="B51" s="45"/>
+      <c r="C51" s="45"/>
+      <c r="D51" s="45" t="s">
+        <v>137</v>
+      </c>
+      <c r="E51" s="45"/>
+      <c r="F51" s="45"/>
     </row>
   </sheetData>
   <mergeCells count="25">

--- a/templates_excel/03_Checklist_Hệ thống mới.xlsx
+++ b/templates_excel/03_Checklist_Hệ thống mới.xlsx
@@ -5,10 +5,10 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://vngms-my.sharepoint.com/personal/quantc_vng_com_vn/Documents/quantc/Task-and-planing/Kiểm soát hardening IT Infrastructure với chuẩn hóa cấu hình/Hardening_System_Application/templates_excel/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://vngms-my.sharepoint.com/personal/quantc_vng_com_vn/Documents/quantc/Task-and-planing/Kiểm soát hardening IT Infrastructure với chuẩn hóa cấu hình/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="91" documentId="13_ncr:1_{24055782-F57B-453E-8ABC-F4DD773A7A72}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{48B3BC85-D83F-4BE4-A5A6-2D59A281ADEB}"/>
+  <xr:revisionPtr revIDLastSave="90" documentId="13_ncr:1_{24055782-F57B-453E-8ABC-F4DD773A7A72}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{7270943C-9F72-4F14-93A8-E181AC866449}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="500" firstSheet="1" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -42,7 +42,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="913" uniqueCount="476">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="923" uniqueCount="482">
   <si>
     <t>CHECKLIST KIỂM SOÁT HARDENING CHO HỆ THỐNG SETUP MỚI</t>
   </si>
@@ -134,9 +134,6 @@
     <t>ip -br a</t>
   </si>
   <si>
-    <t>Default Gateway và DNS được cấu hình chính xác.</t>
-  </si>
-  <si>
     <t>ip route; nslookup google.com</t>
   </si>
   <si>
@@ -164,9 +161,15 @@
     <t>grep PermitRootLogin /etc/ssh/sshd_config</t>
   </si>
   <si>
+    <t>MaxAuthTries = 5</t>
+  </si>
+  <si>
     <t>grep MaxAuthTries /etc/ssh/sshd_config</t>
   </si>
   <si>
+    <t>LoginGraceTime = 20</t>
+  </si>
+  <si>
     <t>grep LoginGraceTime /etc/ssh/sshd_config</t>
   </si>
   <si>
@@ -1466,10 +1469,26 @@
     <t>stat -c '%n %a %U:%G' /etc/security/opasswd 2&gt;/dev/null || echo 'file not exist'</t>
   </si>
   <si>
-    <t>MaxAuthTries = 4</t>
-  </si>
-  <si>
-    <t>LoginGraceTime = 60</t>
+    <t>Tạo một file cấu hình cấu hình cho /run/sshd</t>
+  </si>
+  <si>
+    <t>sudo echo "d /run/sshd 0755 root root -" | sudo tee /etc/tmpfiles.d/sshd.conf</t>
+  </si>
+  <si>
+    <t>Cập nhật kernal</t>
+  </si>
+  <si>
+    <t>Default Gateway (.1) và DNS (10.31.100.30) được cấu hình chính xác.</t>
+  </si>
+  <si>
+    <t>sudo apt update &amp;&amp; sudo apt upgrade -y ( lưu ý: Override local changes to /etc/pam.d/common-*? [yes/no] no)</t>
+  </si>
+  <si>
+    <t>Kiểm tra sshd (Nếu lỗi chạy tiếp lệnh thứ 2)</t>
+  </si>
+  <si>
+    <t>sudo sshd -t
+systemd-tmpfiles --create /etc/tmpfiles.d/sshd.conf</t>
   </si>
 </sst>
 </file>
@@ -1587,7 +1606,6 @@
     <font>
       <sz val="10"/>
       <name val="Arial"/>
-      <family val="2"/>
     </font>
   </fonts>
   <fills count="8">
@@ -1704,7 +1722,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="52">
+  <cellXfs count="53">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1" applyAlignment="1">
@@ -1788,6 +1806,9 @@
     <xf numFmtId="0" fontId="13" fillId="7" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
@@ -1797,11 +1818,23 @@
     <xf numFmtId="0" fontId="4" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="3" fontId="5" fillId="2" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="3" fontId="6" fillId="3" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="3" fontId="2" fillId="5" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="3" fontId="8" fillId="2" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="3" fontId="6" fillId="3" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="3" fontId="2" fillId="6" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="164" fontId="2" fillId="6" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -1809,20 +1842,17 @@
     <xf numFmtId="3" fontId="6" fillId="3" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="3" fontId="2" fillId="6" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
+    <xf numFmtId="0" fontId="9" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="3" fontId="2" fillId="5" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
+    <xf numFmtId="0" fontId="10" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="3" fontId="8" fillId="2" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
+    <xf numFmtId="0" fontId="12" fillId="5" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="3" fontId="5" fillId="2" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="3" fontId="6" fillId="3" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
+    <xf numFmtId="0" fontId="11" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="10" fillId="3" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
@@ -1833,16 +1863,7 @@
     <xf numFmtId="9" fontId="12" fillId="6" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="5" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="3" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -2303,118 +2324,113 @@
   <sheetData>
     <row r="1" spans="2:4" ht="18.75" customHeight="1" x14ac:dyDescent="0.3"/>
     <row r="2" spans="2:4" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B2" s="36" t="s">
+      <c r="B2" s="33" t="s">
         <v>0</v>
       </c>
-      <c r="C2" s="36"/>
-      <c r="D2" s="36"/>
+      <c r="C2" s="33"/>
+      <c r="D2" s="33"/>
     </row>
     <row r="3" spans="2:4" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B3" s="36"/>
-      <c r="C3" s="36"/>
-      <c r="D3" s="36"/>
+      <c r="B3" s="33"/>
+      <c r="C3" s="33"/>
+      <c r="D3" s="33"/>
     </row>
     <row r="4" spans="2:4" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B4" s="36"/>
-      <c r="C4" s="36"/>
-      <c r="D4" s="36"/>
+      <c r="B4" s="33"/>
+      <c r="C4" s="33"/>
+      <c r="D4" s="33"/>
     </row>
     <row r="5" spans="2:4" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B5" s="36"/>
-      <c r="C5" s="36"/>
-      <c r="D5" s="36"/>
+      <c r="B5" s="33"/>
+      <c r="C5" s="33"/>
+      <c r="D5" s="33"/>
     </row>
     <row r="6" spans="2:4" ht="18.75" customHeight="1" x14ac:dyDescent="0.3"/>
     <row r="7" spans="2:4" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B7" s="3" t="s">
         <v>1</v>
       </c>
-      <c r="C7" s="33" t="s">
+      <c r="C7" s="34" t="s">
         <v>2</v>
       </c>
-      <c r="D7" s="33"/>
+      <c r="D7" s="34"/>
     </row>
     <row r="8" spans="2:4" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B8" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="C8" s="33" t="s">
+      <c r="C8" s="34" t="s">
         <v>4</v>
       </c>
-      <c r="D8" s="33"/>
+      <c r="D8" s="34"/>
     </row>
     <row r="9" spans="2:4" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B9" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="C9" s="33" t="s">
+      <c r="C9" s="34" t="s">
         <v>6</v>
       </c>
-      <c r="D9" s="33"/>
+      <c r="D9" s="34"/>
     </row>
     <row r="10" spans="2:4" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B10" s="3" t="s">
         <v>7</v>
       </c>
-      <c r="C10" s="33" t="s">
+      <c r="C10" s="34" t="s">
         <v>8</v>
       </c>
-      <c r="D10" s="33"/>
+      <c r="D10" s="34"/>
     </row>
     <row r="11" spans="2:4" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B11" s="35" t="s">
-        <v>432</v>
-      </c>
-      <c r="C11" s="35"/>
-      <c r="D11" s="35"/>
+      <c r="B11" s="36" t="s">
+        <v>433</v>
+      </c>
+      <c r="C11" s="36"/>
+      <c r="D11" s="36"/>
     </row>
     <row r="12" spans="2:4" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B12" s="33" t="s">
+      <c r="B12" s="34" t="s">
         <v>9</v>
       </c>
-      <c r="C12" s="33"/>
-      <c r="D12" s="33"/>
+      <c r="C12" s="34"/>
+      <c r="D12" s="34"/>
     </row>
     <row r="13" spans="2:4" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B13" s="33" t="s">
+      <c r="B13" s="34" t="s">
         <v>10</v>
       </c>
-      <c r="C13" s="33"/>
-      <c r="D13" s="33"/>
+      <c r="C13" s="34"/>
+      <c r="D13" s="34"/>
     </row>
     <row r="14" spans="2:4" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B14" s="33" t="s">
+      <c r="B14" s="34" t="s">
         <v>11</v>
       </c>
-      <c r="C14" s="33"/>
-      <c r="D14" s="33"/>
+      <c r="C14" s="34"/>
+      <c r="D14" s="34"/>
     </row>
     <row r="15" spans="2:4" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B15" s="33" t="s">
+      <c r="B15" s="34" t="s">
         <v>12</v>
       </c>
-      <c r="C15" s="33"/>
-      <c r="D15" s="33"/>
+      <c r="C15" s="34"/>
+      <c r="D15" s="34"/>
     </row>
     <row r="16" spans="2:4" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B16" s="33" t="s">
+      <c r="B16" s="34" t="s">
         <v>13</v>
       </c>
-      <c r="C16" s="33"/>
-      <c r="D16" s="33"/>
+      <c r="C16" s="34"/>
+      <c r="D16" s="34"/>
     </row>
     <row r="17" spans="2:4" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B17" s="34"/>
-      <c r="C17" s="34"/>
-      <c r="D17" s="34"/>
+      <c r="B17" s="35"/>
+      <c r="C17" s="35"/>
+      <c r="D17" s="35"/>
     </row>
   </sheetData>
   <mergeCells count="12">
-    <mergeCell ref="B2:D5"/>
-    <mergeCell ref="C7:D7"/>
-    <mergeCell ref="C8:D8"/>
-    <mergeCell ref="C9:D9"/>
-    <mergeCell ref="C10:D10"/>
     <mergeCell ref="B16:D16"/>
     <mergeCell ref="B17:D17"/>
     <mergeCell ref="B11:D11"/>
@@ -2422,6 +2438,11 @@
     <mergeCell ref="B13:D13"/>
     <mergeCell ref="B14:D14"/>
     <mergeCell ref="B15:D15"/>
+    <mergeCell ref="B2:D5"/>
+    <mergeCell ref="C7:D7"/>
+    <mergeCell ref="C8:D8"/>
+    <mergeCell ref="C9:D9"/>
+    <mergeCell ref="C10:D10"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.511811023622047" footer="0.511811023622047"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300"/>
@@ -2430,33 +2451,33 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
-  <dimension ref="A1:F85"/>
+  <dimension ref="A1:F88"/>
   <sheetFormatPr defaultColWidth="8.6640625" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="5" style="4" customWidth="1"/>
     <col min="2" max="2" width="22" style="1" customWidth="1"/>
     <col min="3" max="3" width="72.109375" style="1" customWidth="1"/>
-    <col min="4" max="4" width="77.21875" style="5" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="92.88671875" style="5" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="26" style="1" customWidth="1"/>
     <col min="6" max="6" width="30" style="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:6" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A1" s="43" t="s">
+      <c r="A1" s="37" t="s">
         <v>14</v>
       </c>
-      <c r="B1" s="43"/>
-      <c r="C1" s="43"/>
-      <c r="D1" s="43"/>
-      <c r="E1" s="43"/>
-      <c r="F1" s="43"/>
+      <c r="B1" s="37"/>
+      <c r="C1" s="37"/>
+      <c r="D1" s="37"/>
+      <c r="E1" s="37"/>
+      <c r="F1" s="37"/>
     </row>
     <row r="2" spans="1:6" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A2" s="44" t="s">
+      <c r="A2" s="38" t="s">
         <v>15</v>
       </c>
-      <c r="B2" s="44"/>
-      <c r="C2" s="44"/>
+      <c r="B2" s="38"/>
+      <c r="C2" s="38"/>
       <c r="D2" s="8" t="s">
         <v>16</v>
       </c>
@@ -2488,1354 +2509,1398 @@
       </c>
     </row>
     <row r="4" spans="1:6" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A4" s="41" t="s">
-        <v>433</v>
-      </c>
-      <c r="B4" s="41"/>
-      <c r="C4" s="41"/>
-      <c r="D4" s="41"/>
-      <c r="E4" s="41"/>
-      <c r="F4" s="41"/>
+      <c r="A4" s="39" t="s">
+        <v>434</v>
+      </c>
+      <c r="B4" s="39"/>
+      <c r="C4" s="39"/>
+      <c r="D4" s="39"/>
+      <c r="E4" s="39"/>
+      <c r="F4" s="39"/>
     </row>
     <row r="5" spans="1:6" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A5" s="15">
-        <v>1</v>
-      </c>
+      <c r="A5" s="15"/>
       <c r="B5" s="16" t="s">
         <v>25</v>
       </c>
       <c r="C5" s="16" t="s">
-        <v>26</v>
+        <v>477</v>
       </c>
       <c r="D5" s="17" t="s">
-        <v>27</v>
-      </c>
-      <c r="E5" s="18" t="s">
-        <v>435</v>
-      </c>
+        <v>479</v>
+      </c>
+      <c r="E5" s="18"/>
       <c r="F5" s="16"/>
     </row>
     <row r="6" spans="1:6" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A6" s="15">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="B6" s="16" t="s">
         <v>25</v>
       </c>
       <c r="C6" s="16" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="D6" s="17" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="E6" s="18" t="s">
-        <v>435</v>
+        <v>436</v>
       </c>
       <c r="F6" s="16"/>
     </row>
     <row r="7" spans="1:6" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A7" s="15">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="B7" s="16" t="s">
         <v>25</v>
       </c>
       <c r="C7" s="16" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="D7" s="17" t="s">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="E7" s="18" t="s">
-        <v>435</v>
+        <v>436</v>
       </c>
       <c r="F7" s="16"/>
     </row>
     <row r="8" spans="1:6" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A8" s="15">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="B8" s="16" t="s">
         <v>25</v>
       </c>
       <c r="C8" s="16" t="s">
-        <v>32</v>
+        <v>478</v>
       </c>
       <c r="D8" s="17" t="s">
-        <v>33</v>
+        <v>30</v>
       </c>
       <c r="E8" s="18" t="s">
-        <v>435</v>
+        <v>436</v>
       </c>
       <c r="F8" s="16"/>
     </row>
     <row r="9" spans="1:6" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A9" s="15">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="B9" s="16" t="s">
         <v>25</v>
       </c>
       <c r="C9" s="16" t="s">
+        <v>31</v>
+      </c>
+      <c r="D9" s="17" t="s">
+        <v>32</v>
+      </c>
+      <c r="E9" s="18" t="s">
+        <v>436</v>
+      </c>
+      <c r="F9" s="16"/>
+    </row>
+    <row r="10" spans="1:6" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A10" s="15">
+        <v>5</v>
+      </c>
+      <c r="B10" s="16" t="s">
+        <v>25</v>
+      </c>
+      <c r="C10" s="16" t="s">
+        <v>33</v>
+      </c>
+      <c r="D10" s="17" t="s">
         <v>34</v>
       </c>
-      <c r="D9" s="17" t="s">
+      <c r="E10" s="18" t="s">
+        <v>436</v>
+      </c>
+      <c r="F10" s="16"/>
+    </row>
+    <row r="11" spans="1:6" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A11" s="39" t="s">
         <v>35</v>
       </c>
-      <c r="E9" s="18" t="s">
-        <v>435</v>
-      </c>
-      <c r="F9" s="16"/>
-    </row>
-    <row r="10" spans="1:6" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A10" s="41" t="s">
+      <c r="B11" s="39"/>
+      <c r="C11" s="39"/>
+      <c r="D11" s="39"/>
+      <c r="E11" s="39"/>
+      <c r="F11" s="39"/>
+    </row>
+    <row r="12" spans="1:6" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A12" s="15"/>
+      <c r="B12" s="16" t="s">
         <v>36</v>
       </c>
-      <c r="B10" s="41"/>
-      <c r="C10" s="41"/>
-      <c r="D10" s="41"/>
-      <c r="E10" s="41"/>
-      <c r="F10" s="41"/>
-    </row>
-    <row r="11" spans="1:6" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A11" s="15">
-        <v>6</v>
-      </c>
-      <c r="B11" s="16" t="s">
-        <v>37</v>
-      </c>
-      <c r="C11" s="16" t="s">
-        <v>38</v>
-      </c>
-      <c r="D11" s="17" t="s">
-        <v>39</v>
-      </c>
-      <c r="E11" s="18" t="s">
-        <v>435</v>
-      </c>
-      <c r="F11" s="16"/>
-    </row>
-    <row r="12" spans="1:6" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A12" s="15">
-        <v>7</v>
-      </c>
-      <c r="B12" s="16" t="s">
-        <v>37</v>
-      </c>
       <c r="C12" s="16" t="s">
-        <v>474</v>
+        <v>475</v>
       </c>
       <c r="D12" s="17" t="s">
-        <v>40</v>
+        <v>476</v>
       </c>
       <c r="E12" s="18" t="s">
-        <v>435</v>
+        <v>436</v>
       </c>
       <c r="F12" s="16"/>
     </row>
-    <row r="13" spans="1:6" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A13" s="15">
-        <v>8</v>
-      </c>
+    <row r="13" spans="1:6" ht="26.4" x14ac:dyDescent="0.3">
+      <c r="A13" s="15"/>
       <c r="B13" s="16" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="C13" s="16" t="s">
-        <v>475</v>
-      </c>
-      <c r="D13" s="17" t="s">
-        <v>41</v>
-      </c>
-      <c r="E13" s="18" t="s">
-        <v>435</v>
-      </c>
+        <v>480</v>
+      </c>
+      <c r="D13" s="52" t="s">
+        <v>481</v>
+      </c>
+      <c r="E13" s="18"/>
       <c r="F13" s="16"/>
     </row>
     <row r="14" spans="1:6" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A14" s="15">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="B14" s="16" t="s">
+        <v>36</v>
+      </c>
+      <c r="C14" s="16" t="s">
         <v>37</v>
       </c>
-      <c r="C14" s="16" t="s">
-        <v>42</v>
-      </c>
       <c r="D14" s="17" t="s">
-        <v>43</v>
+        <v>38</v>
       </c>
       <c r="E14" s="18" t="s">
-        <v>435</v>
+        <v>436</v>
       </c>
       <c r="F14" s="16"/>
     </row>
     <row r="15" spans="1:6" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A15" s="15">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="B15" s="16" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="C15" s="16" t="s">
-        <v>44</v>
+        <v>39</v>
       </c>
       <c r="D15" s="17" t="s">
-        <v>45</v>
+        <v>40</v>
       </c>
       <c r="E15" s="18" t="s">
-        <v>435</v>
+        <v>436</v>
       </c>
       <c r="F15" s="16"/>
     </row>
     <row r="16" spans="1:6" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A16" s="15">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="B16" s="16" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="C16" s="16" t="s">
-        <v>46</v>
+        <v>41</v>
       </c>
       <c r="D16" s="17" t="s">
-        <v>47</v>
+        <v>42</v>
       </c>
       <c r="E16" s="18" t="s">
-        <v>435</v>
+        <v>436</v>
       </c>
       <c r="F16" s="16"/>
     </row>
-    <row r="17" spans="1:6" ht="26.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:6" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A17" s="15">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="B17" s="16" t="s">
-        <v>37</v>
-      </c>
-      <c r="C17" s="19" t="s">
-        <v>48</v>
+        <v>36</v>
+      </c>
+      <c r="C17" s="16" t="s">
+        <v>43</v>
       </c>
       <c r="D17" s="17" t="s">
-        <v>49</v>
+        <v>44</v>
       </c>
       <c r="E17" s="18" t="s">
-        <v>435</v>
+        <v>436</v>
       </c>
       <c r="F17" s="16"/>
     </row>
     <row r="18" spans="1:6" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A18" s="15">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="B18" s="16" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="C18" s="16" t="s">
-        <v>50</v>
+        <v>45</v>
       </c>
       <c r="D18" s="17" t="s">
-        <v>51</v>
+        <v>46</v>
       </c>
       <c r="E18" s="18" t="s">
-        <v>435</v>
+        <v>436</v>
       </c>
       <c r="F18" s="16"/>
     </row>
     <row r="19" spans="1:6" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A19" s="15">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="B19" s="16" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="C19" s="16" t="s">
-        <v>437</v>
+        <v>47</v>
       </c>
       <c r="D19" s="17" t="s">
-        <v>444</v>
+        <v>48</v>
       </c>
       <c r="E19" s="18" t="s">
-        <v>435</v>
+        <v>436</v>
       </c>
       <c r="F19" s="16"/>
     </row>
-    <row r="20" spans="1:6" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:6" ht="26.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A20" s="15">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="B20" s="16" t="s">
-        <v>37</v>
-      </c>
-      <c r="C20" s="16" t="s">
-        <v>438</v>
+        <v>36</v>
+      </c>
+      <c r="C20" s="19" t="s">
+        <v>49</v>
       </c>
       <c r="D20" s="17" t="s">
-        <v>445</v>
+        <v>50</v>
       </c>
       <c r="E20" s="18" t="s">
-        <v>435</v>
+        <v>436</v>
       </c>
       <c r="F20" s="16"/>
     </row>
     <row r="21" spans="1:6" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A21" s="15">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="B21" s="16" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="C21" s="16" t="s">
-        <v>439</v>
+        <v>438</v>
       </c>
       <c r="D21" s="17" t="s">
-        <v>446</v>
+        <v>445</v>
       </c>
       <c r="E21" s="18" t="s">
-        <v>435</v>
+        <v>436</v>
       </c>
       <c r="F21" s="16"/>
     </row>
     <row r="22" spans="1:6" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A22" s="15">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="B22" s="16" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="C22" s="16" t="s">
-        <v>440</v>
+        <v>439</v>
       </c>
       <c r="D22" s="17" t="s">
-        <v>447</v>
+        <v>446</v>
       </c>
       <c r="E22" s="18" t="s">
-        <v>435</v>
+        <v>436</v>
       </c>
       <c r="F22" s="16"/>
     </row>
     <row r="23" spans="1:6" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A23" s="15">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="B23" s="16" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="C23" s="16" t="s">
-        <v>441</v>
+        <v>440</v>
       </c>
       <c r="D23" s="17" t="s">
-        <v>448</v>
+        <v>447</v>
       </c>
       <c r="E23" s="18" t="s">
-        <v>435</v>
+        <v>436</v>
       </c>
       <c r="F23" s="16"/>
     </row>
     <row r="24" spans="1:6" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A24" s="15">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="B24" s="16" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="C24" s="16" t="s">
-        <v>442</v>
+        <v>441</v>
       </c>
       <c r="D24" s="17" t="s">
-        <v>449</v>
+        <v>448</v>
       </c>
       <c r="E24" s="18" t="s">
-        <v>435</v>
+        <v>436</v>
       </c>
       <c r="F24" s="16"/>
     </row>
     <row r="25" spans="1:6" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A25" s="15">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="B25" s="16" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="C25" s="16" t="s">
+        <v>442</v>
+      </c>
+      <c r="D25" s="17" t="s">
+        <v>449</v>
+      </c>
+      <c r="E25" s="18" t="s">
+        <v>436</v>
+      </c>
+      <c r="F25" s="16"/>
+    </row>
+    <row r="26" spans="1:6" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A26" s="15">
+        <v>19</v>
+      </c>
+      <c r="B26" s="16" t="s">
+        <v>36</v>
+      </c>
+      <c r="C26" s="16" t="s">
         <v>443</v>
       </c>
-      <c r="D25" s="17" t="s">
+      <c r="D26" s="17" t="s">
         <v>450</v>
       </c>
-      <c r="E25" s="18" t="s">
-        <v>435</v>
-      </c>
-      <c r="F25" s="16"/>
-    </row>
-    <row r="26" spans="1:6" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A26" s="41" t="s">
-        <v>52</v>
-      </c>
-      <c r="B26" s="41"/>
-      <c r="C26" s="41"/>
-      <c r="D26" s="41"/>
-      <c r="E26" s="41"/>
-      <c r="F26" s="41"/>
+      <c r="E26" s="18" t="s">
+        <v>436</v>
+      </c>
+      <c r="F26" s="16"/>
     </row>
     <row r="27" spans="1:6" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A27" s="15">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="B27" s="16" t="s">
-        <v>53</v>
+        <v>36</v>
       </c>
       <c r="C27" s="16" t="s">
-        <v>54</v>
+        <v>444</v>
       </c>
       <c r="D27" s="17" t="s">
-        <v>55</v>
+        <v>451</v>
       </c>
       <c r="E27" s="18" t="s">
-        <v>435</v>
+        <v>436</v>
       </c>
       <c r="F27" s="16"/>
     </row>
     <row r="28" spans="1:6" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A28" s="15">
-        <v>22</v>
+        <v>13</v>
       </c>
       <c r="B28" s="16" t="s">
+        <v>36</v>
+      </c>
+      <c r="C28" s="16" t="s">
+        <v>51</v>
+      </c>
+      <c r="D28" s="17" t="s">
+        <v>52</v>
+      </c>
+      <c r="E28" s="18" t="s">
+        <v>436</v>
+      </c>
+      <c r="F28" s="16"/>
+    </row>
+    <row r="29" spans="1:6" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A29" s="39" t="s">
         <v>53</v>
       </c>
-      <c r="C28" s="16" t="s">
-        <v>56</v>
-      </c>
-      <c r="D28" s="17" t="s">
-        <v>57</v>
-      </c>
-      <c r="E28" s="18" t="s">
-        <v>435</v>
-      </c>
-      <c r="F28" s="16"/>
-    </row>
-    <row r="29" spans="1:6" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A29" s="15">
-        <v>23</v>
-      </c>
-      <c r="B29" s="16" t="s">
-        <v>53</v>
-      </c>
-      <c r="C29" s="16" t="s">
-        <v>58</v>
-      </c>
-      <c r="D29" s="17" t="s">
-        <v>59</v>
-      </c>
-      <c r="E29" s="18" t="s">
-        <v>435</v>
-      </c>
-      <c r="F29" s="16"/>
+      <c r="B29" s="39"/>
+      <c r="C29" s="39"/>
+      <c r="D29" s="39"/>
+      <c r="E29" s="39"/>
+      <c r="F29" s="39"/>
     </row>
     <row r="30" spans="1:6" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A30" s="15">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="B30" s="16" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="C30" s="16" t="s">
-        <v>60</v>
+        <v>55</v>
       </c>
       <c r="D30" s="17" t="s">
-        <v>61</v>
+        <v>56</v>
       </c>
       <c r="E30" s="18" t="s">
-        <v>435</v>
+        <v>436</v>
       </c>
       <c r="F30" s="16"/>
     </row>
     <row r="31" spans="1:6" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A31" s="15">
-        <v>25</v>
+        <v>22</v>
       </c>
       <c r="B31" s="16" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="C31" s="16" t="s">
-        <v>451</v>
+        <v>57</v>
       </c>
       <c r="D31" s="17" t="s">
-        <v>454</v>
+        <v>58</v>
       </c>
       <c r="E31" s="18" t="s">
-        <v>435</v>
+        <v>436</v>
       </c>
       <c r="F31" s="16"/>
     </row>
     <row r="32" spans="1:6" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A32" s="15">
-        <v>26</v>
+        <v>23</v>
       </c>
       <c r="B32" s="16" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="C32" s="16" t="s">
-        <v>452</v>
+        <v>59</v>
       </c>
       <c r="D32" s="17" t="s">
-        <v>455</v>
+        <v>60</v>
       </c>
       <c r="E32" s="18" t="s">
-        <v>435</v>
+        <v>436</v>
       </c>
       <c r="F32" s="16"/>
     </row>
     <row r="33" spans="1:6" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A33" s="15">
-        <v>27</v>
+        <v>24</v>
       </c>
       <c r="B33" s="16" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="C33" s="16" t="s">
-        <v>453</v>
+        <v>61</v>
       </c>
       <c r="D33" s="17" t="s">
-        <v>456</v>
+        <v>62</v>
       </c>
       <c r="E33" s="18" t="s">
-        <v>435</v>
+        <v>436</v>
       </c>
       <c r="F33" s="16"/>
     </row>
     <row r="34" spans="1:6" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A34" s="41" t="s">
-        <v>434</v>
-      </c>
-      <c r="B34" s="41"/>
-      <c r="C34" s="41"/>
-      <c r="D34" s="41"/>
-      <c r="E34" s="41"/>
-      <c r="F34" s="41"/>
+      <c r="A34" s="15">
+        <v>25</v>
+      </c>
+      <c r="B34" s="16" t="s">
+        <v>54</v>
+      </c>
+      <c r="C34" s="16" t="s">
+        <v>452</v>
+      </c>
+      <c r="D34" s="17" t="s">
+        <v>455</v>
+      </c>
+      <c r="E34" s="18" t="s">
+        <v>436</v>
+      </c>
+      <c r="F34" s="16"/>
     </row>
     <row r="35" spans="1:6" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A35" s="15">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="B35" s="16" t="s">
-        <v>62</v>
+        <v>54</v>
       </c>
       <c r="C35" s="16" t="s">
-        <v>63</v>
+        <v>453</v>
       </c>
       <c r="D35" s="17" t="s">
-        <v>64</v>
+        <v>456</v>
       </c>
       <c r="E35" s="18" t="s">
-        <v>435</v>
+        <v>436</v>
       </c>
       <c r="F35" s="16"/>
     </row>
     <row r="36" spans="1:6" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A36" s="15">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="B36" s="16" t="s">
-        <v>62</v>
+        <v>54</v>
       </c>
       <c r="C36" s="16" t="s">
-        <v>65</v>
+        <v>454</v>
       </c>
       <c r="D36" s="17" t="s">
-        <v>66</v>
+        <v>457</v>
       </c>
       <c r="E36" s="18" t="s">
+        <v>436</v>
+      </c>
+      <c r="F36" s="16"/>
+    </row>
+    <row r="37" spans="1:6" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A37" s="39" t="s">
         <v>435</v>
       </c>
-      <c r="F36" s="16"/>
-    </row>
-    <row r="37" spans="1:6" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A37" s="15">
-        <v>30</v>
-      </c>
-      <c r="B37" s="16" t="s">
-        <v>62</v>
-      </c>
-      <c r="C37" s="16" t="s">
-        <v>67</v>
-      </c>
-      <c r="D37" s="17" t="s">
-        <v>68</v>
-      </c>
-      <c r="E37" s="18" t="s">
-        <v>435</v>
-      </c>
-      <c r="F37" s="16"/>
+      <c r="B37" s="39"/>
+      <c r="C37" s="39"/>
+      <c r="D37" s="39"/>
+      <c r="E37" s="39"/>
+      <c r="F37" s="39"/>
     </row>
     <row r="38" spans="1:6" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A38" s="15">
-        <v>31</v>
+        <v>28</v>
       </c>
       <c r="B38" s="16" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="C38" s="16" t="s">
-        <v>69</v>
+        <v>64</v>
       </c>
       <c r="D38" s="17" t="s">
-        <v>436</v>
+        <v>65</v>
       </c>
       <c r="E38" s="18" t="s">
-        <v>435</v>
+        <v>436</v>
       </c>
       <c r="F38" s="16"/>
     </row>
     <row r="39" spans="1:6" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A39" s="41" t="s">
-        <v>70</v>
-      </c>
-      <c r="B39" s="41"/>
-      <c r="C39" s="41"/>
-      <c r="D39" s="41"/>
-      <c r="E39" s="41"/>
-      <c r="F39" s="41"/>
+      <c r="A39" s="15">
+        <v>29</v>
+      </c>
+      <c r="B39" s="16" t="s">
+        <v>63</v>
+      </c>
+      <c r="C39" s="16" t="s">
+        <v>66</v>
+      </c>
+      <c r="D39" s="17" t="s">
+        <v>67</v>
+      </c>
+      <c r="E39" s="18" t="s">
+        <v>436</v>
+      </c>
+      <c r="F39" s="16"/>
     </row>
     <row r="40" spans="1:6" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A40" s="15">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="B40" s="16" t="s">
-        <v>71</v>
+        <v>63</v>
       </c>
       <c r="C40" s="16" t="s">
-        <v>72</v>
+        <v>68</v>
       </c>
       <c r="D40" s="17" t="s">
-        <v>73</v>
+        <v>69</v>
       </c>
       <c r="E40" s="18" t="s">
-        <v>435</v>
+        <v>436</v>
       </c>
       <c r="F40" s="16"/>
     </row>
     <row r="41" spans="1:6" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A41" s="15">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="B41" s="16" t="s">
+        <v>63</v>
+      </c>
+      <c r="C41" s="16" t="s">
+        <v>70</v>
+      </c>
+      <c r="D41" s="17" t="s">
+        <v>437</v>
+      </c>
+      <c r="E41" s="18" t="s">
+        <v>436</v>
+      </c>
+      <c r="F41" s="16"/>
+    </row>
+    <row r="42" spans="1:6" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A42" s="39" t="s">
         <v>71</v>
       </c>
-      <c r="C41" s="16" t="s">
-        <v>74</v>
-      </c>
-      <c r="D41" s="17" t="s">
-        <v>75</v>
-      </c>
-      <c r="E41" s="18" t="s">
-        <v>435</v>
-      </c>
-      <c r="F41" s="16"/>
-    </row>
-    <row r="42" spans="1:6" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A42" s="15">
-        <v>34</v>
-      </c>
-      <c r="B42" s="16" t="s">
-        <v>71</v>
-      </c>
-      <c r="C42" s="16" t="s">
-        <v>76</v>
-      </c>
-      <c r="D42" s="17" t="s">
-        <v>77</v>
-      </c>
-      <c r="E42" s="18" t="s">
-        <v>435</v>
-      </c>
-      <c r="F42" s="16"/>
+      <c r="B42" s="39"/>
+      <c r="C42" s="39"/>
+      <c r="D42" s="39"/>
+      <c r="E42" s="39"/>
+      <c r="F42" s="39"/>
     </row>
     <row r="43" spans="1:6" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A43" s="15">
-        <v>35</v>
+        <v>32</v>
       </c>
       <c r="B43" s="16" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="C43" s="16" t="s">
-        <v>78</v>
+        <v>73</v>
       </c>
       <c r="D43" s="17" t="s">
-        <v>79</v>
+        <v>74</v>
       </c>
       <c r="E43" s="18" t="s">
-        <v>435</v>
+        <v>436</v>
       </c>
       <c r="F43" s="16"/>
     </row>
     <row r="44" spans="1:6" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A44" s="15">
-        <v>36</v>
+        <v>33</v>
       </c>
       <c r="B44" s="16" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="C44" s="16" t="s">
-        <v>80</v>
+        <v>75</v>
       </c>
       <c r="D44" s="17" t="s">
-        <v>81</v>
+        <v>76</v>
       </c>
       <c r="E44" s="18" t="s">
-        <v>435</v>
+        <v>436</v>
       </c>
       <c r="F44" s="16"/>
     </row>
     <row r="45" spans="1:6" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A45" s="15">
-        <v>37</v>
+        <v>34</v>
       </c>
       <c r="B45" s="16" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="C45" s="16" t="s">
-        <v>82</v>
+        <v>77</v>
       </c>
       <c r="D45" s="17" t="s">
-        <v>83</v>
+        <v>78</v>
       </c>
       <c r="E45" s="18" t="s">
-        <v>435</v>
+        <v>436</v>
       </c>
       <c r="F45" s="16"/>
     </row>
     <row r="46" spans="1:6" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A46" s="41" t="s">
-        <v>84</v>
-      </c>
-      <c r="B46" s="41"/>
-      <c r="C46" s="41"/>
-      <c r="D46" s="41"/>
-      <c r="E46" s="41"/>
-      <c r="F46" s="41"/>
+      <c r="A46" s="15">
+        <v>35</v>
+      </c>
+      <c r="B46" s="16" t="s">
+        <v>72</v>
+      </c>
+      <c r="C46" s="16" t="s">
+        <v>79</v>
+      </c>
+      <c r="D46" s="17" t="s">
+        <v>80</v>
+      </c>
+      <c r="E46" s="18" t="s">
+        <v>436</v>
+      </c>
+      <c r="F46" s="16"/>
     </row>
     <row r="47" spans="1:6" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A47" s="15">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="B47" s="16" t="s">
-        <v>85</v>
+        <v>72</v>
       </c>
       <c r="C47" s="16" t="s">
-        <v>86</v>
+        <v>81</v>
       </c>
       <c r="D47" s="17" t="s">
-        <v>87</v>
+        <v>82</v>
       </c>
       <c r="E47" s="18" t="s">
-        <v>435</v>
+        <v>436</v>
       </c>
       <c r="F47" s="16"/>
     </row>
     <row r="48" spans="1:6" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A48" s="15">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="B48" s="16" t="s">
+        <v>72</v>
+      </c>
+      <c r="C48" s="16" t="s">
+        <v>83</v>
+      </c>
+      <c r="D48" s="17" t="s">
+        <v>84</v>
+      </c>
+      <c r="E48" s="18" t="s">
+        <v>436</v>
+      </c>
+      <c r="F48" s="16"/>
+    </row>
+    <row r="49" spans="1:6" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A49" s="39" t="s">
         <v>85</v>
       </c>
-      <c r="C48" s="16" t="s">
+      <c r="B49" s="39"/>
+      <c r="C49" s="39"/>
+      <c r="D49" s="39"/>
+      <c r="E49" s="39"/>
+      <c r="F49" s="39"/>
+    </row>
+    <row r="50" spans="1:6" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A50" s="15">
+        <v>38</v>
+      </c>
+      <c r="B50" s="16" t="s">
+        <v>86</v>
+      </c>
+      <c r="C50" s="16" t="s">
+        <v>87</v>
+      </c>
+      <c r="D50" s="17" t="s">
         <v>88</v>
       </c>
-      <c r="D48" s="17" t="s">
-        <v>89</v>
-      </c>
-      <c r="E48" s="18" t="s">
-        <v>435</v>
-      </c>
-      <c r="F48" s="16"/>
-    </row>
-    <row r="49" spans="1:6" ht="26.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A49" s="15">
-        <v>40</v>
-      </c>
-      <c r="B49" s="16" t="s">
-        <v>85</v>
-      </c>
-      <c r="C49" s="19" t="s">
-        <v>90</v>
-      </c>
-      <c r="D49" s="17" t="s">
-        <v>91</v>
-      </c>
-      <c r="E49" s="18" t="s">
-        <v>435</v>
-      </c>
-      <c r="F49" s="16"/>
-    </row>
-    <row r="50" spans="1:6" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A50" s="41" t="s">
-        <v>92</v>
-      </c>
-      <c r="B50" s="41"/>
-      <c r="C50" s="41"/>
-      <c r="D50" s="41"/>
-      <c r="E50" s="41"/>
-      <c r="F50" s="41"/>
+      <c r="E50" s="18" t="s">
+        <v>436</v>
+      </c>
+      <c r="F50" s="16"/>
     </row>
     <row r="51" spans="1:6" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A51" s="15">
+        <v>39</v>
+      </c>
+      <c r="B51" s="16" t="s">
+        <v>86</v>
+      </c>
+      <c r="C51" s="16" t="s">
+        <v>89</v>
+      </c>
+      <c r="D51" s="17" t="s">
+        <v>90</v>
+      </c>
+      <c r="E51" s="18" t="s">
+        <v>436</v>
+      </c>
+      <c r="F51" s="16"/>
+    </row>
+    <row r="52" spans="1:6" ht="26.25" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A52" s="15">
+        <v>40</v>
+      </c>
+      <c r="B52" s="16" t="s">
+        <v>86</v>
+      </c>
+      <c r="C52" s="19" t="s">
+        <v>91</v>
+      </c>
+      <c r="D52" s="17" t="s">
+        <v>92</v>
+      </c>
+      <c r="E52" s="18" t="s">
+        <v>436</v>
+      </c>
+      <c r="F52" s="16"/>
+    </row>
+    <row r="53" spans="1:6" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A53" s="39" t="s">
+        <v>93</v>
+      </c>
+      <c r="B53" s="39"/>
+      <c r="C53" s="39"/>
+      <c r="D53" s="39"/>
+      <c r="E53" s="39"/>
+      <c r="F53" s="39"/>
+    </row>
+    <row r="54" spans="1:6" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A54" s="15">
         <v>41</v>
       </c>
-      <c r="B51" s="16" t="s">
-        <v>93</v>
-      </c>
-      <c r="C51" s="16" t="s">
+      <c r="B54" s="16" t="s">
         <v>94</v>
       </c>
-      <c r="D51" s="17" t="s">
+      <c r="C54" s="16" t="s">
         <v>95</v>
       </c>
-      <c r="E51" s="18" t="s">
-        <v>435</v>
-      </c>
-      <c r="F51" s="16"/>
-    </row>
-    <row r="52" spans="1:6" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A52" s="15">
-        <v>42</v>
-      </c>
-      <c r="B52" s="16" t="s">
-        <v>93</v>
-      </c>
-      <c r="C52" s="16" t="s">
+      <c r="D54" s="17" t="s">
         <v>96</v>
       </c>
-      <c r="D52" s="17" t="s">
-        <v>97</v>
-      </c>
-      <c r="E52" s="18" t="s">
-        <v>435</v>
-      </c>
-      <c r="F52" s="16"/>
-    </row>
-    <row r="53" spans="1:6" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A53" s="15">
-        <v>43</v>
-      </c>
-      <c r="B53" s="16" t="s">
-        <v>93</v>
-      </c>
-      <c r="C53" s="16" t="s">
-        <v>98</v>
-      </c>
-      <c r="D53" s="17" t="s">
-        <v>99</v>
-      </c>
-      <c r="E53" s="18" t="s">
-        <v>435</v>
-      </c>
-      <c r="F53" s="16"/>
-    </row>
-    <row r="54" spans="1:6" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A54" s="41" t="s">
-        <v>100</v>
-      </c>
-      <c r="B54" s="41"/>
-      <c r="C54" s="41"/>
-      <c r="D54" s="41"/>
-      <c r="E54" s="41"/>
-      <c r="F54" s="41"/>
+      <c r="E54" s="18" t="s">
+        <v>436</v>
+      </c>
+      <c r="F54" s="16"/>
     </row>
     <row r="55" spans="1:6" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A55" s="15">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="B55" s="16" t="s">
-        <v>101</v>
+        <v>94</v>
       </c>
       <c r="C55" s="16" t="s">
-        <v>102</v>
+        <v>97</v>
       </c>
       <c r="D55" s="17" t="s">
-        <v>103</v>
+        <v>98</v>
       </c>
       <c r="E55" s="18" t="s">
-        <v>435</v>
+        <v>436</v>
       </c>
       <c r="F55" s="16"/>
     </row>
     <row r="56" spans="1:6" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A56" s="15">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="B56" s="16" t="s">
+        <v>94</v>
+      </c>
+      <c r="C56" s="16" t="s">
+        <v>99</v>
+      </c>
+      <c r="D56" s="17" t="s">
+        <v>100</v>
+      </c>
+      <c r="E56" s="18" t="s">
+        <v>436</v>
+      </c>
+      <c r="F56" s="16"/>
+    </row>
+    <row r="57" spans="1:6" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A57" s="39" t="s">
         <v>101</v>
       </c>
-      <c r="C56" s="16" t="s">
-        <v>104</v>
-      </c>
-      <c r="D56" s="17" t="s">
-        <v>105</v>
-      </c>
-      <c r="E56" s="18" t="s">
-        <v>435</v>
-      </c>
-      <c r="F56" s="16"/>
-    </row>
-    <row r="57" spans="1:6" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A57" s="15">
-        <v>46</v>
-      </c>
-      <c r="B57" s="16" t="s">
-        <v>101</v>
-      </c>
-      <c r="C57" s="16" t="s">
-        <v>106</v>
-      </c>
-      <c r="D57" s="17" t="s">
-        <v>107</v>
-      </c>
-      <c r="E57" s="18" t="s">
-        <v>435</v>
-      </c>
-      <c r="F57" s="16"/>
+      <c r="B57" s="39"/>
+      <c r="C57" s="39"/>
+      <c r="D57" s="39"/>
+      <c r="E57" s="39"/>
+      <c r="F57" s="39"/>
     </row>
     <row r="58" spans="1:6" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A58" s="15">
-        <v>47</v>
+        <v>44</v>
       </c>
       <c r="B58" s="16" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="C58" s="16" t="s">
-        <v>108</v>
+        <v>103</v>
       </c>
       <c r="D58" s="17" t="s">
-        <v>109</v>
+        <v>104</v>
       </c>
       <c r="E58" s="18" t="s">
-        <v>435</v>
+        <v>436</v>
       </c>
       <c r="F58" s="16"/>
     </row>
     <row r="59" spans="1:6" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A59" s="15">
-        <v>48</v>
+        <v>45</v>
       </c>
       <c r="B59" s="16" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="C59" s="16" t="s">
-        <v>110</v>
+        <v>105</v>
       </c>
       <c r="D59" s="17" t="s">
-        <v>111</v>
+        <v>106</v>
       </c>
       <c r="E59" s="18" t="s">
-        <v>435</v>
+        <v>436</v>
       </c>
       <c r="F59" s="16"/>
     </row>
     <row r="60" spans="1:6" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A60" s="41" t="s">
-        <v>112</v>
-      </c>
-      <c r="B60" s="41"/>
-      <c r="C60" s="41"/>
-      <c r="D60" s="41"/>
-      <c r="E60" s="41"/>
-      <c r="F60" s="41"/>
+      <c r="A60" s="15">
+        <v>46</v>
+      </c>
+      <c r="B60" s="16" t="s">
+        <v>102</v>
+      </c>
+      <c r="C60" s="16" t="s">
+        <v>107</v>
+      </c>
+      <c r="D60" s="17" t="s">
+        <v>108</v>
+      </c>
+      <c r="E60" s="18" t="s">
+        <v>436</v>
+      </c>
+      <c r="F60" s="16"/>
     </row>
     <row r="61" spans="1:6" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A61" s="15">
-        <v>49</v>
+        <v>47</v>
       </c>
       <c r="B61" s="16" t="s">
-        <v>113</v>
+        <v>102</v>
       </c>
       <c r="C61" s="16" t="s">
-        <v>114</v>
+        <v>109</v>
       </c>
       <c r="D61" s="17" t="s">
-        <v>115</v>
+        <v>110</v>
       </c>
       <c r="E61" s="18" t="s">
-        <v>435</v>
+        <v>436</v>
       </c>
       <c r="F61" s="16"/>
     </row>
     <row r="62" spans="1:6" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A62" s="15">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="B62" s="16" t="s">
+        <v>102</v>
+      </c>
+      <c r="C62" s="16" t="s">
+        <v>111</v>
+      </c>
+      <c r="D62" s="17" t="s">
+        <v>112</v>
+      </c>
+      <c r="E62" s="18" t="s">
+        <v>436</v>
+      </c>
+      <c r="F62" s="16"/>
+    </row>
+    <row r="63" spans="1:6" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A63" s="39" t="s">
         <v>113</v>
       </c>
-      <c r="C62" s="16" t="s">
+      <c r="B63" s="39"/>
+      <c r="C63" s="39"/>
+      <c r="D63" s="39"/>
+      <c r="E63" s="39"/>
+      <c r="F63" s="39"/>
+    </row>
+    <row r="64" spans="1:6" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A64" s="15">
+        <v>49</v>
+      </c>
+      <c r="B64" s="16" t="s">
+        <v>114</v>
+      </c>
+      <c r="C64" s="16" t="s">
+        <v>115</v>
+      </c>
+      <c r="D64" s="17" t="s">
         <v>116</v>
       </c>
-      <c r="D62" s="17" t="s">
-        <v>117</v>
-      </c>
-      <c r="E62" s="18" t="s">
-        <v>435</v>
-      </c>
-      <c r="F62" s="16"/>
-    </row>
-    <row r="63" spans="1:6" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A63" s="15">
-        <v>51</v>
-      </c>
-      <c r="B63" s="16" t="s">
-        <v>113</v>
-      </c>
-      <c r="C63" s="16" t="s">
-        <v>118</v>
-      </c>
-      <c r="D63" s="17" t="s">
-        <v>119</v>
-      </c>
-      <c r="E63" s="18" t="s">
-        <v>435</v>
-      </c>
-      <c r="F63" s="16"/>
-    </row>
-    <row r="64" spans="1:6" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A64" s="41" t="s">
-        <v>457</v>
-      </c>
-      <c r="B64" s="41"/>
-      <c r="C64" s="41"/>
-      <c r="D64" s="41"/>
-      <c r="E64" s="41"/>
-      <c r="F64" s="41"/>
+      <c r="E64" s="18" t="s">
+        <v>436</v>
+      </c>
+      <c r="F64" s="16"/>
     </row>
     <row r="65" spans="1:6" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A65" s="15">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="B65" s="16" t="s">
-        <v>120</v>
+        <v>114</v>
       </c>
       <c r="C65" s="16" t="s">
-        <v>121</v>
+        <v>117</v>
       </c>
       <c r="D65" s="17" t="s">
-        <v>122</v>
+        <v>118</v>
       </c>
       <c r="E65" s="18" t="s">
-        <v>435</v>
+        <v>436</v>
       </c>
       <c r="F65" s="16"/>
     </row>
     <row r="66" spans="1:6" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A66" s="15">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="B66" s="16" t="s">
+        <v>114</v>
+      </c>
+      <c r="C66" s="16" t="s">
+        <v>119</v>
+      </c>
+      <c r="D66" s="17" t="s">
         <v>120</v>
       </c>
-      <c r="C66" s="16" t="s">
-        <v>123</v>
-      </c>
-      <c r="D66" s="17" t="s">
-        <v>124</v>
-      </c>
       <c r="E66" s="18" t="s">
-        <v>435</v>
+        <v>436</v>
       </c>
       <c r="F66" s="16"/>
     </row>
     <row r="67" spans="1:6" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A67" s="15">
-        <v>54</v>
-      </c>
-      <c r="B67" s="16" t="s">
-        <v>120</v>
-      </c>
-      <c r="C67" s="16" t="s">
-        <v>125</v>
-      </c>
-      <c r="D67" s="17" t="s">
-        <v>126</v>
-      </c>
-      <c r="E67" s="18" t="s">
-        <v>435</v>
-      </c>
-      <c r="F67" s="16"/>
+      <c r="A67" s="39" t="s">
+        <v>458</v>
+      </c>
+      <c r="B67" s="39"/>
+      <c r="C67" s="39"/>
+      <c r="D67" s="39"/>
+      <c r="E67" s="39"/>
+      <c r="F67" s="39"/>
     </row>
     <row r="68" spans="1:6" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A68" s="15">
+        <v>52</v>
+      </c>
+      <c r="B68" s="16" t="s">
+        <v>121</v>
+      </c>
+      <c r="C68" s="16" t="s">
+        <v>122</v>
+      </c>
+      <c r="D68" s="17" t="s">
+        <v>123</v>
+      </c>
+      <c r="E68" s="18" t="s">
+        <v>436</v>
+      </c>
+      <c r="F68" s="16"/>
+    </row>
+    <row r="69" spans="1:6" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A69" s="15">
+        <v>53</v>
+      </c>
+      <c r="B69" s="16" t="s">
+        <v>121</v>
+      </c>
+      <c r="C69" s="16" t="s">
+        <v>124</v>
+      </c>
+      <c r="D69" s="17" t="s">
+        <v>125</v>
+      </c>
+      <c r="E69" s="18" t="s">
+        <v>436</v>
+      </c>
+      <c r="F69" s="16"/>
+    </row>
+    <row r="70" spans="1:6" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A70" s="15">
+        <v>54</v>
+      </c>
+      <c r="B70" s="16" t="s">
+        <v>121</v>
+      </c>
+      <c r="C70" s="16" t="s">
+        <v>126</v>
+      </c>
+      <c r="D70" s="17" t="s">
+        <v>127</v>
+      </c>
+      <c r="E70" s="18" t="s">
+        <v>436</v>
+      </c>
+      <c r="F70" s="16"/>
+    </row>
+    <row r="71" spans="1:6" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A71" s="15">
         <v>55</v>
       </c>
-      <c r="B68" s="16" t="s">
-        <v>120</v>
-      </c>
-      <c r="C68" s="16" t="s">
-        <v>127</v>
-      </c>
-      <c r="D68" s="17" t="s">
+      <c r="B71" s="16" t="s">
+        <v>121</v>
+      </c>
+      <c r="C71" s="16" t="s">
         <v>128</v>
       </c>
-      <c r="E68" s="18" t="s">
-        <v>435</v>
-      </c>
-      <c r="F68" s="16"/>
-    </row>
-    <row r="69" spans="1:6" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A69" s="41" t="s">
+      <c r="D71" s="17" t="s">
+        <v>129</v>
+      </c>
+      <c r="E71" s="18" t="s">
+        <v>436</v>
+      </c>
+      <c r="F71" s="16"/>
+    </row>
+    <row r="72" spans="1:6" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A72" s="39" t="s">
+        <v>466</v>
+      </c>
+      <c r="B72" s="39"/>
+      <c r="C72" s="39"/>
+      <c r="D72" s="39"/>
+      <c r="E72" s="39"/>
+      <c r="F72" s="39"/>
+    </row>
+    <row r="73" spans="1:6" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A73" s="21">
+        <v>56</v>
+      </c>
+      <c r="B73" s="22" t="s">
+        <v>459</v>
+      </c>
+      <c r="C73" s="22" t="s">
+        <v>460</v>
+      </c>
+      <c r="D73" s="23" t="s">
+        <v>463</v>
+      </c>
+      <c r="E73" s="18" t="s">
+        <v>436</v>
+      </c>
+      <c r="F73" s="22"/>
+    </row>
+    <row r="74" spans="1:6" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A74" s="21">
+        <v>57</v>
+      </c>
+      <c r="B74" s="22" t="s">
+        <v>459</v>
+      </c>
+      <c r="C74" s="22" t="s">
+        <v>461</v>
+      </c>
+      <c r="D74" s="23" t="s">
+        <v>464</v>
+      </c>
+      <c r="E74" s="18" t="s">
+        <v>436</v>
+      </c>
+      <c r="F74" s="22"/>
+    </row>
+    <row r="75" spans="1:6" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A75" s="21">
+        <v>58</v>
+      </c>
+      <c r="B75" s="22" t="s">
+        <v>459</v>
+      </c>
+      <c r="C75" s="22" t="s">
+        <v>462</v>
+      </c>
+      <c r="D75" s="23" t="s">
         <v>465</v>
       </c>
-      <c r="B69" s="41"/>
-      <c r="C69" s="41"/>
-      <c r="D69" s="41"/>
-      <c r="E69" s="41"/>
-      <c r="F69" s="41"/>
-    </row>
-    <row r="70" spans="1:6" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A70" s="21">
-        <v>56</v>
-      </c>
-      <c r="B70" s="22" t="s">
-        <v>458</v>
-      </c>
-      <c r="C70" s="22" t="s">
-        <v>459</v>
-      </c>
-      <c r="D70" s="23" t="s">
-        <v>462</v>
-      </c>
-      <c r="E70" s="18" t="s">
-        <v>435</v>
-      </c>
-      <c r="F70" s="22"/>
-    </row>
-    <row r="71" spans="1:6" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A71" s="21">
-        <v>57</v>
-      </c>
-      <c r="B71" s="22" t="s">
-        <v>458</v>
-      </c>
-      <c r="C71" s="22" t="s">
-        <v>460</v>
-      </c>
-      <c r="D71" s="23" t="s">
-        <v>463</v>
-      </c>
-      <c r="E71" s="18" t="s">
-        <v>435</v>
-      </c>
-      <c r="F71" s="22"/>
-    </row>
-    <row r="72" spans="1:6" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A72" s="21">
-        <v>58</v>
-      </c>
-      <c r="B72" s="22" t="s">
-        <v>458</v>
-      </c>
-      <c r="C72" s="22" t="s">
-        <v>461</v>
-      </c>
-      <c r="D72" s="23" t="s">
-        <v>464</v>
-      </c>
-      <c r="E72" s="18" t="s">
-        <v>435</v>
-      </c>
-      <c r="F72" s="22"/>
-    </row>
-    <row r="73" spans="1:6" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A73" s="41" t="s">
-        <v>466</v>
-      </c>
-      <c r="B73" s="41"/>
-      <c r="C73" s="41"/>
-      <c r="D73" s="41"/>
-      <c r="E73" s="41"/>
-      <c r="F73" s="41"/>
-    </row>
-    <row r="74" spans="1:6" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A74" s="20">
+      <c r="E75" s="18" t="s">
+        <v>436</v>
+      </c>
+      <c r="F75" s="22"/>
+    </row>
+    <row r="76" spans="1:6" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A76" s="39" t="s">
+        <v>467</v>
+      </c>
+      <c r="B76" s="39"/>
+      <c r="C76" s="39"/>
+      <c r="D76" s="39"/>
+      <c r="E76" s="39"/>
+      <c r="F76" s="39"/>
+    </row>
+    <row r="77" spans="1:6" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A77" s="20">
         <v>59</v>
       </c>
-      <c r="B74" s="13" t="s">
-        <v>467</v>
-      </c>
-      <c r="C74" s="24" t="s">
+      <c r="B77" s="13" t="s">
         <v>468</v>
       </c>
-      <c r="D74" s="14" t="s">
+      <c r="C77" s="24" t="s">
+        <v>469</v>
+      </c>
+      <c r="D77" s="14" t="s">
+        <v>472</v>
+      </c>
+      <c r="E77" s="18" t="s">
+        <v>436</v>
+      </c>
+      <c r="F77" s="13"/>
+    </row>
+    <row r="78" spans="1:6" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A78" s="20">
+        <v>60</v>
+      </c>
+      <c r="B78" s="13" t="s">
+        <v>468</v>
+      </c>
+      <c r="C78" s="24" t="s">
+        <v>470</v>
+      </c>
+      <c r="D78" s="14" t="s">
+        <v>473</v>
+      </c>
+      <c r="E78" s="18" t="s">
+        <v>436</v>
+      </c>
+      <c r="F78" s="13"/>
+    </row>
+    <row r="79" spans="1:6" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A79" s="20">
+        <v>61</v>
+      </c>
+      <c r="B79" s="13" t="s">
+        <v>468</v>
+      </c>
+      <c r="C79" s="24" t="s">
         <v>471</v>
       </c>
-      <c r="E74" s="18" t="s">
-        <v>435</v>
-      </c>
-      <c r="F74" s="13"/>
-    </row>
-    <row r="75" spans="1:6" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A75" s="20">
-        <v>60</v>
-      </c>
-      <c r="B75" s="13" t="s">
-        <v>467</v>
-      </c>
-      <c r="C75" s="24" t="s">
-        <v>469</v>
-      </c>
-      <c r="D75" s="14" t="s">
-        <v>472</v>
-      </c>
-      <c r="E75" s="18" t="s">
-        <v>435</v>
-      </c>
-      <c r="F75" s="13"/>
-    </row>
-    <row r="76" spans="1:6" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A76" s="20">
-        <v>61</v>
-      </c>
-      <c r="B76" s="13" t="s">
-        <v>467</v>
-      </c>
-      <c r="C76" s="24" t="s">
-        <v>470</v>
-      </c>
-      <c r="D76" s="14" t="s">
-        <v>473</v>
-      </c>
-      <c r="E76" s="18" t="s">
-        <v>435</v>
-      </c>
-      <c r="F76" s="13"/>
-    </row>
-    <row r="77" spans="1:6" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A77" s="42" t="s">
-        <v>129</v>
-      </c>
-      <c r="B77" s="42"/>
-      <c r="C77" s="42"/>
-      <c r="D77" s="42"/>
-      <c r="E77" s="42"/>
-      <c r="F77" s="42"/>
-    </row>
-    <row r="78" spans="1:6" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A78" s="37" t="s">
+      <c r="D79" s="14" t="s">
+        <v>474</v>
+      </c>
+      <c r="E79" s="18" t="s">
+        <v>436</v>
+      </c>
+      <c r="F79" s="13"/>
+    </row>
+    <row r="80" spans="1:6" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A80" s="40" t="s">
         <v>130</v>
       </c>
-      <c r="B78" s="37"/>
-      <c r="C78" s="37"/>
-      <c r="D78" s="40">
-        <f>COUNTA(E4:E76)</f>
-        <v>61</v>
-      </c>
-      <c r="E78" s="40"/>
-      <c r="F78" s="40"/>
-    </row>
-    <row r="79" spans="1:6" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A79" s="37" t="s">
-        <v>131</v>
-      </c>
-      <c r="B79" s="37"/>
-      <c r="C79" s="37"/>
-      <c r="D79" s="40">
-        <f>COUNTIF(E4:E68,"PASS")</f>
-        <v>0</v>
-      </c>
-      <c r="E79" s="40"/>
-      <c r="F79" s="40"/>
-    </row>
-    <row r="80" spans="1:6" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A80" s="37" t="s">
-        <v>132</v>
-      </c>
-      <c r="B80" s="37"/>
-      <c r="C80" s="37"/>
-      <c r="D80" s="40">
-        <f>COUNTIF(E4:E68,"FAIL")</f>
-        <v>0</v>
-      </c>
+      <c r="B80" s="40"/>
+      <c r="C80" s="40"/>
+      <c r="D80" s="40"/>
       <c r="E80" s="40"/>
       <c r="F80" s="40"/>
     </row>
     <row r="81" spans="1:6" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A81" s="37" t="s">
+      <c r="A81" s="41" t="s">
+        <v>131</v>
+      </c>
+      <c r="B81" s="41"/>
+      <c r="C81" s="41"/>
+      <c r="D81" s="42">
+        <f>COUNTA(E4:E79)</f>
+        <v>62</v>
+      </c>
+      <c r="E81" s="42"/>
+      <c r="F81" s="42"/>
+    </row>
+    <row r="82" spans="1:6" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A82" s="41" t="s">
+        <v>132</v>
+      </c>
+      <c r="B82" s="41"/>
+      <c r="C82" s="41"/>
+      <c r="D82" s="42">
+        <f>COUNTIF(E4:E71,"PASS")</f>
+        <v>0</v>
+      </c>
+      <c r="E82" s="42"/>
+      <c r="F82" s="42"/>
+    </row>
+    <row r="83" spans="1:6" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A83" s="41" t="s">
         <v>133</v>
       </c>
-      <c r="B81" s="37"/>
-      <c r="C81" s="37"/>
-      <c r="D81" s="40">
-        <f>COUNTIF(E4:E76,"N/A")</f>
-        <v>61</v>
-      </c>
-      <c r="E81" s="40"/>
-      <c r="F81" s="40"/>
-    </row>
-    <row r="82" spans="1:6" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A82" s="37" t="s">
+      <c r="B83" s="41"/>
+      <c r="C83" s="41"/>
+      <c r="D83" s="42">
+        <f>COUNTIF(E4:E71,"FAIL")</f>
+        <v>0</v>
+      </c>
+      <c r="E83" s="42"/>
+      <c r="F83" s="42"/>
+    </row>
+    <row r="84" spans="1:6" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A84" s="41" t="s">
         <v>134</v>
       </c>
-      <c r="B82" s="37"/>
-      <c r="C82" s="37"/>
-      <c r="D82" s="38">
-        <f>IFERROR(COUNTIF(E4:E68,"PASS")/(COUNTA(E4:E68)-COUNTIF(E4:E68,"N/A")),0)</f>
+      <c r="B84" s="41"/>
+      <c r="C84" s="41"/>
+      <c r="D84" s="42">
+        <f>COUNTIF(E4:E79,"N/A")</f>
+        <v>62</v>
+      </c>
+      <c r="E84" s="42"/>
+      <c r="F84" s="42"/>
+    </row>
+    <row r="85" spans="1:6" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A85" s="41" t="s">
+        <v>135</v>
+      </c>
+      <c r="B85" s="41"/>
+      <c r="C85" s="41"/>
+      <c r="D85" s="43">
+        <f>IFERROR(COUNTIF(E4:E71,"PASS")/(COUNTA(E4:E71)-COUNTIF(E4:E71,"N/A")),0)</f>
         <v>0</v>
       </c>
-      <c r="E82" s="38"/>
-      <c r="F82" s="38"/>
-    </row>
-    <row r="83" spans="1:6" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A83" s="37" t="s">
-        <v>135</v>
-      </c>
-      <c r="B83" s="37"/>
-      <c r="C83" s="37"/>
-      <c r="D83" s="38" t="str">
-        <f>IF(IFERROR(COUNTIF(E4:E68,"PASS")/(COUNTA(E4:E68)-COUNTIF(E4:E68,"N/A")),0)=1,"ĐẠT YÊU CẦU","CHƯA ĐẠT - CẦN XỬ LÝ")</f>
+      <c r="E85" s="43"/>
+      <c r="F85" s="43"/>
+    </row>
+    <row r="86" spans="1:6" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A86" s="41" t="s">
+        <v>136</v>
+      </c>
+      <c r="B86" s="41"/>
+      <c r="C86" s="41"/>
+      <c r="D86" s="43" t="str">
+        <f>IF(IFERROR(COUNTIF(E4:E71,"PASS")/(COUNTA(E4:E71)-COUNTIF(E4:E71,"N/A")),0)=1,"ĐẠT YÊU CẦU","CHƯA ĐẠT - CẦN XỬ LÝ")</f>
         <v>CHƯA ĐẠT - CẦN XỬ LÝ</v>
       </c>
-      <c r="E83" s="38"/>
-      <c r="F83" s="38"/>
-    </row>
-    <row r="84" spans="1:6" ht="18.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="85" spans="1:6" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A85" s="39" t="s">
-        <v>136</v>
-      </c>
-      <c r="B85" s="39"/>
-      <c r="C85" s="39"/>
-      <c r="D85" s="7" t="s">
+      <c r="E86" s="43"/>
+      <c r="F86" s="43"/>
+    </row>
+    <row r="87" spans="1:6" ht="18.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="88" spans="1:6" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A88" s="44" t="s">
         <v>137</v>
+      </c>
+      <c r="B88" s="44"/>
+      <c r="C88" s="44"/>
+      <c r="D88" s="7" t="s">
+        <v>138</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="28">
-    <mergeCell ref="A1:F1"/>
-    <mergeCell ref="A2:C2"/>
-    <mergeCell ref="A4:F4"/>
-    <mergeCell ref="A10:F10"/>
-    <mergeCell ref="A26:F26"/>
-    <mergeCell ref="A34:F34"/>
-    <mergeCell ref="A39:F39"/>
-    <mergeCell ref="A46:F46"/>
-    <mergeCell ref="A50:F50"/>
-    <mergeCell ref="A54:F54"/>
-    <mergeCell ref="A60:F60"/>
-    <mergeCell ref="A64:F64"/>
-    <mergeCell ref="A77:F77"/>
-    <mergeCell ref="A78:C78"/>
-    <mergeCell ref="D78:F78"/>
-    <mergeCell ref="A69:F69"/>
-    <mergeCell ref="A73:F73"/>
-    <mergeCell ref="A79:C79"/>
-    <mergeCell ref="D79:F79"/>
-    <mergeCell ref="A80:C80"/>
-    <mergeCell ref="D80:F80"/>
-    <mergeCell ref="A81:C81"/>
-    <mergeCell ref="D81:F81"/>
+    <mergeCell ref="A85:C85"/>
+    <mergeCell ref="D85:F85"/>
+    <mergeCell ref="A86:C86"/>
+    <mergeCell ref="D86:F86"/>
+    <mergeCell ref="A88:C88"/>
     <mergeCell ref="A82:C82"/>
     <mergeCell ref="D82:F82"/>
     <mergeCell ref="A83:C83"/>
     <mergeCell ref="D83:F83"/>
-    <mergeCell ref="A85:C85"/>
+    <mergeCell ref="A84:C84"/>
+    <mergeCell ref="D84:F84"/>
+    <mergeCell ref="A63:F63"/>
+    <mergeCell ref="A67:F67"/>
+    <mergeCell ref="A80:F80"/>
+    <mergeCell ref="A81:C81"/>
+    <mergeCell ref="D81:F81"/>
+    <mergeCell ref="A72:F72"/>
+    <mergeCell ref="A76:F76"/>
+    <mergeCell ref="A37:F37"/>
+    <mergeCell ref="A42:F42"/>
+    <mergeCell ref="A49:F49"/>
+    <mergeCell ref="A53:F53"/>
+    <mergeCell ref="A57:F57"/>
+    <mergeCell ref="A1:F1"/>
+    <mergeCell ref="A2:C2"/>
+    <mergeCell ref="A4:F4"/>
+    <mergeCell ref="A11:F11"/>
+    <mergeCell ref="A29:F29"/>
   </mergeCells>
-  <conditionalFormatting sqref="D83:F83">
+  <conditionalFormatting sqref="D86:F86">
     <cfRule type="cellIs" dxfId="21" priority="2" operator="equal">
       <formula>"ĐẠT YÊU CẦU"</formula>
     </cfRule>
@@ -3844,7 +3909,7 @@
     </cfRule>
   </conditionalFormatting>
   <dataValidations count="1">
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="E1 E4:E1085" xr:uid="{00000000-0002-0000-0100-000000000000}">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="E1 E4:E20 E21:E1088" xr:uid="{00000000-0002-0000-0100-000000000000}">
       <formula1>"PASS,FAIL,N/A"</formula1>
       <formula2>0</formula2>
     </dataValidation>
@@ -3868,21 +3933,21 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:6" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A1" s="50" t="s">
-        <v>138</v>
-      </c>
-      <c r="B1" s="50"/>
-      <c r="C1" s="50"/>
-      <c r="D1" s="50"/>
-      <c r="E1" s="50"/>
-      <c r="F1" s="50"/>
+      <c r="A1" s="45" t="s">
+        <v>139</v>
+      </c>
+      <c r="B1" s="45"/>
+      <c r="C1" s="45"/>
+      <c r="D1" s="45"/>
+      <c r="E1" s="45"/>
+      <c r="F1" s="45"/>
     </row>
     <row r="2" spans="1:6" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A2" s="51" t="s">
+      <c r="A2" s="46" t="s">
         <v>15</v>
       </c>
-      <c r="B2" s="51"/>
-      <c r="C2" s="51"/>
+      <c r="B2" s="46"/>
+      <c r="C2" s="46"/>
       <c r="D2" s="25" t="s">
         <v>16</v>
       </c>
@@ -3914,14 +3979,14 @@
       </c>
     </row>
     <row r="4" spans="1:6" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A4" s="48" t="s">
-        <v>139</v>
-      </c>
-      <c r="B4" s="48"/>
-      <c r="C4" s="48"/>
-      <c r="D4" s="48"/>
-      <c r="E4" s="48"/>
-      <c r="F4" s="48"/>
+      <c r="A4" s="47" t="s">
+        <v>140</v>
+      </c>
+      <c r="B4" s="47"/>
+      <c r="C4" s="47"/>
+      <c r="D4" s="47"/>
+      <c r="E4" s="47"/>
+      <c r="F4" s="47"/>
     </row>
     <row r="5" spans="1:6" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A5" s="27">
@@ -3931,13 +3996,13 @@
         <v>25</v>
       </c>
       <c r="C5" s="28" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="D5" s="28" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="E5" s="27" t="s">
-        <v>435</v>
+        <v>436</v>
       </c>
       <c r="F5" s="28"/>
     </row>
@@ -3949,13 +4014,13 @@
         <v>25</v>
       </c>
       <c r="C6" s="28" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="D6" s="28" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="E6" s="27" t="s">
-        <v>435</v>
+        <v>436</v>
       </c>
       <c r="F6" s="28"/>
     </row>
@@ -3967,13 +4032,13 @@
         <v>25</v>
       </c>
       <c r="C7" s="28" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="D7" s="28" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="E7" s="27" t="s">
-        <v>435</v>
+        <v>436</v>
       </c>
       <c r="F7" s="28"/>
     </row>
@@ -3985,13 +4050,13 @@
         <v>25</v>
       </c>
       <c r="C8" s="28" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="D8" s="28" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="E8" s="27" t="s">
-        <v>435</v>
+        <v>436</v>
       </c>
       <c r="F8" s="28"/>
     </row>
@@ -4003,13 +4068,13 @@
         <v>25</v>
       </c>
       <c r="C9" s="28" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="D9" s="28" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="E9" s="27" t="s">
-        <v>435</v>
+        <v>436</v>
       </c>
       <c r="F9" s="28"/>
     </row>
@@ -4021,41 +4086,41 @@
         <v>25</v>
       </c>
       <c r="C10" s="28" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="D10" s="28" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="E10" s="27" t="s">
-        <v>435</v>
+        <v>436</v>
       </c>
       <c r="F10" s="28"/>
     </row>
     <row r="11" spans="1:6" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A11" s="48" t="s">
-        <v>152</v>
-      </c>
-      <c r="B11" s="48"/>
-      <c r="C11" s="48"/>
-      <c r="D11" s="48"/>
-      <c r="E11" s="48"/>
-      <c r="F11" s="48"/>
+      <c r="A11" s="47" t="s">
+        <v>153</v>
+      </c>
+      <c r="B11" s="47"/>
+      <c r="C11" s="47"/>
+      <c r="D11" s="47"/>
+      <c r="E11" s="47"/>
+      <c r="F11" s="47"/>
     </row>
     <row r="12" spans="1:6" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A12" s="27">
         <v>7</v>
       </c>
       <c r="B12" s="28" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="C12" s="28" t="s">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="D12" s="28" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="E12" s="27" t="s">
-        <v>435</v>
+        <v>436</v>
       </c>
       <c r="F12" s="28"/>
     </row>
@@ -4064,16 +4129,16 @@
         <v>8</v>
       </c>
       <c r="B13" s="28" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="C13" s="28" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="D13" s="28" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="E13" s="27" t="s">
-        <v>435</v>
+        <v>436</v>
       </c>
       <c r="F13" s="28"/>
     </row>
@@ -4082,16 +4147,16 @@
         <v>9</v>
       </c>
       <c r="B14" s="28" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="C14" s="28" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="D14" s="28" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="E14" s="27" t="s">
-        <v>435</v>
+        <v>436</v>
       </c>
       <c r="F14" s="28"/>
     </row>
@@ -4100,16 +4165,16 @@
         <v>10</v>
       </c>
       <c r="B15" s="28" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="C15" s="28" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="D15" s="28" t="s">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="E15" s="27" t="s">
-        <v>435</v>
+        <v>436</v>
       </c>
       <c r="F15" s="28"/>
     </row>
@@ -4118,16 +4183,16 @@
         <v>11</v>
       </c>
       <c r="B16" s="28" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="C16" s="28" t="s">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="D16" s="28" t="s">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="E16" s="27" t="s">
-        <v>435</v>
+        <v>436</v>
       </c>
       <c r="F16" s="28"/>
     </row>
@@ -4136,44 +4201,44 @@
         <v>12</v>
       </c>
       <c r="B17" s="28" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="C17" s="28" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="D17" s="28" t="s">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="E17" s="27" t="s">
-        <v>435</v>
+        <v>436</v>
       </c>
       <c r="F17" s="28"/>
     </row>
     <row r="18" spans="1:6" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A18" s="48" t="s">
-        <v>166</v>
-      </c>
-      <c r="B18" s="48"/>
-      <c r="C18" s="48"/>
-      <c r="D18" s="48"/>
-      <c r="E18" s="48"/>
-      <c r="F18" s="48"/>
+      <c r="A18" s="47" t="s">
+        <v>167</v>
+      </c>
+      <c r="B18" s="47"/>
+      <c r="C18" s="47"/>
+      <c r="D18" s="47"/>
+      <c r="E18" s="47"/>
+      <c r="F18" s="47"/>
     </row>
     <row r="19" spans="1:6" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A19" s="27">
         <v>13</v>
       </c>
       <c r="B19" s="28" t="s">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="C19" s="28" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="D19" s="28" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="E19" s="27" t="s">
-        <v>435</v>
+        <v>436</v>
       </c>
       <c r="F19" s="28"/>
     </row>
@@ -4182,16 +4247,16 @@
         <v>14</v>
       </c>
       <c r="B20" s="28" t="s">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="C20" s="28" t="s">
+        <v>171</v>
+      </c>
+      <c r="D20" s="28" t="s">
         <v>170</v>
       </c>
-      <c r="D20" s="28" t="s">
-        <v>169</v>
-      </c>
       <c r="E20" s="27" t="s">
-        <v>435</v>
+        <v>436</v>
       </c>
       <c r="F20" s="28"/>
     </row>
@@ -4200,44 +4265,44 @@
         <v>15</v>
       </c>
       <c r="B21" s="28" t="s">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="C21" s="28" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="D21" s="28" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="E21" s="27" t="s">
-        <v>435</v>
+        <v>436</v>
       </c>
       <c r="F21" s="28"/>
     </row>
     <row r="22" spans="1:6" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A22" s="48" t="s">
-        <v>172</v>
-      </c>
-      <c r="B22" s="48"/>
-      <c r="C22" s="48"/>
-      <c r="D22" s="48"/>
-      <c r="E22" s="48"/>
-      <c r="F22" s="48"/>
+      <c r="A22" s="47" t="s">
+        <v>173</v>
+      </c>
+      <c r="B22" s="47"/>
+      <c r="C22" s="47"/>
+      <c r="D22" s="47"/>
+      <c r="E22" s="47"/>
+      <c r="F22" s="47"/>
     </row>
     <row r="23" spans="1:6" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A23" s="27">
         <v>16</v>
       </c>
       <c r="B23" s="28" t="s">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="C23" s="28" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="D23" s="28" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="E23" s="27" t="s">
-        <v>435</v>
+        <v>436</v>
       </c>
       <c r="F23" s="28"/>
     </row>
@@ -4246,16 +4311,16 @@
         <v>17</v>
       </c>
       <c r="B24" s="28" t="s">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="C24" s="28" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="D24" s="28" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="E24" s="27" t="s">
-        <v>435</v>
+        <v>436</v>
       </c>
       <c r="F24" s="28"/>
     </row>
@@ -4264,16 +4329,16 @@
         <v>18</v>
       </c>
       <c r="B25" s="28" t="s">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="C25" s="28" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="D25" s="28" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="E25" s="27" t="s">
-        <v>435</v>
+        <v>436</v>
       </c>
       <c r="F25" s="28"/>
     </row>
@@ -4282,16 +4347,16 @@
         <v>19</v>
       </c>
       <c r="B26" s="28" t="s">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="C26" s="28" t="s">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="D26" s="28" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="E26" s="27" t="s">
-        <v>435</v>
+        <v>436</v>
       </c>
       <c r="F26" s="28"/>
     </row>
@@ -4300,16 +4365,16 @@
         <v>20</v>
       </c>
       <c r="B27" s="28" t="s">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="C27" s="28" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="D27" s="28" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="E27" s="27" t="s">
-        <v>435</v>
+        <v>436</v>
       </c>
       <c r="F27" s="28"/>
     </row>
@@ -4318,16 +4383,16 @@
         <v>21</v>
       </c>
       <c r="B28" s="28" t="s">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="C28" s="28" t="s">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="D28" s="28" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="E28" s="27" t="s">
-        <v>435</v>
+        <v>436</v>
       </c>
       <c r="F28" s="28"/>
     </row>
@@ -4336,44 +4401,44 @@
         <v>22</v>
       </c>
       <c r="B29" s="28" t="s">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="C29" s="28" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="D29" s="28" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="E29" s="27" t="s">
-        <v>435</v>
+        <v>436</v>
       </c>
       <c r="F29" s="28"/>
     </row>
     <row r="30" spans="1:6" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A30" s="48" t="s">
-        <v>188</v>
-      </c>
-      <c r="B30" s="48"/>
-      <c r="C30" s="48"/>
-      <c r="D30" s="48"/>
-      <c r="E30" s="48"/>
-      <c r="F30" s="48"/>
+      <c r="A30" s="47" t="s">
+        <v>189</v>
+      </c>
+      <c r="B30" s="47"/>
+      <c r="C30" s="47"/>
+      <c r="D30" s="47"/>
+      <c r="E30" s="47"/>
+      <c r="F30" s="47"/>
     </row>
     <row r="31" spans="1:6" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A31" s="27">
         <v>23</v>
       </c>
       <c r="B31" s="28" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="C31" s="28" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="D31" s="28" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="E31" s="27" t="s">
-        <v>435</v>
+        <v>436</v>
       </c>
       <c r="F31" s="28"/>
     </row>
@@ -4382,16 +4447,16 @@
         <v>24</v>
       </c>
       <c r="B32" s="28" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="C32" s="28" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="D32" s="28" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="E32" s="27" t="s">
-        <v>435</v>
+        <v>436</v>
       </c>
       <c r="F32" s="28"/>
     </row>
@@ -4400,16 +4465,16 @@
         <v>25</v>
       </c>
       <c r="B33" s="28" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="C33" s="28" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="D33" s="28" t="s">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="E33" s="27" t="s">
-        <v>435</v>
+        <v>436</v>
       </c>
       <c r="F33" s="28"/>
     </row>
@@ -4418,44 +4483,44 @@
         <v>26</v>
       </c>
       <c r="B34" s="28" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="C34" s="28" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="D34" s="28" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="E34" s="27" t="s">
-        <v>435</v>
+        <v>436</v>
       </c>
       <c r="F34" s="28"/>
     </row>
     <row r="35" spans="1:6" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A35" s="48" t="s">
-        <v>198</v>
-      </c>
-      <c r="B35" s="48"/>
-      <c r="C35" s="48"/>
-      <c r="D35" s="48"/>
-      <c r="E35" s="48"/>
-      <c r="F35" s="48"/>
+      <c r="A35" s="47" t="s">
+        <v>199</v>
+      </c>
+      <c r="B35" s="47"/>
+      <c r="C35" s="47"/>
+      <c r="D35" s="47"/>
+      <c r="E35" s="47"/>
+      <c r="F35" s="47"/>
     </row>
     <row r="36" spans="1:6" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A36" s="27">
         <v>27</v>
       </c>
       <c r="B36" s="28" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="C36" s="28" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="D36" s="28" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="E36" s="27" t="s">
-        <v>435</v>
+        <v>436</v>
       </c>
       <c r="F36" s="28"/>
     </row>
@@ -4464,16 +4529,16 @@
         <v>28</v>
       </c>
       <c r="B37" s="28" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="C37" s="28" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="D37" s="28" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="E37" s="27" t="s">
-        <v>435</v>
+        <v>436</v>
       </c>
       <c r="F37" s="28"/>
     </row>
@@ -4482,16 +4547,16 @@
         <v>29</v>
       </c>
       <c r="B38" s="28" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="C38" s="28" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="D38" s="28" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="E38" s="27" t="s">
-        <v>435</v>
+        <v>436</v>
       </c>
       <c r="F38" s="28"/>
     </row>
@@ -4500,16 +4565,16 @@
         <v>30</v>
       </c>
       <c r="B39" s="28" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="C39" s="28" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="D39" s="28" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="E39" s="27" t="s">
-        <v>435</v>
+        <v>436</v>
       </c>
       <c r="F39" s="28"/>
     </row>
@@ -4518,16 +4583,16 @@
         <v>31</v>
       </c>
       <c r="B40" s="28" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="C40" s="28" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="D40" s="28" t="s">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="E40" s="27" t="s">
-        <v>435</v>
+        <v>436</v>
       </c>
       <c r="F40" s="28"/>
     </row>
@@ -4536,16 +4601,16 @@
         <v>32</v>
       </c>
       <c r="B41" s="28" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="C41" s="28" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="D41" s="28" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="E41" s="27" t="s">
-        <v>435</v>
+        <v>436</v>
       </c>
       <c r="F41" s="28"/>
     </row>
@@ -4554,16 +4619,16 @@
         <v>33</v>
       </c>
       <c r="B42" s="28" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="C42" s="28" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="D42" s="28" t="s">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="E42" s="27" t="s">
-        <v>435</v>
+        <v>436</v>
       </c>
       <c r="F42" s="28"/>
     </row>
@@ -4572,44 +4637,44 @@
         <v>34</v>
       </c>
       <c r="B43" s="28" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="C43" s="28" t="s">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="D43" s="28" t="s">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="E43" s="27" t="s">
-        <v>435</v>
+        <v>436</v>
       </c>
       <c r="F43" s="28"/>
     </row>
     <row r="44" spans="1:6" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A44" s="48" t="s">
-        <v>216</v>
-      </c>
-      <c r="B44" s="48"/>
-      <c r="C44" s="48"/>
-      <c r="D44" s="48"/>
-      <c r="E44" s="48"/>
-      <c r="F44" s="48"/>
+      <c r="A44" s="47" t="s">
+        <v>217</v>
+      </c>
+      <c r="B44" s="47"/>
+      <c r="C44" s="47"/>
+      <c r="D44" s="47"/>
+      <c r="E44" s="47"/>
+      <c r="F44" s="47"/>
     </row>
     <row r="45" spans="1:6" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A45" s="27">
         <v>35</v>
       </c>
       <c r="B45" s="28" t="s">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="C45" s="28" t="s">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="D45" s="28" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="E45" s="27" t="s">
-        <v>435</v>
+        <v>436</v>
       </c>
       <c r="F45" s="28"/>
     </row>
@@ -4618,16 +4683,16 @@
         <v>36</v>
       </c>
       <c r="B46" s="28" t="s">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="C46" s="28" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="D46" s="28" t="s">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="E46" s="27" t="s">
-        <v>435</v>
+        <v>436</v>
       </c>
       <c r="F46" s="28"/>
     </row>
@@ -4636,16 +4701,16 @@
         <v>37</v>
       </c>
       <c r="B47" s="28" t="s">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="C47" s="28" t="s">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="D47" s="28" t="s">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="E47" s="27" t="s">
-        <v>435</v>
+        <v>436</v>
       </c>
       <c r="F47" s="28"/>
     </row>
@@ -4654,44 +4719,44 @@
         <v>38</v>
       </c>
       <c r="B48" s="28" t="s">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="C48" s="28" t="s">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="D48" s="28" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="E48" s="27" t="s">
-        <v>435</v>
+        <v>436</v>
       </c>
       <c r="F48" s="28"/>
     </row>
     <row r="49" spans="1:6" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A49" s="48" t="s">
-        <v>225</v>
-      </c>
-      <c r="B49" s="48"/>
-      <c r="C49" s="48"/>
-      <c r="D49" s="48"/>
-      <c r="E49" s="48"/>
-      <c r="F49" s="48"/>
+      <c r="A49" s="47" t="s">
+        <v>226</v>
+      </c>
+      <c r="B49" s="47"/>
+      <c r="C49" s="47"/>
+      <c r="D49" s="47"/>
+      <c r="E49" s="47"/>
+      <c r="F49" s="47"/>
     </row>
     <row r="50" spans="1:6" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A50" s="27">
         <v>39</v>
       </c>
       <c r="B50" s="28" t="s">
-        <v>226</v>
+        <v>227</v>
       </c>
       <c r="C50" s="28" t="s">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="D50" s="28" t="s">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="E50" s="27" t="s">
-        <v>435</v>
+        <v>436</v>
       </c>
       <c r="F50" s="28"/>
     </row>
@@ -4700,44 +4765,44 @@
         <v>40</v>
       </c>
       <c r="B51" s="28" t="s">
-        <v>226</v>
+        <v>227</v>
       </c>
       <c r="C51" s="28" t="s">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="D51" s="28" t="s">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="E51" s="27" t="s">
-        <v>435</v>
+        <v>436</v>
       </c>
       <c r="F51" s="28"/>
     </row>
     <row r="52" spans="1:6" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A52" s="48" t="s">
-        <v>231</v>
-      </c>
-      <c r="B52" s="48"/>
-      <c r="C52" s="48"/>
-      <c r="D52" s="48"/>
-      <c r="E52" s="48"/>
-      <c r="F52" s="48"/>
+      <c r="A52" s="47" t="s">
+        <v>232</v>
+      </c>
+      <c r="B52" s="47"/>
+      <c r="C52" s="47"/>
+      <c r="D52" s="47"/>
+      <c r="E52" s="47"/>
+      <c r="F52" s="47"/>
     </row>
     <row r="53" spans="1:6" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A53" s="27">
         <v>41</v>
       </c>
       <c r="B53" s="28" t="s">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="C53" s="28" t="s">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="D53" s="28" t="s">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="E53" s="27" t="s">
-        <v>435</v>
+        <v>436</v>
       </c>
       <c r="F53" s="28"/>
     </row>
@@ -4746,137 +4811,121 @@
         <v>42</v>
       </c>
       <c r="B54" s="28" t="s">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="C54" s="28" t="s">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c r="D54" s="28" t="s">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c r="E54" s="27" t="s">
-        <v>435</v>
+        <v>436</v>
       </c>
       <c r="F54" s="28"/>
     </row>
     <row r="56" spans="1:6" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A56" s="49" t="s">
-        <v>129</v>
-      </c>
-      <c r="B56" s="49"/>
-      <c r="C56" s="49"/>
-      <c r="D56" s="49"/>
-      <c r="E56" s="49"/>
-      <c r="F56" s="49"/>
+      <c r="A56" s="48" t="s">
+        <v>130</v>
+      </c>
+      <c r="B56" s="48"/>
+      <c r="C56" s="48"/>
+      <c r="D56" s="48"/>
+      <c r="E56" s="48"/>
+      <c r="F56" s="48"/>
     </row>
     <row r="57" spans="1:6" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A57" s="45" t="s">
-        <v>130</v>
-      </c>
-      <c r="B57" s="45"/>
-      <c r="C57" s="45"/>
-      <c r="D57" s="46">
+      <c r="A57" s="49" t="s">
+        <v>131</v>
+      </c>
+      <c r="B57" s="49"/>
+      <c r="C57" s="49"/>
+      <c r="D57" s="50">
         <f>COUNTA(E4:E54)</f>
         <v>42</v>
       </c>
-      <c r="E57" s="46"/>
-      <c r="F57" s="46"/>
+      <c r="E57" s="50"/>
+      <c r="F57" s="50"/>
     </row>
     <row r="58" spans="1:6" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A58" s="45" t="s">
-        <v>131</v>
-      </c>
-      <c r="B58" s="45"/>
-      <c r="C58" s="45"/>
-      <c r="D58" s="46">
+      <c r="A58" s="49" t="s">
+        <v>132</v>
+      </c>
+      <c r="B58" s="49"/>
+      <c r="C58" s="49"/>
+      <c r="D58" s="50">
         <f>COUNTIF(E4:E54,"PASS")</f>
         <v>0</v>
       </c>
-      <c r="E58" s="46"/>
-      <c r="F58" s="46"/>
+      <c r="E58" s="50"/>
+      <c r="F58" s="50"/>
     </row>
     <row r="59" spans="1:6" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A59" s="45" t="s">
-        <v>132</v>
-      </c>
-      <c r="B59" s="45"/>
-      <c r="C59" s="45"/>
-      <c r="D59" s="46">
+      <c r="A59" s="49" t="s">
+        <v>133</v>
+      </c>
+      <c r="B59" s="49"/>
+      <c r="C59" s="49"/>
+      <c r="D59" s="50">
         <f>COUNTIF(E4:E54,"FAIL")</f>
         <v>0</v>
       </c>
-      <c r="E59" s="46"/>
-      <c r="F59" s="46"/>
+      <c r="E59" s="50"/>
+      <c r="F59" s="50"/>
     </row>
     <row r="60" spans="1:6" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A60" s="45" t="s">
-        <v>133</v>
-      </c>
-      <c r="B60" s="45"/>
-      <c r="C60" s="45"/>
-      <c r="D60" s="46">
+      <c r="A60" s="49" t="s">
+        <v>134</v>
+      </c>
+      <c r="B60" s="49"/>
+      <c r="C60" s="49"/>
+      <c r="D60" s="50">
         <f>COUNTIF(E4:E54,"N/A")</f>
         <v>42</v>
       </c>
-      <c r="E60" s="46"/>
-      <c r="F60" s="46"/>
+      <c r="E60" s="50"/>
+      <c r="F60" s="50"/>
     </row>
     <row r="61" spans="1:6" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A61" s="45" t="s">
-        <v>134</v>
-      </c>
-      <c r="B61" s="45"/>
-      <c r="C61" s="45"/>
-      <c r="D61" s="47">
+      <c r="A61" s="49" t="s">
+        <v>135</v>
+      </c>
+      <c r="B61" s="49"/>
+      <c r="C61" s="49"/>
+      <c r="D61" s="51">
         <f>IFERROR(COUNTIF(E4:E54,"PASS")/(COUNTA(E4:E54)-COUNTIF(E4:E54,"N/A")),0)</f>
         <v>0</v>
       </c>
-      <c r="E61" s="47"/>
-      <c r="F61" s="47"/>
+      <c r="E61" s="51"/>
+      <c r="F61" s="51"/>
     </row>
     <row r="62" spans="1:6" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A62" s="45" t="s">
-        <v>135</v>
-      </c>
-      <c r="B62" s="45"/>
-      <c r="C62" s="45"/>
-      <c r="D62" s="46" t="str">
+      <c r="A62" s="49" t="s">
+        <v>136</v>
+      </c>
+      <c r="B62" s="49"/>
+      <c r="C62" s="49"/>
+      <c r="D62" s="50" t="str">
         <f>IF(IFERROR(COUNTIF(E4:E54,"PASS")/(COUNTA(E4:E54)-COUNTIF(E4:E54,"N/A")),0)=1,"ĐẠT YÊU CẦU","CHƯA ĐẠT - CẦN XỬ LÝ")</f>
         <v>CHƯA ĐẠT - CẦN XỬ LÝ</v>
       </c>
-      <c r="E62" s="46"/>
-      <c r="F62" s="46"/>
+      <c r="E62" s="50"/>
+      <c r="F62" s="50"/>
     </row>
     <row r="64" spans="1:6" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A64" s="45" t="s">
-        <v>136</v>
-      </c>
-      <c r="B64" s="45"/>
-      <c r="C64" s="45"/>
-      <c r="D64" s="45" t="s">
+      <c r="A64" s="49" t="s">
         <v>137</v>
       </c>
-      <c r="E64" s="45"/>
-      <c r="F64" s="45"/>
+      <c r="B64" s="49"/>
+      <c r="C64" s="49"/>
+      <c r="D64" s="49" t="s">
+        <v>138</v>
+      </c>
+      <c r="E64" s="49"/>
+      <c r="F64" s="49"/>
     </row>
   </sheetData>
   <mergeCells count="26">
-    <mergeCell ref="A1:F1"/>
-    <mergeCell ref="A2:C2"/>
-    <mergeCell ref="A4:F4"/>
-    <mergeCell ref="A11:F11"/>
-    <mergeCell ref="A18:F18"/>
-    <mergeCell ref="A22:F22"/>
-    <mergeCell ref="A30:F30"/>
-    <mergeCell ref="A35:F35"/>
-    <mergeCell ref="A44:F44"/>
-    <mergeCell ref="A49:F49"/>
-    <mergeCell ref="A52:F52"/>
-    <mergeCell ref="A56:F56"/>
-    <mergeCell ref="A57:C57"/>
-    <mergeCell ref="D57:F57"/>
-    <mergeCell ref="A58:C58"/>
-    <mergeCell ref="D58:F58"/>
     <mergeCell ref="A62:C62"/>
     <mergeCell ref="D62:F62"/>
     <mergeCell ref="A64:C64"/>
@@ -4887,6 +4936,22 @@
     <mergeCell ref="D60:F60"/>
     <mergeCell ref="A61:C61"/>
     <mergeCell ref="D61:F61"/>
+    <mergeCell ref="A52:F52"/>
+    <mergeCell ref="A56:F56"/>
+    <mergeCell ref="A57:C57"/>
+    <mergeCell ref="D57:F57"/>
+    <mergeCell ref="A58:C58"/>
+    <mergeCell ref="D58:F58"/>
+    <mergeCell ref="A22:F22"/>
+    <mergeCell ref="A30:F30"/>
+    <mergeCell ref="A35:F35"/>
+    <mergeCell ref="A44:F44"/>
+    <mergeCell ref="A49:F49"/>
+    <mergeCell ref="A1:F1"/>
+    <mergeCell ref="A2:C2"/>
+    <mergeCell ref="A4:F4"/>
+    <mergeCell ref="A11:F11"/>
+    <mergeCell ref="A18:F18"/>
   </mergeCells>
   <conditionalFormatting sqref="E4:E54">
     <cfRule type="cellIs" dxfId="19" priority="2" operator="equal">
@@ -4932,21 +4997,21 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:6" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A1" s="50" t="s">
-        <v>237</v>
-      </c>
-      <c r="B1" s="50"/>
-      <c r="C1" s="50"/>
-      <c r="D1" s="50"/>
-      <c r="E1" s="50"/>
-      <c r="F1" s="50"/>
+      <c r="A1" s="45" t="s">
+        <v>238</v>
+      </c>
+      <c r="B1" s="45"/>
+      <c r="C1" s="45"/>
+      <c r="D1" s="45"/>
+      <c r="E1" s="45"/>
+      <c r="F1" s="45"/>
     </row>
     <row r="2" spans="1:6" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A2" s="51" t="s">
+      <c r="A2" s="46" t="s">
         <v>15</v>
       </c>
-      <c r="B2" s="51"/>
-      <c r="C2" s="51"/>
+      <c r="B2" s="46"/>
+      <c r="C2" s="46"/>
       <c r="D2" s="25" t="s">
         <v>16</v>
       </c>
@@ -4978,14 +5043,14 @@
       </c>
     </row>
     <row r="4" spans="1:6" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A4" s="48" t="s">
-        <v>139</v>
-      </c>
-      <c r="B4" s="48"/>
-      <c r="C4" s="48"/>
-      <c r="D4" s="48"/>
-      <c r="E4" s="48"/>
-      <c r="F4" s="48"/>
+      <c r="A4" s="47" t="s">
+        <v>140</v>
+      </c>
+      <c r="B4" s="47"/>
+      <c r="C4" s="47"/>
+      <c r="D4" s="47"/>
+      <c r="E4" s="47"/>
+      <c r="F4" s="47"/>
     </row>
     <row r="5" spans="1:6" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A5" s="29">
@@ -4995,13 +5060,13 @@
         <v>25</v>
       </c>
       <c r="C5" s="30" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="D5" s="30" t="s">
-        <v>238</v>
+        <v>239</v>
       </c>
       <c r="E5" s="29" t="s">
-        <v>435</v>
+        <v>436</v>
       </c>
       <c r="F5" s="30"/>
     </row>
@@ -5013,13 +5078,13 @@
         <v>25</v>
       </c>
       <c r="C6" s="32" t="s">
-        <v>239</v>
+        <v>240</v>
       </c>
       <c r="D6" s="32" t="s">
-        <v>240</v>
+        <v>241</v>
       </c>
       <c r="E6" s="29" t="s">
-        <v>435</v>
+        <v>436</v>
       </c>
       <c r="F6" s="32"/>
     </row>
@@ -5031,13 +5096,13 @@
         <v>25</v>
       </c>
       <c r="C7" s="30" t="s">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="D7" s="30" t="s">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="E7" s="29" t="s">
-        <v>435</v>
+        <v>436</v>
       </c>
       <c r="F7" s="30"/>
     </row>
@@ -5049,41 +5114,41 @@
         <v>25</v>
       </c>
       <c r="C8" s="32" t="s">
-        <v>243</v>
+        <v>244</v>
       </c>
       <c r="D8" s="32" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="E8" s="29" t="s">
-        <v>435</v>
+        <v>436</v>
       </c>
       <c r="F8" s="32"/>
     </row>
     <row r="9" spans="1:6" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A9" s="48" t="s">
-        <v>245</v>
-      </c>
-      <c r="B9" s="48"/>
-      <c r="C9" s="48"/>
-      <c r="D9" s="48"/>
-      <c r="E9" s="48"/>
-      <c r="F9" s="48"/>
+      <c r="A9" s="47" t="s">
+        <v>246</v>
+      </c>
+      <c r="B9" s="47"/>
+      <c r="C9" s="47"/>
+      <c r="D9" s="47"/>
+      <c r="E9" s="47"/>
+      <c r="F9" s="47"/>
     </row>
     <row r="10" spans="1:6" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A10" s="29">
         <v>5</v>
       </c>
       <c r="B10" s="30" t="s">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="C10" s="30" t="s">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="D10" s="30" t="s">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="E10" s="29" t="s">
-        <v>435</v>
+        <v>436</v>
       </c>
       <c r="F10" s="30"/>
     </row>
@@ -5092,16 +5157,16 @@
         <v>6</v>
       </c>
       <c r="B11" s="32" t="s">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="C11" s="32" t="s">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c r="D11" s="32" t="s">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="E11" s="29" t="s">
-        <v>435</v>
+        <v>436</v>
       </c>
       <c r="F11" s="32"/>
     </row>
@@ -5110,16 +5175,16 @@
         <v>7</v>
       </c>
       <c r="B12" s="30" t="s">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="C12" s="30" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="D12" s="30" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="E12" s="29" t="s">
-        <v>435</v>
+        <v>436</v>
       </c>
       <c r="F12" s="30"/>
     </row>
@@ -5128,16 +5193,16 @@
         <v>8</v>
       </c>
       <c r="B13" s="32" t="s">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="C13" s="32" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="D13" s="32" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="E13" s="29" t="s">
-        <v>435</v>
+        <v>436</v>
       </c>
       <c r="F13" s="32"/>
     </row>
@@ -5146,44 +5211,44 @@
         <v>9</v>
       </c>
       <c r="B14" s="30" t="s">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="C14" s="30" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="D14" s="30" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="E14" s="29" t="s">
-        <v>435</v>
+        <v>436</v>
       </c>
       <c r="F14" s="30"/>
     </row>
     <row r="15" spans="1:6" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A15" s="48" t="s">
-        <v>257</v>
-      </c>
-      <c r="B15" s="48"/>
-      <c r="C15" s="48"/>
-      <c r="D15" s="48"/>
-      <c r="E15" s="48"/>
-      <c r="F15" s="48"/>
+      <c r="A15" s="47" t="s">
+        <v>258</v>
+      </c>
+      <c r="B15" s="47"/>
+      <c r="C15" s="47"/>
+      <c r="D15" s="47"/>
+      <c r="E15" s="47"/>
+      <c r="F15" s="47"/>
     </row>
     <row r="16" spans="1:6" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A16" s="31">
         <v>10</v>
       </c>
       <c r="B16" s="32" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="C16" s="32" t="s">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="D16" s="32" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="E16" s="29" t="s">
-        <v>435</v>
+        <v>436</v>
       </c>
       <c r="F16" s="32"/>
     </row>
@@ -5192,44 +5257,44 @@
         <v>11</v>
       </c>
       <c r="B17" s="30" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="C17" s="30" t="s">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="D17" s="30" t="s">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="E17" s="29" t="s">
-        <v>435</v>
+        <v>436</v>
       </c>
       <c r="F17" s="30"/>
     </row>
     <row r="18" spans="1:6" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A18" s="48" t="s">
-        <v>262</v>
-      </c>
-      <c r="B18" s="48"/>
-      <c r="C18" s="48"/>
-      <c r="D18" s="48"/>
-      <c r="E18" s="48"/>
-      <c r="F18" s="48"/>
+      <c r="A18" s="47" t="s">
+        <v>263</v>
+      </c>
+      <c r="B18" s="47"/>
+      <c r="C18" s="47"/>
+      <c r="D18" s="47"/>
+      <c r="E18" s="47"/>
+      <c r="F18" s="47"/>
     </row>
     <row r="19" spans="1:6" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A19" s="31">
         <v>12</v>
       </c>
       <c r="B19" s="32" t="s">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="C19" s="32" t="s">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="D19" s="32" t="s">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="E19" s="29" t="s">
-        <v>435</v>
+        <v>436</v>
       </c>
       <c r="F19" s="32"/>
     </row>
@@ -5238,16 +5303,16 @@
         <v>13</v>
       </c>
       <c r="B20" s="30" t="s">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="C20" s="30" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="D20" s="30" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="E20" s="29" t="s">
-        <v>435</v>
+        <v>436</v>
       </c>
       <c r="F20" s="30"/>
     </row>
@@ -5256,16 +5321,16 @@
         <v>14</v>
       </c>
       <c r="B21" s="32" t="s">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="C21" s="32" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="D21" s="32" t="s">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="E21" s="29" t="s">
-        <v>435</v>
+        <v>436</v>
       </c>
       <c r="F21" s="32"/>
     </row>
@@ -5274,16 +5339,16 @@
         <v>15</v>
       </c>
       <c r="B22" s="30" t="s">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="C22" s="30" t="s">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="D22" s="30" t="s">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="E22" s="29" t="s">
-        <v>435</v>
+        <v>436</v>
       </c>
       <c r="F22" s="30"/>
     </row>
@@ -5292,44 +5357,44 @@
         <v>16</v>
       </c>
       <c r="B23" s="32" t="s">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="C23" s="32" t="s">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="D23" s="32" t="s">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="E23" s="29" t="s">
-        <v>435</v>
+        <v>436</v>
       </c>
       <c r="F23" s="32"/>
     </row>
     <row r="24" spans="1:6" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A24" s="48" t="s">
-        <v>274</v>
-      </c>
-      <c r="B24" s="48"/>
-      <c r="C24" s="48"/>
-      <c r="D24" s="48"/>
-      <c r="E24" s="48"/>
-      <c r="F24" s="48"/>
+      <c r="A24" s="47" t="s">
+        <v>275</v>
+      </c>
+      <c r="B24" s="47"/>
+      <c r="C24" s="47"/>
+      <c r="D24" s="47"/>
+      <c r="E24" s="47"/>
+      <c r="F24" s="47"/>
     </row>
     <row r="25" spans="1:6" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A25" s="29">
         <v>17</v>
       </c>
       <c r="B25" s="30" t="s">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="C25" s="30" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="D25" s="30" t="s">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="E25" s="29" t="s">
-        <v>435</v>
+        <v>436</v>
       </c>
       <c r="F25" s="30"/>
     </row>
@@ -5338,44 +5403,44 @@
         <v>18</v>
       </c>
       <c r="B26" s="32" t="s">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="C26" s="32" t="s">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="D26" s="32" t="s">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="E26" s="29" t="s">
-        <v>435</v>
+        <v>436</v>
       </c>
       <c r="F26" s="32"/>
     </row>
     <row r="27" spans="1:6" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A27" s="48" t="s">
-        <v>280</v>
-      </c>
-      <c r="B27" s="48"/>
-      <c r="C27" s="48"/>
-      <c r="D27" s="48"/>
-      <c r="E27" s="48"/>
-      <c r="F27" s="48"/>
+      <c r="A27" s="47" t="s">
+        <v>281</v>
+      </c>
+      <c r="B27" s="47"/>
+      <c r="C27" s="47"/>
+      <c r="D27" s="47"/>
+      <c r="E27" s="47"/>
+      <c r="F27" s="47"/>
     </row>
     <row r="28" spans="1:6" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A28" s="29">
         <v>19</v>
       </c>
       <c r="B28" s="30" t="s">
-        <v>281</v>
+        <v>282</v>
       </c>
       <c r="C28" s="30" t="s">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="D28" s="30" t="s">
-        <v>283</v>
+        <v>284</v>
       </c>
       <c r="E28" s="29" t="s">
-        <v>435</v>
+        <v>436</v>
       </c>
       <c r="F28" s="30"/>
     </row>
@@ -5384,16 +5449,16 @@
         <v>20</v>
       </c>
       <c r="B29" s="32" t="s">
-        <v>281</v>
+        <v>282</v>
       </c>
       <c r="C29" s="32" t="s">
-        <v>284</v>
+        <v>285</v>
       </c>
       <c r="D29" s="32" t="s">
-        <v>285</v>
+        <v>286</v>
       </c>
       <c r="E29" s="29" t="s">
-        <v>435</v>
+        <v>436</v>
       </c>
       <c r="F29" s="32"/>
     </row>
@@ -5402,44 +5467,44 @@
         <v>21</v>
       </c>
       <c r="B30" s="30" t="s">
-        <v>281</v>
+        <v>282</v>
       </c>
       <c r="C30" s="30" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="D30" s="30" t="s">
-        <v>286</v>
+        <v>287</v>
       </c>
       <c r="E30" s="29" t="s">
-        <v>435</v>
+        <v>436</v>
       </c>
       <c r="F30" s="30"/>
     </row>
     <row r="31" spans="1:6" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A31" s="48" t="s">
-        <v>287</v>
-      </c>
-      <c r="B31" s="48"/>
-      <c r="C31" s="48"/>
-      <c r="D31" s="48"/>
-      <c r="E31" s="48"/>
-      <c r="F31" s="48"/>
+      <c r="A31" s="47" t="s">
+        <v>288</v>
+      </c>
+      <c r="B31" s="47"/>
+      <c r="C31" s="47"/>
+      <c r="D31" s="47"/>
+      <c r="E31" s="47"/>
+      <c r="F31" s="47"/>
     </row>
     <row r="32" spans="1:6" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A32" s="31">
         <v>22</v>
       </c>
       <c r="B32" s="32" t="s">
-        <v>288</v>
+        <v>289</v>
       </c>
       <c r="C32" s="32" t="s">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="D32" s="32" t="s">
-        <v>290</v>
+        <v>291</v>
       </c>
       <c r="E32" s="29" t="s">
-        <v>435</v>
+        <v>436</v>
       </c>
       <c r="F32" s="32"/>
     </row>
@@ -5448,44 +5513,44 @@
         <v>23</v>
       </c>
       <c r="B33" s="30" t="s">
-        <v>288</v>
+        <v>289</v>
       </c>
       <c r="C33" s="30" t="s">
-        <v>291</v>
+        <v>292</v>
       </c>
       <c r="D33" s="30" t="s">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c r="E33" s="29" t="s">
-        <v>435</v>
+        <v>436</v>
       </c>
       <c r="F33" s="30"/>
     </row>
     <row r="34" spans="1:6" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A34" s="48" t="s">
-        <v>293</v>
-      </c>
-      <c r="B34" s="48"/>
-      <c r="C34" s="48"/>
-      <c r="D34" s="48"/>
-      <c r="E34" s="48"/>
-      <c r="F34" s="48"/>
+      <c r="A34" s="47" t="s">
+        <v>294</v>
+      </c>
+      <c r="B34" s="47"/>
+      <c r="C34" s="47"/>
+      <c r="D34" s="47"/>
+      <c r="E34" s="47"/>
+      <c r="F34" s="47"/>
     </row>
     <row r="35" spans="1:6" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A35" s="31">
         <v>24</v>
       </c>
       <c r="B35" s="32" t="s">
-        <v>294</v>
+        <v>295</v>
       </c>
       <c r="C35" s="32" t="s">
-        <v>295</v>
+        <v>296</v>
       </c>
       <c r="D35" s="32" t="s">
-        <v>296</v>
+        <v>297</v>
       </c>
       <c r="E35" s="29" t="s">
-        <v>435</v>
+        <v>436</v>
       </c>
       <c r="F35" s="32"/>
     </row>
@@ -5494,44 +5559,44 @@
         <v>25</v>
       </c>
       <c r="B36" s="30" t="s">
-        <v>294</v>
+        <v>295</v>
       </c>
       <c r="C36" s="30" t="s">
-        <v>297</v>
+        <v>298</v>
       </c>
       <c r="D36" s="30" t="s">
-        <v>298</v>
+        <v>299</v>
       </c>
       <c r="E36" s="29" t="s">
-        <v>435</v>
+        <v>436</v>
       </c>
       <c r="F36" s="30"/>
     </row>
     <row r="37" spans="1:6" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A37" s="48" t="s">
-        <v>299</v>
-      </c>
-      <c r="B37" s="48"/>
-      <c r="C37" s="48"/>
-      <c r="D37" s="48"/>
-      <c r="E37" s="48"/>
-      <c r="F37" s="48"/>
+      <c r="A37" s="47" t="s">
+        <v>300</v>
+      </c>
+      <c r="B37" s="47"/>
+      <c r="C37" s="47"/>
+      <c r="D37" s="47"/>
+      <c r="E37" s="47"/>
+      <c r="F37" s="47"/>
     </row>
     <row r="38" spans="1:6" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A38" s="31">
         <v>26</v>
       </c>
       <c r="B38" s="32" t="s">
-        <v>300</v>
+        <v>301</v>
       </c>
       <c r="C38" s="32" t="s">
-        <v>301</v>
+        <v>302</v>
       </c>
       <c r="D38" s="32" t="s">
-        <v>302</v>
+        <v>303</v>
       </c>
       <c r="E38" s="29" t="s">
-        <v>435</v>
+        <v>436</v>
       </c>
       <c r="F38" s="32"/>
     </row>
@@ -5540,16 +5605,16 @@
         <v>27</v>
       </c>
       <c r="B39" s="30" t="s">
-        <v>300</v>
+        <v>301</v>
       </c>
       <c r="C39" s="30" t="s">
-        <v>303</v>
+        <v>304</v>
       </c>
       <c r="D39" s="30" t="s">
-        <v>304</v>
+        <v>305</v>
       </c>
       <c r="E39" s="29" t="s">
-        <v>435</v>
+        <v>436</v>
       </c>
       <c r="F39" s="30"/>
     </row>
@@ -5558,16 +5623,16 @@
         <v>28</v>
       </c>
       <c r="B40" s="32" t="s">
-        <v>300</v>
+        <v>301</v>
       </c>
       <c r="C40" s="32" t="s">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="D40" s="32" t="s">
-        <v>306</v>
+        <v>307</v>
       </c>
       <c r="E40" s="29" t="s">
-        <v>435</v>
+        <v>436</v>
       </c>
       <c r="F40" s="32"/>
     </row>
@@ -5576,137 +5641,121 @@
         <v>29</v>
       </c>
       <c r="B41" s="30" t="s">
-        <v>300</v>
+        <v>301</v>
       </c>
       <c r="C41" s="30" t="s">
-        <v>307</v>
+        <v>308</v>
       </c>
       <c r="D41" s="30" t="s">
-        <v>308</v>
+        <v>309</v>
       </c>
       <c r="E41" s="29" t="s">
-        <v>435</v>
+        <v>436</v>
       </c>
       <c r="F41" s="30"/>
     </row>
     <row r="43" spans="1:6" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A43" s="49" t="s">
-        <v>129</v>
-      </c>
-      <c r="B43" s="49"/>
-      <c r="C43" s="49"/>
-      <c r="D43" s="49"/>
-      <c r="E43" s="49"/>
-      <c r="F43" s="49"/>
+      <c r="A43" s="48" t="s">
+        <v>130</v>
+      </c>
+      <c r="B43" s="48"/>
+      <c r="C43" s="48"/>
+      <c r="D43" s="48"/>
+      <c r="E43" s="48"/>
+      <c r="F43" s="48"/>
     </row>
     <row r="44" spans="1:6" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A44" s="45" t="s">
-        <v>130</v>
-      </c>
-      <c r="B44" s="45"/>
-      <c r="C44" s="45"/>
-      <c r="D44" s="46">
+      <c r="A44" s="49" t="s">
+        <v>131</v>
+      </c>
+      <c r="B44" s="49"/>
+      <c r="C44" s="49"/>
+      <c r="D44" s="50">
         <f>COUNTA(E4:E41)</f>
         <v>29</v>
       </c>
-      <c r="E44" s="46"/>
-      <c r="F44" s="46"/>
+      <c r="E44" s="50"/>
+      <c r="F44" s="50"/>
     </row>
     <row r="45" spans="1:6" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A45" s="45" t="s">
-        <v>131</v>
-      </c>
-      <c r="B45" s="45"/>
-      <c r="C45" s="45"/>
-      <c r="D45" s="46">
+      <c r="A45" s="49" t="s">
+        <v>132</v>
+      </c>
+      <c r="B45" s="49"/>
+      <c r="C45" s="49"/>
+      <c r="D45" s="50">
         <f>COUNTIF(E4:E41,"PASS")</f>
         <v>0</v>
       </c>
-      <c r="E45" s="46"/>
-      <c r="F45" s="46"/>
+      <c r="E45" s="50"/>
+      <c r="F45" s="50"/>
     </row>
     <row r="46" spans="1:6" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A46" s="45" t="s">
-        <v>132</v>
-      </c>
-      <c r="B46" s="45"/>
-      <c r="C46" s="45"/>
-      <c r="D46" s="46">
+      <c r="A46" s="49" t="s">
+        <v>133</v>
+      </c>
+      <c r="B46" s="49"/>
+      <c r="C46" s="49"/>
+      <c r="D46" s="50">
         <f>COUNTIF(E4:E41,"FAIL")</f>
         <v>0</v>
       </c>
-      <c r="E46" s="46"/>
-      <c r="F46" s="46"/>
+      <c r="E46" s="50"/>
+      <c r="F46" s="50"/>
     </row>
     <row r="47" spans="1:6" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A47" s="45" t="s">
-        <v>133</v>
-      </c>
-      <c r="B47" s="45"/>
-      <c r="C47" s="45"/>
-      <c r="D47" s="46">
+      <c r="A47" s="49" t="s">
+        <v>134</v>
+      </c>
+      <c r="B47" s="49"/>
+      <c r="C47" s="49"/>
+      <c r="D47" s="50">
         <f>COUNTIF(E4:E41,"N/A")</f>
         <v>29</v>
       </c>
-      <c r="E47" s="46"/>
-      <c r="F47" s="46"/>
+      <c r="E47" s="50"/>
+      <c r="F47" s="50"/>
     </row>
     <row r="48" spans="1:6" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A48" s="45" t="s">
-        <v>134</v>
-      </c>
-      <c r="B48" s="45"/>
-      <c r="C48" s="45"/>
-      <c r="D48" s="47">
+      <c r="A48" s="49" t="s">
+        <v>135</v>
+      </c>
+      <c r="B48" s="49"/>
+      <c r="C48" s="49"/>
+      <c r="D48" s="51">
         <f>IFERROR(COUNTIF(E4:E41,"PASS")/(COUNTA(E4:E41)-COUNTIF(E4:E41,"N/A")),0)</f>
         <v>0</v>
       </c>
-      <c r="E48" s="47"/>
-      <c r="F48" s="47"/>
+      <c r="E48" s="51"/>
+      <c r="F48" s="51"/>
     </row>
     <row r="49" spans="1:6" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A49" s="45" t="s">
-        <v>135</v>
-      </c>
-      <c r="B49" s="45"/>
-      <c r="C49" s="45"/>
-      <c r="D49" s="46" t="str">
+      <c r="A49" s="49" t="s">
+        <v>136</v>
+      </c>
+      <c r="B49" s="49"/>
+      <c r="C49" s="49"/>
+      <c r="D49" s="50" t="str">
         <f>IF(IFERROR(COUNTIF(E4:E41,"PASS")/(COUNTA(E4:E41)-COUNTIF(E4:E41,"N/A")),0)=1,"ĐẠT YÊU CẦU","CHƯA ĐẠT - CẦN XỬ LÝ")</f>
         <v>CHƯA ĐẠT - CẦN XỬ LÝ</v>
       </c>
-      <c r="E49" s="46"/>
-      <c r="F49" s="46"/>
+      <c r="E49" s="50"/>
+      <c r="F49" s="50"/>
     </row>
     <row r="51" spans="1:6" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A51" s="45" t="s">
-        <v>136</v>
-      </c>
-      <c r="B51" s="45"/>
-      <c r="C51" s="45"/>
-      <c r="D51" s="45" t="s">
+      <c r="A51" s="49" t="s">
         <v>137</v>
       </c>
-      <c r="E51" s="45"/>
-      <c r="F51" s="45"/>
+      <c r="B51" s="49"/>
+      <c r="C51" s="49"/>
+      <c r="D51" s="49" t="s">
+        <v>138</v>
+      </c>
+      <c r="E51" s="49"/>
+      <c r="F51" s="49"/>
     </row>
   </sheetData>
   <mergeCells count="26">
-    <mergeCell ref="A1:F1"/>
-    <mergeCell ref="A2:C2"/>
-    <mergeCell ref="A4:F4"/>
-    <mergeCell ref="A9:F9"/>
-    <mergeCell ref="A15:F15"/>
-    <mergeCell ref="A18:F18"/>
-    <mergeCell ref="A24:F24"/>
-    <mergeCell ref="A27:F27"/>
-    <mergeCell ref="A31:F31"/>
-    <mergeCell ref="A34:F34"/>
-    <mergeCell ref="A37:F37"/>
-    <mergeCell ref="A43:F43"/>
-    <mergeCell ref="A44:C44"/>
-    <mergeCell ref="D44:F44"/>
-    <mergeCell ref="A45:C45"/>
-    <mergeCell ref="D45:F45"/>
     <mergeCell ref="A49:C49"/>
     <mergeCell ref="D49:F49"/>
     <mergeCell ref="A51:C51"/>
@@ -5717,6 +5766,22 @@
     <mergeCell ref="D47:F47"/>
     <mergeCell ref="A48:C48"/>
     <mergeCell ref="D48:F48"/>
+    <mergeCell ref="A37:F37"/>
+    <mergeCell ref="A43:F43"/>
+    <mergeCell ref="A44:C44"/>
+    <mergeCell ref="D44:F44"/>
+    <mergeCell ref="A45:C45"/>
+    <mergeCell ref="D45:F45"/>
+    <mergeCell ref="A18:F18"/>
+    <mergeCell ref="A24:F24"/>
+    <mergeCell ref="A27:F27"/>
+    <mergeCell ref="A31:F31"/>
+    <mergeCell ref="A34:F34"/>
+    <mergeCell ref="A1:F1"/>
+    <mergeCell ref="A2:C2"/>
+    <mergeCell ref="A4:F4"/>
+    <mergeCell ref="A9:F9"/>
+    <mergeCell ref="A15:F15"/>
   </mergeCells>
   <conditionalFormatting sqref="E4:E41">
     <cfRule type="cellIs" dxfId="14" priority="2" operator="equal">
@@ -5762,21 +5827,21 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:6" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A1" s="50" t="s">
-        <v>309</v>
-      </c>
-      <c r="B1" s="50"/>
-      <c r="C1" s="50"/>
-      <c r="D1" s="50"/>
-      <c r="E1" s="50"/>
-      <c r="F1" s="50"/>
+      <c r="A1" s="45" t="s">
+        <v>310</v>
+      </c>
+      <c r="B1" s="45"/>
+      <c r="C1" s="45"/>
+      <c r="D1" s="45"/>
+      <c r="E1" s="45"/>
+      <c r="F1" s="45"/>
     </row>
     <row r="2" spans="1:6" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A2" s="51" t="s">
+      <c r="A2" s="46" t="s">
         <v>15</v>
       </c>
-      <c r="B2" s="51"/>
-      <c r="C2" s="51"/>
+      <c r="B2" s="46"/>
+      <c r="C2" s="46"/>
       <c r="D2" s="25" t="s">
         <v>16</v>
       </c>
@@ -5808,14 +5873,14 @@
       </c>
     </row>
     <row r="4" spans="1:6" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A4" s="48" t="s">
-        <v>139</v>
-      </c>
-      <c r="B4" s="48"/>
-      <c r="C4" s="48"/>
-      <c r="D4" s="48"/>
-      <c r="E4" s="48"/>
-      <c r="F4" s="48"/>
+      <c r="A4" s="47" t="s">
+        <v>140</v>
+      </c>
+      <c r="B4" s="47"/>
+      <c r="C4" s="47"/>
+      <c r="D4" s="47"/>
+      <c r="E4" s="47"/>
+      <c r="F4" s="47"/>
     </row>
     <row r="5" spans="1:6" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A5" s="29">
@@ -5825,13 +5890,13 @@
         <v>25</v>
       </c>
       <c r="C5" s="30" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="D5" s="30" t="s">
-        <v>310</v>
+        <v>311</v>
       </c>
       <c r="E5" s="29" t="s">
-        <v>435</v>
+        <v>436</v>
       </c>
       <c r="F5" s="30"/>
     </row>
@@ -5843,10 +5908,10 @@
         <v>25</v>
       </c>
       <c r="C6" s="32" t="s">
-        <v>239</v>
+        <v>240</v>
       </c>
       <c r="D6" s="32" t="s">
-        <v>311</v>
+        <v>312</v>
       </c>
       <c r="E6" s="31"/>
       <c r="F6" s="32"/>
@@ -5859,10 +5924,10 @@
         <v>25</v>
       </c>
       <c r="C7" s="30" t="s">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="D7" s="30" t="s">
-        <v>312</v>
+        <v>313</v>
       </c>
       <c r="E7" s="29"/>
       <c r="F7" s="30"/>
@@ -5875,36 +5940,36 @@
         <v>25</v>
       </c>
       <c r="C8" s="32" t="s">
-        <v>313</v>
+        <v>314</v>
       </c>
       <c r="D8" s="32" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="E8" s="31"/>
       <c r="F8" s="32"/>
     </row>
     <row r="9" spans="1:6" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A9" s="48" t="s">
-        <v>245</v>
-      </c>
-      <c r="B9" s="48"/>
-      <c r="C9" s="48"/>
-      <c r="D9" s="48"/>
-      <c r="E9" s="48"/>
-      <c r="F9" s="48"/>
+      <c r="A9" s="47" t="s">
+        <v>246</v>
+      </c>
+      <c r="B9" s="47"/>
+      <c r="C9" s="47"/>
+      <c r="D9" s="47"/>
+      <c r="E9" s="47"/>
+      <c r="F9" s="47"/>
     </row>
     <row r="10" spans="1:6" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A10" s="29">
         <v>5</v>
       </c>
       <c r="B10" s="30" t="s">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="C10" s="30" t="s">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="D10" s="30" t="s">
-        <v>314</v>
+        <v>315</v>
       </c>
       <c r="E10" s="29"/>
       <c r="F10" s="30"/>
@@ -5914,13 +5979,13 @@
         <v>6</v>
       </c>
       <c r="B11" s="32" t="s">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="C11" s="32" t="s">
-        <v>315</v>
+        <v>316</v>
       </c>
       <c r="D11" s="32" t="s">
-        <v>316</v>
+        <v>317</v>
       </c>
       <c r="E11" s="31"/>
       <c r="F11" s="32"/>
@@ -5930,13 +5995,13 @@
         <v>7</v>
       </c>
       <c r="B12" s="30" t="s">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="C12" s="30" t="s">
-        <v>317</v>
+        <v>318</v>
       </c>
       <c r="D12" s="30" t="s">
-        <v>318</v>
+        <v>319</v>
       </c>
       <c r="E12" s="29"/>
       <c r="F12" s="30"/>
@@ -5946,39 +6011,39 @@
         <v>8</v>
       </c>
       <c r="B13" s="32" t="s">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="C13" s="32" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="D13" s="32" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="E13" s="31"/>
       <c r="F13" s="32"/>
     </row>
     <row r="14" spans="1:6" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A14" s="48" t="s">
-        <v>257</v>
-      </c>
-      <c r="B14" s="48"/>
-      <c r="C14" s="48"/>
-      <c r="D14" s="48"/>
-      <c r="E14" s="48"/>
-      <c r="F14" s="48"/>
+      <c r="A14" s="47" t="s">
+        <v>258</v>
+      </c>
+      <c r="B14" s="47"/>
+      <c r="C14" s="47"/>
+      <c r="D14" s="47"/>
+      <c r="E14" s="47"/>
+      <c r="F14" s="47"/>
     </row>
     <row r="15" spans="1:6" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A15" s="29">
         <v>9</v>
       </c>
       <c r="B15" s="30" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="C15" s="30" t="s">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="D15" s="30" t="s">
-        <v>319</v>
+        <v>320</v>
       </c>
       <c r="E15" s="29"/>
       <c r="F15" s="30"/>
@@ -5988,13 +6053,13 @@
         <v>10</v>
       </c>
       <c r="B16" s="32" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="C16" s="32" t="s">
+        <v>321</v>
+      </c>
+      <c r="D16" s="32" t="s">
         <v>320</v>
-      </c>
-      <c r="D16" s="32" t="s">
-        <v>319</v>
       </c>
       <c r="E16" s="31"/>
       <c r="F16" s="32"/>
@@ -6004,13 +6069,13 @@
         <v>11</v>
       </c>
       <c r="B17" s="30" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="C17" s="30" t="s">
-        <v>321</v>
+        <v>322</v>
       </c>
       <c r="D17" s="30" t="s">
-        <v>322</v>
+        <v>323</v>
       </c>
       <c r="E17" s="29"/>
       <c r="F17" s="30"/>
@@ -6020,39 +6085,39 @@
         <v>12</v>
       </c>
       <c r="B18" s="32" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="C18" s="32" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="D18" s="32" t="s">
-        <v>319</v>
+        <v>320</v>
       </c>
       <c r="E18" s="31"/>
       <c r="F18" s="32"/>
     </row>
     <row r="19" spans="1:6" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A19" s="48" t="s">
-        <v>262</v>
-      </c>
-      <c r="B19" s="48"/>
-      <c r="C19" s="48"/>
-      <c r="D19" s="48"/>
-      <c r="E19" s="48"/>
-      <c r="F19" s="48"/>
+      <c r="A19" s="47" t="s">
+        <v>263</v>
+      </c>
+      <c r="B19" s="47"/>
+      <c r="C19" s="47"/>
+      <c r="D19" s="47"/>
+      <c r="E19" s="47"/>
+      <c r="F19" s="47"/>
     </row>
     <row r="20" spans="1:6" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A20" s="29">
         <v>13</v>
       </c>
       <c r="B20" s="30" t="s">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="C20" s="30" t="s">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="D20" s="30" t="s">
-        <v>323</v>
+        <v>324</v>
       </c>
       <c r="E20" s="29"/>
       <c r="F20" s="30"/>
@@ -6062,13 +6127,13 @@
         <v>14</v>
       </c>
       <c r="B21" s="32" t="s">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="C21" s="32" t="s">
-        <v>324</v>
+        <v>325</v>
       </c>
       <c r="D21" s="32" t="s">
-        <v>325</v>
+        <v>326</v>
       </c>
       <c r="E21" s="31"/>
       <c r="F21" s="32"/>
@@ -6078,16 +6143,16 @@
         <v>15</v>
       </c>
       <c r="B22" s="30" t="s">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="C22" s="30" t="s">
-        <v>326</v>
+        <v>327</v>
       </c>
       <c r="D22" s="30" t="s">
-        <v>327</v>
+        <v>328</v>
       </c>
       <c r="E22" s="29" t="s">
-        <v>435</v>
+        <v>436</v>
       </c>
       <c r="F22" s="30"/>
     </row>
@@ -6096,44 +6161,44 @@
         <v>16</v>
       </c>
       <c r="B23" s="32" t="s">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="C23" s="32" t="s">
-        <v>328</v>
+        <v>329</v>
       </c>
       <c r="D23" s="32" t="s">
-        <v>329</v>
+        <v>330</v>
       </c>
       <c r="E23" s="29" t="s">
-        <v>435</v>
+        <v>436</v>
       </c>
       <c r="F23" s="32"/>
     </row>
     <row r="24" spans="1:6" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A24" s="48" t="s">
-        <v>330</v>
-      </c>
-      <c r="B24" s="48"/>
-      <c r="C24" s="48"/>
-      <c r="D24" s="48"/>
-      <c r="E24" s="48"/>
-      <c r="F24" s="48"/>
+      <c r="A24" s="47" t="s">
+        <v>331</v>
+      </c>
+      <c r="B24" s="47"/>
+      <c r="C24" s="47"/>
+      <c r="D24" s="47"/>
+      <c r="E24" s="47"/>
+      <c r="F24" s="47"/>
     </row>
     <row r="25" spans="1:6" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A25" s="29">
         <v>17</v>
       </c>
       <c r="B25" s="30" t="s">
-        <v>331</v>
+        <v>332</v>
       </c>
       <c r="C25" s="30" t="s">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="D25" s="30" t="s">
-        <v>283</v>
+        <v>284</v>
       </c>
       <c r="E25" s="29" t="s">
-        <v>435</v>
+        <v>436</v>
       </c>
       <c r="F25" s="30"/>
     </row>
@@ -6142,16 +6207,16 @@
         <v>18</v>
       </c>
       <c r="B26" s="32" t="s">
-        <v>331</v>
+        <v>332</v>
       </c>
       <c r="C26" s="32" t="s">
-        <v>284</v>
+        <v>285</v>
       </c>
       <c r="D26" s="32" t="s">
-        <v>332</v>
+        <v>333</v>
       </c>
       <c r="E26" s="29" t="s">
-        <v>435</v>
+        <v>436</v>
       </c>
       <c r="F26" s="32"/>
     </row>
@@ -6160,72 +6225,72 @@
         <v>19</v>
       </c>
       <c r="B27" s="30" t="s">
-        <v>331</v>
+        <v>332</v>
       </c>
       <c r="C27" s="30" t="s">
-        <v>333</v>
+        <v>334</v>
       </c>
       <c r="D27" s="30" t="s">
-        <v>334</v>
+        <v>335</v>
       </c>
       <c r="E27" s="29" t="s">
-        <v>435</v>
+        <v>436</v>
       </c>
       <c r="F27" s="30"/>
     </row>
     <row r="28" spans="1:6" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A28" s="48" t="s">
-        <v>335</v>
-      </c>
-      <c r="B28" s="48"/>
-      <c r="C28" s="48"/>
-      <c r="D28" s="48"/>
-      <c r="E28" s="48"/>
-      <c r="F28" s="48"/>
+      <c r="A28" s="47" t="s">
+        <v>336</v>
+      </c>
+      <c r="B28" s="47"/>
+      <c r="C28" s="47"/>
+      <c r="D28" s="47"/>
+      <c r="E28" s="47"/>
+      <c r="F28" s="47"/>
     </row>
     <row r="29" spans="1:6" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A29" s="31">
         <v>20</v>
       </c>
       <c r="B29" s="32" t="s">
-        <v>336</v>
+        <v>337</v>
       </c>
       <c r="C29" s="32" t="s">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="D29" s="32" t="s">
-        <v>337</v>
+        <v>338</v>
       </c>
       <c r="E29" s="29" t="s">
-        <v>435</v>
+        <v>436</v>
       </c>
       <c r="F29" s="32"/>
     </row>
     <row r="30" spans="1:6" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A30" s="48" t="s">
-        <v>338</v>
-      </c>
-      <c r="B30" s="48"/>
-      <c r="C30" s="48"/>
-      <c r="D30" s="48"/>
-      <c r="E30" s="48"/>
-      <c r="F30" s="48"/>
+      <c r="A30" s="47" t="s">
+        <v>339</v>
+      </c>
+      <c r="B30" s="47"/>
+      <c r="C30" s="47"/>
+      <c r="D30" s="47"/>
+      <c r="E30" s="47"/>
+      <c r="F30" s="47"/>
     </row>
     <row r="31" spans="1:6" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A31" s="29">
         <v>21</v>
       </c>
       <c r="B31" s="30" t="s">
-        <v>339</v>
+        <v>340</v>
       </c>
       <c r="C31" s="30" t="s">
-        <v>295</v>
+        <v>296</v>
       </c>
       <c r="D31" s="30" t="s">
-        <v>340</v>
+        <v>341</v>
       </c>
       <c r="E31" s="29" t="s">
-        <v>435</v>
+        <v>436</v>
       </c>
       <c r="F31" s="30"/>
     </row>
@@ -6234,44 +6299,44 @@
         <v>22</v>
       </c>
       <c r="B32" s="32" t="s">
-        <v>339</v>
+        <v>340</v>
       </c>
       <c r="C32" s="32" t="s">
-        <v>297</v>
+        <v>298</v>
       </c>
       <c r="D32" s="32" t="s">
-        <v>341</v>
+        <v>342</v>
       </c>
       <c r="E32" s="29" t="s">
-        <v>435</v>
+        <v>436</v>
       </c>
       <c r="F32" s="32"/>
     </row>
     <row r="33" spans="1:6" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A33" s="48" t="s">
-        <v>342</v>
-      </c>
-      <c r="B33" s="48"/>
-      <c r="C33" s="48"/>
-      <c r="D33" s="48"/>
-      <c r="E33" s="48"/>
-      <c r="F33" s="48"/>
+      <c r="A33" s="47" t="s">
+        <v>343</v>
+      </c>
+      <c r="B33" s="47"/>
+      <c r="C33" s="47"/>
+      <c r="D33" s="47"/>
+      <c r="E33" s="47"/>
+      <c r="F33" s="47"/>
     </row>
     <row r="34" spans="1:6" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A34" s="29">
         <v>23</v>
       </c>
       <c r="B34" s="30" t="s">
-        <v>343</v>
+        <v>344</v>
       </c>
       <c r="C34" s="30" t="s">
-        <v>344</v>
+        <v>345</v>
       </c>
       <c r="D34" s="30" t="s">
-        <v>345</v>
+        <v>346</v>
       </c>
       <c r="E34" s="29" t="s">
-        <v>435</v>
+        <v>436</v>
       </c>
       <c r="F34" s="30"/>
     </row>
@@ -6280,16 +6345,16 @@
         <v>24</v>
       </c>
       <c r="B35" s="32" t="s">
-        <v>343</v>
+        <v>344</v>
       </c>
       <c r="C35" s="32" t="s">
-        <v>346</v>
+        <v>347</v>
       </c>
       <c r="D35" s="32" t="s">
-        <v>347</v>
+        <v>348</v>
       </c>
       <c r="E35" s="29" t="s">
-        <v>435</v>
+        <v>436</v>
       </c>
       <c r="F35" s="32"/>
     </row>
@@ -6298,16 +6363,16 @@
         <v>25</v>
       </c>
       <c r="B36" s="30" t="s">
-        <v>343</v>
+        <v>344</v>
       </c>
       <c r="C36" s="30" t="s">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="D36" s="30" t="s">
-        <v>348</v>
+        <v>349</v>
       </c>
       <c r="E36" s="29" t="s">
-        <v>435</v>
+        <v>436</v>
       </c>
       <c r="F36" s="30"/>
     </row>
@@ -6316,16 +6381,16 @@
         <v>26</v>
       </c>
       <c r="B37" s="32" t="s">
-        <v>343</v>
+        <v>344</v>
       </c>
       <c r="C37" s="32" t="s">
-        <v>349</v>
+        <v>350</v>
       </c>
       <c r="D37" s="32" t="s">
-        <v>350</v>
+        <v>351</v>
       </c>
       <c r="E37" s="29" t="s">
-        <v>435</v>
+        <v>436</v>
       </c>
       <c r="F37" s="32"/>
     </row>
@@ -6334,16 +6399,16 @@
         <v>27</v>
       </c>
       <c r="B38" s="30" t="s">
-        <v>343</v>
+        <v>344</v>
       </c>
       <c r="C38" s="30" t="s">
-        <v>351</v>
+        <v>352</v>
       </c>
       <c r="D38" s="30" t="s">
-        <v>352</v>
+        <v>353</v>
       </c>
       <c r="E38" s="29" t="s">
-        <v>435</v>
+        <v>436</v>
       </c>
       <c r="F38" s="30"/>
     </row>
@@ -6352,165 +6417,149 @@
         <v>28</v>
       </c>
       <c r="B39" s="32" t="s">
-        <v>343</v>
+        <v>344</v>
       </c>
       <c r="C39" s="32" t="s">
-        <v>353</v>
+        <v>354</v>
       </c>
       <c r="D39" s="32" t="s">
-        <v>354</v>
+        <v>355</v>
       </c>
       <c r="E39" s="29" t="s">
-        <v>435</v>
+        <v>436</v>
       </c>
       <c r="F39" s="32"/>
     </row>
     <row r="40" spans="1:6" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A40" s="48" t="s">
-        <v>355</v>
-      </c>
-      <c r="B40" s="48"/>
-      <c r="C40" s="48"/>
-      <c r="D40" s="48"/>
-      <c r="E40" s="48"/>
-      <c r="F40" s="48"/>
+      <c r="A40" s="47" t="s">
+        <v>356</v>
+      </c>
+      <c r="B40" s="47"/>
+      <c r="C40" s="47"/>
+      <c r="D40" s="47"/>
+      <c r="E40" s="47"/>
+      <c r="F40" s="47"/>
     </row>
     <row r="41" spans="1:6" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A41" s="29">
         <v>29</v>
       </c>
       <c r="B41" s="30" t="s">
-        <v>356</v>
+        <v>357</v>
       </c>
       <c r="C41" s="30" t="s">
-        <v>357</v>
+        <v>358</v>
       </c>
       <c r="D41" s="30" t="s">
-        <v>358</v>
+        <v>359</v>
       </c>
       <c r="E41" s="29" t="s">
-        <v>435</v>
+        <v>436</v>
       </c>
       <c r="F41" s="30"/>
     </row>
     <row r="43" spans="1:6" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A43" s="49" t="s">
-        <v>129</v>
-      </c>
-      <c r="B43" s="49"/>
-      <c r="C43" s="49"/>
-      <c r="D43" s="49"/>
-      <c r="E43" s="49"/>
-      <c r="F43" s="49"/>
+      <c r="A43" s="48" t="s">
+        <v>130</v>
+      </c>
+      <c r="B43" s="48"/>
+      <c r="C43" s="48"/>
+      <c r="D43" s="48"/>
+      <c r="E43" s="48"/>
+      <c r="F43" s="48"/>
     </row>
     <row r="44" spans="1:6" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A44" s="45" t="s">
-        <v>130</v>
-      </c>
-      <c r="B44" s="45"/>
-      <c r="C44" s="45"/>
-      <c r="D44" s="46">
+      <c r="A44" s="49" t="s">
+        <v>131</v>
+      </c>
+      <c r="B44" s="49"/>
+      <c r="C44" s="49"/>
+      <c r="D44" s="50">
         <f>COUNTA(E4:E41)</f>
         <v>16</v>
       </c>
-      <c r="E44" s="46"/>
-      <c r="F44" s="46"/>
+      <c r="E44" s="50"/>
+      <c r="F44" s="50"/>
     </row>
     <row r="45" spans="1:6" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A45" s="45" t="s">
-        <v>131</v>
-      </c>
-      <c r="B45" s="45"/>
-      <c r="C45" s="45"/>
-      <c r="D45" s="46">
+      <c r="A45" s="49" t="s">
+        <v>132</v>
+      </c>
+      <c r="B45" s="49"/>
+      <c r="C45" s="49"/>
+      <c r="D45" s="50">
         <f>COUNTIF(E4:E41,"PASS")</f>
         <v>0</v>
       </c>
-      <c r="E45" s="46"/>
-      <c r="F45" s="46"/>
+      <c r="E45" s="50"/>
+      <c r="F45" s="50"/>
     </row>
     <row r="46" spans="1:6" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A46" s="45" t="s">
-        <v>132</v>
-      </c>
-      <c r="B46" s="45"/>
-      <c r="C46" s="45"/>
-      <c r="D46" s="46">
+      <c r="A46" s="49" t="s">
+        <v>133</v>
+      </c>
+      <c r="B46" s="49"/>
+      <c r="C46" s="49"/>
+      <c r="D46" s="50">
         <f>COUNTIF(E4:E41,"FAIL")</f>
         <v>0</v>
       </c>
-      <c r="E46" s="46"/>
-      <c r="F46" s="46"/>
+      <c r="E46" s="50"/>
+      <c r="F46" s="50"/>
     </row>
     <row r="47" spans="1:6" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A47" s="45" t="s">
-        <v>133</v>
-      </c>
-      <c r="B47" s="45"/>
-      <c r="C47" s="45"/>
-      <c r="D47" s="46">
+      <c r="A47" s="49" t="s">
+        <v>134</v>
+      </c>
+      <c r="B47" s="49"/>
+      <c r="C47" s="49"/>
+      <c r="D47" s="50">
         <f>COUNTIF(E4:E41,"N/A")</f>
         <v>16</v>
       </c>
-      <c r="E47" s="46"/>
-      <c r="F47" s="46"/>
+      <c r="E47" s="50"/>
+      <c r="F47" s="50"/>
     </row>
     <row r="48" spans="1:6" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A48" s="45" t="s">
-        <v>134</v>
-      </c>
-      <c r="B48" s="45"/>
-      <c r="C48" s="45"/>
-      <c r="D48" s="47">
+      <c r="A48" s="49" t="s">
+        <v>135</v>
+      </c>
+      <c r="B48" s="49"/>
+      <c r="C48" s="49"/>
+      <c r="D48" s="51">
         <f>IFERROR(COUNTIF(E4:E41,"PASS")/(COUNTA(E4:E41)-COUNTIF(E4:E41,"N/A")),0)</f>
         <v>0</v>
       </c>
-      <c r="E48" s="47"/>
-      <c r="F48" s="47"/>
+      <c r="E48" s="51"/>
+      <c r="F48" s="51"/>
     </row>
     <row r="49" spans="1:6" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A49" s="45" t="s">
-        <v>135</v>
-      </c>
-      <c r="B49" s="45"/>
-      <c r="C49" s="45"/>
-      <c r="D49" s="46" t="str">
+      <c r="A49" s="49" t="s">
+        <v>136</v>
+      </c>
+      <c r="B49" s="49"/>
+      <c r="C49" s="49"/>
+      <c r="D49" s="50" t="str">
         <f>IF(IFERROR(COUNTIF(E4:E41,"PASS")/(COUNTA(E4:E41)-COUNTIF(E4:E41,"N/A")),0)=1,"ĐẠT YÊU CẦU","CHƯA ĐẠT - CẦN XỬ LÝ")</f>
         <v>CHƯA ĐẠT - CẦN XỬ LÝ</v>
       </c>
-      <c r="E49" s="46"/>
-      <c r="F49" s="46"/>
+      <c r="E49" s="50"/>
+      <c r="F49" s="50"/>
     </row>
     <row r="51" spans="1:6" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A51" s="45" t="s">
-        <v>136</v>
-      </c>
-      <c r="B51" s="45"/>
-      <c r="C51" s="45"/>
-      <c r="D51" s="45" t="s">
+      <c r="A51" s="49" t="s">
         <v>137</v>
       </c>
-      <c r="E51" s="45"/>
-      <c r="F51" s="45"/>
+      <c r="B51" s="49"/>
+      <c r="C51" s="49"/>
+      <c r="D51" s="49" t="s">
+        <v>138</v>
+      </c>
+      <c r="E51" s="49"/>
+      <c r="F51" s="49"/>
     </row>
   </sheetData>
   <mergeCells count="26">
-    <mergeCell ref="A1:F1"/>
-    <mergeCell ref="A2:C2"/>
-    <mergeCell ref="A4:F4"/>
-    <mergeCell ref="A9:F9"/>
-    <mergeCell ref="A14:F14"/>
-    <mergeCell ref="A19:F19"/>
-    <mergeCell ref="A24:F24"/>
-    <mergeCell ref="A28:F28"/>
-    <mergeCell ref="A30:F30"/>
-    <mergeCell ref="A33:F33"/>
-    <mergeCell ref="A40:F40"/>
-    <mergeCell ref="A43:F43"/>
-    <mergeCell ref="A44:C44"/>
-    <mergeCell ref="D44:F44"/>
-    <mergeCell ref="A45:C45"/>
-    <mergeCell ref="D45:F45"/>
     <mergeCell ref="A49:C49"/>
     <mergeCell ref="D49:F49"/>
     <mergeCell ref="A51:C51"/>
@@ -6521,6 +6570,22 @@
     <mergeCell ref="D47:F47"/>
     <mergeCell ref="A48:C48"/>
     <mergeCell ref="D48:F48"/>
+    <mergeCell ref="A40:F40"/>
+    <mergeCell ref="A43:F43"/>
+    <mergeCell ref="A44:C44"/>
+    <mergeCell ref="D44:F44"/>
+    <mergeCell ref="A45:C45"/>
+    <mergeCell ref="D45:F45"/>
+    <mergeCell ref="A19:F19"/>
+    <mergeCell ref="A24:F24"/>
+    <mergeCell ref="A28:F28"/>
+    <mergeCell ref="A30:F30"/>
+    <mergeCell ref="A33:F33"/>
+    <mergeCell ref="A1:F1"/>
+    <mergeCell ref="A2:C2"/>
+    <mergeCell ref="A4:F4"/>
+    <mergeCell ref="A9:F9"/>
+    <mergeCell ref="A14:F14"/>
   </mergeCells>
   <conditionalFormatting sqref="E4:E41">
     <cfRule type="cellIs" dxfId="9" priority="2" operator="equal">
@@ -6566,21 +6631,21 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:6" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A1" s="50" t="s">
-        <v>359</v>
-      </c>
-      <c r="B1" s="50"/>
-      <c r="C1" s="50"/>
-      <c r="D1" s="50"/>
-      <c r="E1" s="50"/>
-      <c r="F1" s="50"/>
+      <c r="A1" s="45" t="s">
+        <v>360</v>
+      </c>
+      <c r="B1" s="45"/>
+      <c r="C1" s="45"/>
+      <c r="D1" s="45"/>
+      <c r="E1" s="45"/>
+      <c r="F1" s="45"/>
     </row>
     <row r="2" spans="1:6" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A2" s="51" t="s">
+      <c r="A2" s="46" t="s">
         <v>15</v>
       </c>
-      <c r="B2" s="51"/>
-      <c r="C2" s="51"/>
+      <c r="B2" s="46"/>
+      <c r="C2" s="46"/>
       <c r="D2" s="25" t="s">
         <v>16</v>
       </c>
@@ -6612,30 +6677,30 @@
       </c>
     </row>
     <row r="4" spans="1:6" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A4" s="48" t="s">
-        <v>360</v>
-      </c>
-      <c r="B4" s="48"/>
-      <c r="C4" s="48"/>
-      <c r="D4" s="48"/>
-      <c r="E4" s="48"/>
-      <c r="F4" s="48"/>
+      <c r="A4" s="47" t="s">
+        <v>361</v>
+      </c>
+      <c r="B4" s="47"/>
+      <c r="C4" s="47"/>
+      <c r="D4" s="47"/>
+      <c r="E4" s="47"/>
+      <c r="F4" s="47"/>
     </row>
     <row r="5" spans="1:6" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A5" s="29">
         <v>1</v>
       </c>
       <c r="B5" s="30" t="s">
-        <v>361</v>
+        <v>362</v>
       </c>
       <c r="C5" s="30" t="s">
-        <v>362</v>
+        <v>363</v>
       </c>
       <c r="D5" s="30" t="s">
-        <v>363</v>
+        <v>364</v>
       </c>
       <c r="E5" s="29" t="s">
-        <v>435</v>
+        <v>436</v>
       </c>
       <c r="F5" s="30"/>
     </row>
@@ -6644,16 +6709,16 @@
         <v>2</v>
       </c>
       <c r="B6" s="32" t="s">
-        <v>361</v>
+        <v>362</v>
       </c>
       <c r="C6" s="32" t="s">
-        <v>364</v>
+        <v>365</v>
       </c>
       <c r="D6" s="32" t="s">
-        <v>365</v>
+        <v>366</v>
       </c>
       <c r="E6" s="29" t="s">
-        <v>435</v>
+        <v>436</v>
       </c>
       <c r="F6" s="32"/>
     </row>
@@ -6662,16 +6727,16 @@
         <v>3</v>
       </c>
       <c r="B7" s="30" t="s">
-        <v>361</v>
+        <v>362</v>
       </c>
       <c r="C7" s="30" t="s">
-        <v>366</v>
+        <v>367</v>
       </c>
       <c r="D7" s="30" t="s">
-        <v>367</v>
+        <v>368</v>
       </c>
       <c r="E7" s="29" t="s">
-        <v>435</v>
+        <v>436</v>
       </c>
       <c r="F7" s="30"/>
     </row>
@@ -6680,16 +6745,16 @@
         <v>4</v>
       </c>
       <c r="B8" s="32" t="s">
-        <v>361</v>
+        <v>362</v>
       </c>
       <c r="C8" s="32" t="s">
-        <v>368</v>
+        <v>369</v>
       </c>
       <c r="D8" s="32" t="s">
-        <v>369</v>
+        <v>370</v>
       </c>
       <c r="E8" s="29" t="s">
-        <v>435</v>
+        <v>436</v>
       </c>
       <c r="F8" s="32"/>
     </row>
@@ -6698,44 +6763,44 @@
         <v>5</v>
       </c>
       <c r="B9" s="30" t="s">
-        <v>361</v>
+        <v>362</v>
       </c>
       <c r="C9" s="30" t="s">
-        <v>370</v>
+        <v>371</v>
       </c>
       <c r="D9" s="30" t="s">
-        <v>371</v>
+        <v>372</v>
       </c>
       <c r="E9" s="29" t="s">
-        <v>435</v>
+        <v>436</v>
       </c>
       <c r="F9" s="30"/>
     </row>
     <row r="10" spans="1:6" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A10" s="48" t="s">
-        <v>372</v>
-      </c>
-      <c r="B10" s="48"/>
-      <c r="C10" s="48"/>
-      <c r="D10" s="48"/>
-      <c r="E10" s="48"/>
-      <c r="F10" s="48"/>
+      <c r="A10" s="47" t="s">
+        <v>373</v>
+      </c>
+      <c r="B10" s="47"/>
+      <c r="C10" s="47"/>
+      <c r="D10" s="47"/>
+      <c r="E10" s="47"/>
+      <c r="F10" s="47"/>
     </row>
     <row r="11" spans="1:6" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A11" s="31">
         <v>6</v>
       </c>
       <c r="B11" s="32" t="s">
-        <v>373</v>
+        <v>374</v>
       </c>
       <c r="C11" s="32" t="s">
-        <v>374</v>
+        <v>375</v>
       </c>
       <c r="D11" s="32" t="s">
-        <v>375</v>
+        <v>376</v>
       </c>
       <c r="E11" s="29" t="s">
-        <v>435</v>
+        <v>436</v>
       </c>
       <c r="F11" s="32"/>
     </row>
@@ -6744,16 +6809,16 @@
         <v>7</v>
       </c>
       <c r="B12" s="30" t="s">
-        <v>373</v>
+        <v>374</v>
       </c>
       <c r="C12" s="30" t="s">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="D12" s="30" t="s">
-        <v>376</v>
+        <v>377</v>
       </c>
       <c r="E12" s="29" t="s">
-        <v>435</v>
+        <v>436</v>
       </c>
       <c r="F12" s="30"/>
     </row>
@@ -6762,16 +6827,16 @@
         <v>8</v>
       </c>
       <c r="B13" s="32" t="s">
-        <v>373</v>
+        <v>374</v>
       </c>
       <c r="C13" s="32" t="s">
-        <v>377</v>
+        <v>378</v>
       </c>
       <c r="D13" s="32" t="s">
-        <v>378</v>
+        <v>379</v>
       </c>
       <c r="E13" s="29" t="s">
-        <v>435</v>
+        <v>436</v>
       </c>
       <c r="F13" s="32"/>
     </row>
@@ -6780,16 +6845,16 @@
         <v>9</v>
       </c>
       <c r="B14" s="30" t="s">
-        <v>373</v>
+        <v>374</v>
       </c>
       <c r="C14" s="30" t="s">
-        <v>379</v>
+        <v>380</v>
       </c>
       <c r="D14" s="30" t="s">
-        <v>380</v>
+        <v>381</v>
       </c>
       <c r="E14" s="29" t="s">
-        <v>435</v>
+        <v>436</v>
       </c>
       <c r="F14" s="30"/>
     </row>
@@ -6798,44 +6863,44 @@
         <v>10</v>
       </c>
       <c r="B15" s="32" t="s">
-        <v>373</v>
+        <v>374</v>
       </c>
       <c r="C15" s="32" t="s">
-        <v>381</v>
+        <v>382</v>
       </c>
       <c r="D15" s="32" t="s">
-        <v>382</v>
+        <v>383</v>
       </c>
       <c r="E15" s="29" t="s">
-        <v>435</v>
+        <v>436</v>
       </c>
       <c r="F15" s="32"/>
     </row>
     <row r="16" spans="1:6" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A16" s="48" t="s">
-        <v>383</v>
-      </c>
-      <c r="B16" s="48"/>
-      <c r="C16" s="48"/>
-      <c r="D16" s="48"/>
-      <c r="E16" s="48"/>
-      <c r="F16" s="48"/>
+      <c r="A16" s="47" t="s">
+        <v>384</v>
+      </c>
+      <c r="B16" s="47"/>
+      <c r="C16" s="47"/>
+      <c r="D16" s="47"/>
+      <c r="E16" s="47"/>
+      <c r="F16" s="47"/>
     </row>
     <row r="17" spans="1:6" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A17" s="29">
         <v>11</v>
       </c>
       <c r="B17" s="30" t="s">
-        <v>384</v>
+        <v>385</v>
       </c>
       <c r="C17" s="30" t="s">
-        <v>385</v>
+        <v>386</v>
       </c>
       <c r="D17" s="30" t="s">
-        <v>386</v>
+        <v>387</v>
       </c>
       <c r="E17" s="29" t="s">
-        <v>435</v>
+        <v>436</v>
       </c>
       <c r="F17" s="30"/>
     </row>
@@ -6844,16 +6909,16 @@
         <v>12</v>
       </c>
       <c r="B18" s="32" t="s">
-        <v>384</v>
+        <v>385</v>
       </c>
       <c r="C18" s="32" t="s">
-        <v>387</v>
+        <v>388</v>
       </c>
       <c r="D18" s="32" t="s">
-        <v>388</v>
+        <v>389</v>
       </c>
       <c r="E18" s="29" t="s">
-        <v>435</v>
+        <v>436</v>
       </c>
       <c r="F18" s="32"/>
     </row>
@@ -6862,16 +6927,16 @@
         <v>13</v>
       </c>
       <c r="B19" s="30" t="s">
-        <v>384</v>
+        <v>385</v>
       </c>
       <c r="C19" s="30" t="s">
-        <v>389</v>
+        <v>390</v>
       </c>
       <c r="D19" s="30" t="s">
-        <v>390</v>
+        <v>391</v>
       </c>
       <c r="E19" s="29" t="s">
-        <v>435</v>
+        <v>436</v>
       </c>
       <c r="F19" s="30"/>
     </row>
@@ -6880,44 +6945,44 @@
         <v>14</v>
       </c>
       <c r="B20" s="32" t="s">
-        <v>384</v>
+        <v>385</v>
       </c>
       <c r="C20" s="32" t="s">
-        <v>391</v>
+        <v>392</v>
       </c>
       <c r="D20" s="32" t="s">
-        <v>392</v>
+        <v>393</v>
       </c>
       <c r="E20" s="29" t="s">
-        <v>435</v>
+        <v>436</v>
       </c>
       <c r="F20" s="32"/>
     </row>
     <row r="21" spans="1:6" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A21" s="48" t="s">
-        <v>393</v>
-      </c>
-      <c r="B21" s="48"/>
-      <c r="C21" s="48"/>
-      <c r="D21" s="48"/>
-      <c r="E21" s="48"/>
-      <c r="F21" s="48"/>
+      <c r="A21" s="47" t="s">
+        <v>394</v>
+      </c>
+      <c r="B21" s="47"/>
+      <c r="C21" s="47"/>
+      <c r="D21" s="47"/>
+      <c r="E21" s="47"/>
+      <c r="F21" s="47"/>
     </row>
     <row r="22" spans="1:6" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A22" s="29">
         <v>15</v>
       </c>
       <c r="B22" s="30" t="s">
-        <v>394</v>
+        <v>395</v>
       </c>
       <c r="C22" s="30" t="s">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="D22" s="30" t="s">
-        <v>395</v>
+        <v>396</v>
       </c>
       <c r="E22" s="29" t="s">
-        <v>435</v>
+        <v>436</v>
       </c>
       <c r="F22" s="30"/>
     </row>
@@ -6926,16 +6991,16 @@
         <v>16</v>
       </c>
       <c r="B23" s="32" t="s">
-        <v>394</v>
+        <v>395</v>
       </c>
       <c r="C23" s="32" t="s">
-        <v>284</v>
+        <v>285</v>
       </c>
       <c r="D23" s="32" t="s">
-        <v>396</v>
+        <v>397</v>
       </c>
       <c r="E23" s="29" t="s">
-        <v>435</v>
+        <v>436</v>
       </c>
       <c r="F23" s="32"/>
     </row>
@@ -6944,44 +7009,44 @@
         <v>17</v>
       </c>
       <c r="B24" s="30" t="s">
-        <v>394</v>
+        <v>395</v>
       </c>
       <c r="C24" s="30" t="s">
-        <v>397</v>
+        <v>398</v>
       </c>
       <c r="D24" s="30" t="s">
-        <v>398</v>
+        <v>399</v>
       </c>
       <c r="E24" s="29" t="s">
-        <v>435</v>
+        <v>436</v>
       </c>
       <c r="F24" s="30"/>
     </row>
     <row r="25" spans="1:6" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A25" s="48" t="s">
-        <v>399</v>
-      </c>
-      <c r="B25" s="48"/>
-      <c r="C25" s="48"/>
-      <c r="D25" s="48"/>
-      <c r="E25" s="48"/>
-      <c r="F25" s="48"/>
+      <c r="A25" s="47" t="s">
+        <v>400</v>
+      </c>
+      <c r="B25" s="47"/>
+      <c r="C25" s="47"/>
+      <c r="D25" s="47"/>
+      <c r="E25" s="47"/>
+      <c r="F25" s="47"/>
     </row>
     <row r="26" spans="1:6" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A26" s="31">
         <v>18</v>
       </c>
       <c r="B26" s="32" t="s">
-        <v>400</v>
+        <v>401</v>
       </c>
       <c r="C26" s="32" t="s">
-        <v>401</v>
+        <v>402</v>
       </c>
       <c r="D26" s="32" t="s">
-        <v>402</v>
+        <v>403</v>
       </c>
       <c r="E26" s="29" t="s">
-        <v>435</v>
+        <v>436</v>
       </c>
       <c r="F26" s="32"/>
     </row>
@@ -6990,16 +7055,16 @@
         <v>19</v>
       </c>
       <c r="B27" s="30" t="s">
-        <v>400</v>
+        <v>401</v>
       </c>
       <c r="C27" s="30" t="s">
-        <v>403</v>
+        <v>404</v>
       </c>
       <c r="D27" s="30" t="s">
-        <v>404</v>
+        <v>405</v>
       </c>
       <c r="E27" s="29" t="s">
-        <v>435</v>
+        <v>436</v>
       </c>
       <c r="F27" s="30"/>
     </row>
@@ -7008,16 +7073,16 @@
         <v>20</v>
       </c>
       <c r="B28" s="32" t="s">
-        <v>400</v>
+        <v>401</v>
       </c>
       <c r="C28" s="32" t="s">
-        <v>405</v>
+        <v>406</v>
       </c>
       <c r="D28" s="32" t="s">
-        <v>406</v>
+        <v>407</v>
       </c>
       <c r="E28" s="29" t="s">
-        <v>435</v>
+        <v>436</v>
       </c>
       <c r="F28" s="32"/>
     </row>
@@ -7026,44 +7091,44 @@
         <v>21</v>
       </c>
       <c r="B29" s="30" t="s">
-        <v>400</v>
+        <v>401</v>
       </c>
       <c r="C29" s="30" t="s">
-        <v>407</v>
+        <v>408</v>
       </c>
       <c r="D29" s="30" t="s">
-        <v>408</v>
+        <v>409</v>
       </c>
       <c r="E29" s="29" t="s">
-        <v>435</v>
+        <v>436</v>
       </c>
       <c r="F29" s="30"/>
     </row>
     <row r="30" spans="1:6" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A30" s="48" t="s">
-        <v>409</v>
-      </c>
-      <c r="B30" s="48"/>
-      <c r="C30" s="48"/>
-      <c r="D30" s="48"/>
-      <c r="E30" s="48"/>
-      <c r="F30" s="48"/>
+      <c r="A30" s="47" t="s">
+        <v>410</v>
+      </c>
+      <c r="B30" s="47"/>
+      <c r="C30" s="47"/>
+      <c r="D30" s="47"/>
+      <c r="E30" s="47"/>
+      <c r="F30" s="47"/>
     </row>
     <row r="31" spans="1:6" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A31" s="31">
         <v>22</v>
       </c>
       <c r="B31" s="32" t="s">
-        <v>410</v>
+        <v>411</v>
       </c>
       <c r="C31" s="32" t="s">
-        <v>411</v>
+        <v>412</v>
       </c>
       <c r="D31" s="32" t="s">
-        <v>412</v>
+        <v>413</v>
       </c>
       <c r="E31" s="29" t="s">
-        <v>435</v>
+        <v>436</v>
       </c>
       <c r="F31" s="32"/>
     </row>
@@ -7072,16 +7137,16 @@
         <v>23</v>
       </c>
       <c r="B32" s="30" t="s">
-        <v>410</v>
+        <v>411</v>
       </c>
       <c r="C32" s="30" t="s">
-        <v>413</v>
+        <v>414</v>
       </c>
       <c r="D32" s="30" t="s">
-        <v>414</v>
+        <v>415</v>
       </c>
       <c r="E32" s="29" t="s">
-        <v>435</v>
+        <v>436</v>
       </c>
       <c r="F32" s="30"/>
     </row>
@@ -7090,44 +7155,44 @@
         <v>24</v>
       </c>
       <c r="B33" s="32" t="s">
-        <v>410</v>
+        <v>411</v>
       </c>
       <c r="C33" s="32" t="s">
-        <v>415</v>
+        <v>416</v>
       </c>
       <c r="D33" s="32" t="s">
-        <v>416</v>
+        <v>417</v>
       </c>
       <c r="E33" s="29" t="s">
-        <v>435</v>
+        <v>436</v>
       </c>
       <c r="F33" s="32"/>
     </row>
     <row r="34" spans="1:6" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A34" s="48" t="s">
-        <v>417</v>
-      </c>
-      <c r="B34" s="48"/>
-      <c r="C34" s="48"/>
-      <c r="D34" s="48"/>
-      <c r="E34" s="48"/>
-      <c r="F34" s="48"/>
+      <c r="A34" s="47" t="s">
+        <v>418</v>
+      </c>
+      <c r="B34" s="47"/>
+      <c r="C34" s="47"/>
+      <c r="D34" s="47"/>
+      <c r="E34" s="47"/>
+      <c r="F34" s="47"/>
     </row>
     <row r="35" spans="1:6" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A35" s="29">
         <v>25</v>
       </c>
       <c r="B35" s="30" t="s">
-        <v>418</v>
+        <v>419</v>
       </c>
       <c r="C35" s="30" t="s">
-        <v>419</v>
+        <v>420</v>
       </c>
       <c r="D35" s="30" t="s">
-        <v>420</v>
+        <v>421</v>
       </c>
       <c r="E35" s="29" t="s">
-        <v>435</v>
+        <v>436</v>
       </c>
       <c r="F35" s="30"/>
     </row>
@@ -7136,16 +7201,16 @@
         <v>26</v>
       </c>
       <c r="B36" s="32" t="s">
-        <v>418</v>
+        <v>419</v>
       </c>
       <c r="C36" s="32" t="s">
-        <v>421</v>
+        <v>422</v>
       </c>
       <c r="D36" s="32" t="s">
-        <v>422</v>
+        <v>423</v>
       </c>
       <c r="E36" s="29" t="s">
-        <v>435</v>
+        <v>436</v>
       </c>
       <c r="F36" s="32"/>
     </row>
@@ -7154,44 +7219,44 @@
         <v>27</v>
       </c>
       <c r="B37" s="30" t="s">
-        <v>418</v>
+        <v>419</v>
       </c>
       <c r="C37" s="30" t="s">
-        <v>423</v>
+        <v>424</v>
       </c>
       <c r="D37" s="30" t="s">
-        <v>424</v>
+        <v>425</v>
       </c>
       <c r="E37" s="29" t="s">
-        <v>435</v>
+        <v>436</v>
       </c>
       <c r="F37" s="30"/>
     </row>
     <row r="38" spans="1:6" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A38" s="48" t="s">
-        <v>425</v>
-      </c>
-      <c r="B38" s="48"/>
-      <c r="C38" s="48"/>
-      <c r="D38" s="48"/>
-      <c r="E38" s="48"/>
-      <c r="F38" s="48"/>
+      <c r="A38" s="47" t="s">
+        <v>426</v>
+      </c>
+      <c r="B38" s="47"/>
+      <c r="C38" s="47"/>
+      <c r="D38" s="47"/>
+      <c r="E38" s="47"/>
+      <c r="F38" s="47"/>
     </row>
     <row r="39" spans="1:6" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A39" s="31">
         <v>28</v>
       </c>
       <c r="B39" s="32" t="s">
-        <v>426</v>
+        <v>427</v>
       </c>
       <c r="C39" s="32" t="s">
-        <v>427</v>
+        <v>428</v>
       </c>
       <c r="D39" s="32" t="s">
-        <v>428</v>
+        <v>429</v>
       </c>
       <c r="E39" s="29" t="s">
-        <v>435</v>
+        <v>436</v>
       </c>
       <c r="F39" s="32"/>
     </row>
@@ -7200,16 +7265,16 @@
         <v>29</v>
       </c>
       <c r="B40" s="30" t="s">
-        <v>426</v>
+        <v>427</v>
       </c>
       <c r="C40" s="30" t="s">
-        <v>429</v>
+        <v>430</v>
       </c>
       <c r="D40" s="30" t="s">
-        <v>430</v>
+        <v>431</v>
       </c>
       <c r="E40" s="29" t="s">
-        <v>435</v>
+        <v>436</v>
       </c>
       <c r="F40" s="30"/>
     </row>
@@ -7218,136 +7283,121 @@
         <v>30</v>
       </c>
       <c r="B41" s="32" t="s">
-        <v>426</v>
+        <v>427</v>
       </c>
       <c r="C41" s="32" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="D41" s="32" t="s">
-        <v>431</v>
+        <v>432</v>
       </c>
       <c r="E41" s="29" t="s">
-        <v>435</v>
+        <v>436</v>
       </c>
       <c r="F41" s="32"/>
     </row>
     <row r="43" spans="1:6" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A43" s="49" t="s">
-        <v>129</v>
-      </c>
-      <c r="B43" s="49"/>
-      <c r="C43" s="49"/>
-      <c r="D43" s="49"/>
-      <c r="E43" s="49"/>
-      <c r="F43" s="49"/>
+      <c r="A43" s="48" t="s">
+        <v>130</v>
+      </c>
+      <c r="B43" s="48"/>
+      <c r="C43" s="48"/>
+      <c r="D43" s="48"/>
+      <c r="E43" s="48"/>
+      <c r="F43" s="48"/>
     </row>
     <row r="44" spans="1:6" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A44" s="45" t="s">
-        <v>130</v>
-      </c>
-      <c r="B44" s="45"/>
-      <c r="C44" s="45"/>
-      <c r="D44" s="46">
+      <c r="A44" s="49" t="s">
+        <v>131</v>
+      </c>
+      <c r="B44" s="49"/>
+      <c r="C44" s="49"/>
+      <c r="D44" s="50">
         <f>COUNTA(E4:E41)</f>
         <v>30</v>
       </c>
-      <c r="E44" s="46"/>
-      <c r="F44" s="46"/>
+      <c r="E44" s="50"/>
+      <c r="F44" s="50"/>
     </row>
     <row r="45" spans="1:6" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A45" s="45" t="s">
-        <v>131</v>
-      </c>
-      <c r="B45" s="45"/>
-      <c r="C45" s="45"/>
-      <c r="D45" s="46">
+      <c r="A45" s="49" t="s">
+        <v>132</v>
+      </c>
+      <c r="B45" s="49"/>
+      <c r="C45" s="49"/>
+      <c r="D45" s="50">
         <f>COUNTIF(E4:E41,"PASS")</f>
         <v>0</v>
       </c>
-      <c r="E45" s="46"/>
-      <c r="F45" s="46"/>
+      <c r="E45" s="50"/>
+      <c r="F45" s="50"/>
     </row>
     <row r="46" spans="1:6" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A46" s="45" t="s">
-        <v>132</v>
-      </c>
-      <c r="B46" s="45"/>
-      <c r="C46" s="45"/>
-      <c r="D46" s="46">
+      <c r="A46" s="49" t="s">
+        <v>133</v>
+      </c>
+      <c r="B46" s="49"/>
+      <c r="C46" s="49"/>
+      <c r="D46" s="50">
         <f>COUNTIF(E4:E41,"FAIL")</f>
         <v>0</v>
       </c>
-      <c r="E46" s="46"/>
-      <c r="F46" s="46"/>
+      <c r="E46" s="50"/>
+      <c r="F46" s="50"/>
     </row>
     <row r="47" spans="1:6" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A47" s="45" t="s">
-        <v>133</v>
-      </c>
-      <c r="B47" s="45"/>
-      <c r="C47" s="45"/>
-      <c r="D47" s="46">
+      <c r="A47" s="49" t="s">
+        <v>134</v>
+      </c>
+      <c r="B47" s="49"/>
+      <c r="C47" s="49"/>
+      <c r="D47" s="50">
         <f>COUNTIF(E4:E41,"N/A")</f>
         <v>30</v>
       </c>
-      <c r="E47" s="46"/>
-      <c r="F47" s="46"/>
+      <c r="E47" s="50"/>
+      <c r="F47" s="50"/>
     </row>
     <row r="48" spans="1:6" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A48" s="45" t="s">
-        <v>134</v>
-      </c>
-      <c r="B48" s="45"/>
-      <c r="C48" s="45"/>
-      <c r="D48" s="47">
+      <c r="A48" s="49" t="s">
+        <v>135</v>
+      </c>
+      <c r="B48" s="49"/>
+      <c r="C48" s="49"/>
+      <c r="D48" s="51">
         <f>IFERROR(COUNTIF(E4:E41,"PASS")/(COUNTA(E4:E41)-COUNTIF(E4:E41,"N/A")),0)</f>
         <v>0</v>
       </c>
-      <c r="E48" s="47"/>
-      <c r="F48" s="47"/>
+      <c r="E48" s="51"/>
+      <c r="F48" s="51"/>
     </row>
     <row r="49" spans="1:6" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A49" s="45" t="s">
-        <v>135</v>
-      </c>
-      <c r="B49" s="45"/>
-      <c r="C49" s="45"/>
-      <c r="D49" s="46" t="str">
+      <c r="A49" s="49" t="s">
+        <v>136</v>
+      </c>
+      <c r="B49" s="49"/>
+      <c r="C49" s="49"/>
+      <c r="D49" s="50" t="str">
         <f>IF(IFERROR(COUNTIF(E4:E41,"PASS")/(COUNTA(E4:E41)-COUNTIF(E4:E41,"N/A")),0)=1,"ĐẠT YÊU CẦU","CHƯA ĐẠT - CẦN XỬ LÝ")</f>
         <v>CHƯA ĐẠT - CẦN XỬ LÝ</v>
       </c>
-      <c r="E49" s="46"/>
-      <c r="F49" s="46"/>
+      <c r="E49" s="50"/>
+      <c r="F49" s="50"/>
     </row>
     <row r="51" spans="1:6" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A51" s="45" t="s">
-        <v>136</v>
-      </c>
-      <c r="B51" s="45"/>
-      <c r="C51" s="45"/>
-      <c r="D51" s="45" t="s">
+      <c r="A51" s="49" t="s">
         <v>137</v>
       </c>
-      <c r="E51" s="45"/>
-      <c r="F51" s="45"/>
+      <c r="B51" s="49"/>
+      <c r="C51" s="49"/>
+      <c r="D51" s="49" t="s">
+        <v>138</v>
+      </c>
+      <c r="E51" s="49"/>
+      <c r="F51" s="49"/>
     </row>
   </sheetData>
   <mergeCells count="25">
-    <mergeCell ref="A1:F1"/>
-    <mergeCell ref="A2:C2"/>
-    <mergeCell ref="A4:F4"/>
-    <mergeCell ref="A10:F10"/>
-    <mergeCell ref="A16:F16"/>
-    <mergeCell ref="A21:F21"/>
-    <mergeCell ref="A25:F25"/>
-    <mergeCell ref="A30:F30"/>
-    <mergeCell ref="A34:F34"/>
-    <mergeCell ref="A38:F38"/>
-    <mergeCell ref="A43:F43"/>
-    <mergeCell ref="A44:C44"/>
-    <mergeCell ref="D44:F44"/>
-    <mergeCell ref="A45:C45"/>
-    <mergeCell ref="D45:F45"/>
     <mergeCell ref="A49:C49"/>
     <mergeCell ref="D49:F49"/>
     <mergeCell ref="A51:C51"/>
@@ -7358,6 +7408,21 @@
     <mergeCell ref="D47:F47"/>
     <mergeCell ref="A48:C48"/>
     <mergeCell ref="D48:F48"/>
+    <mergeCell ref="A43:F43"/>
+    <mergeCell ref="A44:C44"/>
+    <mergeCell ref="D44:F44"/>
+    <mergeCell ref="A45:C45"/>
+    <mergeCell ref="D45:F45"/>
+    <mergeCell ref="A21:F21"/>
+    <mergeCell ref="A25:F25"/>
+    <mergeCell ref="A30:F30"/>
+    <mergeCell ref="A34:F34"/>
+    <mergeCell ref="A38:F38"/>
+    <mergeCell ref="A1:F1"/>
+    <mergeCell ref="A2:C2"/>
+    <mergeCell ref="A4:F4"/>
+    <mergeCell ref="A10:F10"/>
+    <mergeCell ref="A16:F16"/>
   </mergeCells>
   <conditionalFormatting sqref="E4:E41">
     <cfRule type="cellIs" dxfId="4" priority="2" operator="equal">
